--- a/Versão5/ARQ/Ontologia_Paisagismo.xlsx
+++ b/Versão5/ARQ/Ontologia_Paisagismo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59602415-1F5B-4F12-8B0E-9ED4DD2F8F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD95574E-C027-4118-999F-45E0EF20AEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="577" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="577" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16198" uniqueCount="1441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16198" uniqueCount="1440">
   <si>
     <t>Key</t>
   </si>
@@ -4373,9 +4373,6 @@
   </si>
   <si>
     <t>Urbanos.Amarelos</t>
-  </si>
-  <si>
-    <t>[ - ]</t>
   </si>
   <si>
     <t>Urbanísticos</t>
@@ -5073,7 +5070,56 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -5528,15 +5574,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10" style="6" customWidth="1"/>
-    <col min="2" max="2" width="51.85546875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="85" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="6"/>
+    <col min="2" max="2" width="51.84375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="85" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>35</v>
       </c>
@@ -5547,7 +5593,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>44</v>
       </c>
@@ -5558,7 +5604,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
         <v>45</v>
       </c>
@@ -5569,7 +5615,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
         <v>36</v>
       </c>
@@ -5580,7 +5626,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>37</v>
       </c>
@@ -5592,7 +5638,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>38</v>
       </c>
@@ -5604,7 +5650,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
         <v>39</v>
       </c>
@@ -5615,7 +5661,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
         <v>40</v>
       </c>
@@ -5626,7 +5672,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
         <v>48</v>
       </c>
@@ -5637,7 +5683,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
         <v>50</v>
       </c>
@@ -5648,7 +5694,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
         <v>41</v>
       </c>
@@ -5659,7 +5705,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
         <v>42</v>
       </c>
@@ -5670,7 +5716,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
         <v>51</v>
       </c>
@@ -5681,7 +5727,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
         <v>52</v>
       </c>
@@ -5692,7 +5738,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
         <v>53</v>
       </c>
@@ -5703,7 +5749,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
         <v>54</v>
       </c>
@@ -5714,7 +5760,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
         <v>43</v>
       </c>
@@ -5725,19 +5771,19 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B18" s="62">
         <f ca="1">NOW()</f>
-        <v>46248.312064004633</v>
+        <v>46249.373228472221</v>
       </c>
       <c r="C18" s="84" t="s">
         <v>1224</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="8" t="s">
         <v>1233</v>
       </c>
@@ -5748,7 +5794,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="8" t="s">
         <v>1227</v>
       </c>
@@ -5759,7 +5805,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="8" t="s">
         <v>1234</v>
       </c>
@@ -5770,7 +5816,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="8" t="s">
         <v>56</v>
       </c>
@@ -5781,7 +5827,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="8" t="s">
         <v>57</v>
       </c>
@@ -5792,7 +5838,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
         <v>58</v>
       </c>
@@ -5803,7 +5849,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
         <v>59</v>
       </c>
@@ -5815,7 +5861,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
         <v>1221</v>
       </c>
@@ -5827,7 +5873,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="8" t="s">
         <v>1341</v>
       </c>
@@ -5838,7 +5884,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="8" t="s">
         <v>1343</v>
       </c>
@@ -5849,7 +5895,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="8" t="s">
         <v>1345</v>
       </c>
@@ -5860,7 +5906,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>1347</v>
       </c>
@@ -5871,7 +5917,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>1348</v>
       </c>
@@ -5882,7 +5928,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>1349</v>
       </c>
@@ -5893,7 +5939,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>1350</v>
       </c>
@@ -5904,7 +5950,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>1351</v>
       </c>
@@ -5915,7 +5961,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>1352</v>
       </c>
@@ -5926,7 +5972,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>1353</v>
       </c>
@@ -5937,7 +5983,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>1354</v>
       </c>
@@ -5948,7 +5994,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="38" spans="1:3" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="10" t="s">
         <v>1355</v>
       </c>
@@ -5959,7 +6005,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="28" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="28" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
         <v>1357</v>
       </c>
@@ -5987,35 +6033,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA79"/>
-  <sheetFormatPr defaultColWidth="32.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="32.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" style="27" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" style="27" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" style="27" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="6.5703125" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5703125" style="27" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="255.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.5703125" style="27" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="40" style="27" customWidth="1"/>
-    <col min="25" max="25" width="41.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.28515625" style="27" customWidth="1"/>
-    <col min="27" max="27" width="255.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="32.140625" style="27"/>
+    <col min="1" max="1" width="2.23046875" customWidth="1"/>
+    <col min="2" max="2" width="4.84375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="7.4609375" style="27" customWidth="1"/>
+    <col min="4" max="4" width="10.4609375" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" style="27" customWidth="1"/>
+    <col min="6" max="6" width="9.69140625" style="27" customWidth="1"/>
+    <col min="7" max="10" width="6.4609375" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.53515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.53515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.53515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.4609375" style="27" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.23046875" style="27" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="255.69140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.61328125" style="27" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.53515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.4609375" style="27" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.921875" style="27" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6" style="27" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="37.61328125" style="27" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="30.3828125" style="27" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16" style="27" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="254.69140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="32.15234375" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13">
         <v>1</v>
       </c>
@@ -6098,7 +6144,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="99">
         <v>2</v>
       </c>
@@ -6190,7 +6236,7 @@
         <v>Large woody plant, with a single trunk and elevated crown. Height greater than 5 m, deep root, used in urban afforestation. They photosynthesize. For the Brazilian Forest Service, it is a habit of the individual defined in the National Forest Inventory.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="99">
         <v>3</v>
       </c>
@@ -6282,7 +6328,7 @@
         <v>Small to medium-sized woody plant, with several stems from the base. Height between 1 and 5 m, dense canopy, ideal for hedges and borders. They photosynthesize. For the Brazilian Forest Service, it is a habit of the patrimonialized individual as a plant.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="99">
         <v>4</v>
       </c>
@@ -6374,7 +6420,7 @@
         <v>Plant that combines characteristics of shrubs and herbaceous plants. Usually with a height of less than 1 meter. It has a woody base (like a shrub), but its upper branches are more fragile and can be herbaceous. Many species are perennials, but the taller branches can die and periodically renew themselves. Some examples of subshrubs are Lavender and Thyme.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="99">
         <v>5</v>
       </c>
@@ -6466,7 +6512,7 @@
         <v>A plant whose growth can be led to become a tree, shrub or vine. They photosynthesize.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="99">
         <v>6</v>
       </c>
@@ -6558,7 +6604,7 @@
         <v>A plant that grows by leaning on structures or other plants. They use tendrils, roots or thorns to attach themselves. With flexible stems they are planted to cover pergolas, walls and fences. They photosynthesize.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="99">
         <v>7</v>
       </c>
@@ -6650,7 +6696,7 @@
         <v>Plant with strain (support structure) of great morphological variety. They photosynthesize. For the Brazilian Forest Service, it is a habit of the individual defined in the National Forest Inventory.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="99">
         <v>8</v>
       </c>
@@ -6742,7 +6788,7 @@
         <v>Plant with a soft stem, non-woody, usually short-cycle, with low height, they are food producers, ornamental or medicinal.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="99">
         <v>9</v>
       </c>
@@ -6834,7 +6880,7 @@
         <v>Usually herbaceous plant, with narrow leaves, hollow stems and flowers grouped in spikelets.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="99">
         <v>10</v>
       </c>
@@ -6926,7 +6972,7 @@
         <v>Generic term for cultivated plants. It can include herbaceous plants, shrubs or vines, it has ornamental use. They photosynthesize.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="99">
         <v>11</v>
       </c>
@@ -7018,7 +7064,7 @@
         <v>Woody grass-type plant. with a cylindrical, hollow stem called a segmented stem by us. It can reach up to 30 meters in height. Elongated, green and resistant leaves. Rhizomatous, allowing underground propagation. Used in civil construction, crafts, food (sprouts), paper, textile fibers and ornamentation. For the Brazilian Forest Service, it is a habit of the individual defined in the National Forest Inventory.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="99">
         <v>12</v>
       </c>
@@ -7110,7 +7156,7 @@
         <v>Woody climbing plant. It germinates in the soil and grows by leaning on other plants to reach light in the forest canopy. Flexible stem capable of deforming without breaking. Use tendrils, staple roots, or adhesive endings to climb. It connects tree canopies, serves as a path for animals, increases floristic diversity. Used to make ropes, handicrafts, traditional anti-inflammatory, antirheumatic medicine. For the Brazilian Forest Service, it is a habit of the individual defined in the National Forest Inventory.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="99">
         <v>13</v>
       </c>
@@ -7202,7 +7248,7 @@
         <v>Shrubby or subshrub plant. With a fleshy, photosynthetic stem that stores water. It can be globose, columnar or racket shaped. Leaves modified into thorns, which protect and reduce evaporation. Shallow and extensive root, absorbs water quickly after rains. It has areoles that are structures exclusive to cacti, from which thorns, flowers and shoots emerge. Large, showy, hermaphroditic flowers, with varied colors. CAM metabolism (do nocturnal photosynthesis), spines, water storage. Widely used for ornamentation, food (prickly pear), fodder, folk medicine. For the Brazilian Forest Service, it is a habit of the individual defined in the National Forest Inventory.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="99">
         <v>14</v>
       </c>
@@ -7294,7 +7340,7 @@
         <v>A generic term for cultivated plants or for parts of a plant. It can include herbaceous plants, shrubs or vines, it has ornamental use. They photosynthesize.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="99">
         <v>15</v>
       </c>
@@ -7386,7 +7432,7 @@
         <v>Fungi do not photosynthesize and obtain energy by decomposition.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="99">
         <v>16</v>
       </c>
@@ -7478,7 +7524,7 @@
         <v>Botanical family.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="99">
         <v>17</v>
       </c>
@@ -7557,10 +7603,10 @@
         <v>Key-PAISA-17</v>
       </c>
       <c r="X17" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y17" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Z17" s="23" t="s">
         <v>1262</v>
@@ -7570,7 +7616,7 @@
         <v>Fauna conservation system.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="99">
         <v>18</v>
       </c>
@@ -7649,10 +7695,10 @@
         <v>Key-PAISA-18</v>
       </c>
       <c r="X18" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y18" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Z18" s="23" t="s">
         <v>1262</v>
@@ -7662,7 +7708,7 @@
         <v>Flora conservation system.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="99">
         <v>19</v>
       </c>
@@ -7741,10 +7787,10 @@
         <v>Key-PAISA-19</v>
       </c>
       <c r="X19" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y19" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Z19" s="23" t="s">
         <v>1262</v>
@@ -7754,7 +7800,7 @@
         <v>Mining conservation system.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="99">
         <v>20</v>
       </c>
@@ -7833,10 +7879,10 @@
         <v>Key-PAISA-20</v>
       </c>
       <c r="X20" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y20" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Z20" s="23" t="s">
         <v>1258</v>
@@ -7846,7 +7892,7 @@
         <v>Soil conservation system.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="99">
         <v>21</v>
       </c>
@@ -7925,10 +7971,10 @@
         <v>Key-PAISA-21</v>
       </c>
       <c r="X21" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y21" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Z21" s="23" t="s">
         <v>1262</v>
@@ -7938,7 +7984,7 @@
         <v>Created in 1997 in the Kyoto Protocol as part of the flexibility mechanisms to help countries meet emission reduction targets. Unit: Each credit is equivalent to 1 ton of Carbon Dioxide not emitted or removed from the atmosphere.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="99">
         <v>22</v>
       </c>
@@ -8017,10 +8063,10 @@
         <v>Key-PAISA-22</v>
       </c>
       <c r="X22" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y22" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Z22" s="23" t="s">
         <v>1262</v>
@@ -8030,7 +8076,7 @@
         <v>Bonds or certificates issued by entities that certify the reduction of emissions such as Verra (VCS – Verified Carbon Standard), Gold Standard, Climate Action Reserve, American Carbon Registry, INCCarbono (National Institute of Carbon Certification) or BNDES.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="99">
         <v>23</v>
       </c>
@@ -8122,7 +8168,7 @@
         <v>Planting soil characteristic: very draining sandy soil</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="99">
         <v>24</v>
       </c>
@@ -8214,7 +8260,7 @@
         <v>Planting soil characteristic: balanced draining clay soil</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="99">
         <v>25</v>
       </c>
@@ -8306,7 +8352,7 @@
         <v>Planting soil characteristic: compact soil with little drainage</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="99">
         <v>26</v>
       </c>
@@ -8385,10 +8431,10 @@
         <v>Key-PAISA-26</v>
       </c>
       <c r="X26" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y26" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Z26" s="23" t="s">
         <v>1262</v>
@@ -8398,7 +8444,7 @@
         <v>Exposure of plants in full sun: 6 or more hours of sunshine per day</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="99">
         <v>27</v>
       </c>
@@ -8477,10 +8523,10 @@
         <v>Key-PAISA-27</v>
       </c>
       <c r="X27" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y27" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Z27" s="23" t="s">
         <v>1262</v>
@@ -8490,7 +8536,7 @@
         <v>Exposure of plants in partial sun: between 3 and 6 hours of sunlight per day</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="99">
         <v>28</v>
       </c>
@@ -8569,10 +8615,10 @@
         <v>Key-PAISA-28</v>
       </c>
       <c r="X28" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y28" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Z28" s="23" t="s">
         <v>1262</v>
@@ -8582,7 +8628,7 @@
         <v>Plant exposure with less than 3 hours of sun</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="99">
         <v>29</v>
       </c>
@@ -8593,7 +8639,7 @@
         <v>1359</v>
       </c>
       <c r="D29" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E29" s="52" t="s">
         <v>1430</v>
@@ -8675,7 +8721,7 @@
         <v>Blue urban landscape element such as rivers, lakes, canals, reservoirs, sustainable drainage systems: It is an urban water channel.</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="99">
         <v>30</v>
       </c>
@@ -8686,7 +8732,7 @@
         <v>1359</v>
       </c>
       <c r="D30" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E30" s="52" t="s">
         <v>1430</v>
@@ -8768,7 +8814,7 @@
         <v>Blue urban landscape element such as rivers, lakes, canals, reservoirs, sustainable drainage systems: It is an urban water body.</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="99">
         <v>31</v>
       </c>
@@ -8779,7 +8825,7 @@
         <v>1359</v>
       </c>
       <c r="D31" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E31" s="52" t="s">
         <v>1430</v>
@@ -8861,7 +8907,7 @@
         <v>Blue urban landscape element such as rivers, lakes, canals, reservoirs, sustainable drainage systems: It is an ornamental fountain.</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="99">
         <v>32</v>
       </c>
@@ -8872,7 +8918,7 @@
         <v>1359</v>
       </c>
       <c r="D32" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E32" s="52" t="s">
         <v>1431</v>
@@ -8954,7 +9000,7 @@
         <v>Element of green urban landscaping, associated with urban parks, ecological corridors, street trees, green roofs. It is a shrub.</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="99">
         <v>33</v>
       </c>
@@ -8965,7 +9011,7 @@
         <v>1359</v>
       </c>
       <c r="D33" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E33" s="52" t="s">
         <v>1431</v>
@@ -9047,7 +9093,7 @@
         <v>Element of green urban landscaping, associated with urban parks, ecological corridors, street trees, green roofs. It's a tree.</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="99">
         <v>34</v>
       </c>
@@ -9058,7 +9104,7 @@
         <v>1359</v>
       </c>
       <c r="D34" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E34" s="52" t="s">
         <v>1431</v>
@@ -9140,7 +9186,7 @@
         <v>Element of green urban landscaping, associated with urban parks, ecological corridors, street trees, green roofs. It's a palm tree.</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="99">
         <v>35</v>
       </c>
@@ -9151,7 +9197,7 @@
         <v>1359</v>
       </c>
       <c r="D35" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E35" s="52" t="s">
         <v>1431</v>
@@ -9233,7 +9279,7 @@
         <v>Element of green urban landscaping, associated with urban parks, ecological corridors, street trees, green roofs. It is an arboreal.</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="99">
         <v>36</v>
       </c>
@@ -9244,7 +9290,7 @@
         <v>1359</v>
       </c>
       <c r="D36" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E36" s="52" t="s">
         <v>1431</v>
@@ -9326,7 +9372,7 @@
         <v>Element of green urban landscaping, associated with urban parks, ecological corridors, street trees, green roofs. Area covered by lawns or plants for vegetation cover.</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="99">
         <v>37</v>
       </c>
@@ -9337,7 +9383,7 @@
         <v>1359</v>
       </c>
       <c r="D37" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E37" s="52" t="s">
         <v>1431</v>
@@ -9419,7 +9465,7 @@
         <v>Element of green urban landscaping, associated with urban parks, ecological corridors, street trees, green roofs. Area covered with climbing plants.</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="99">
         <v>38</v>
       </c>
@@ -9430,7 +9476,7 @@
         <v>1359</v>
       </c>
       <c r="D38" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E38" s="52" t="s">
         <v>1431</v>
@@ -9512,7 +9558,7 @@
         <v>Element of green urban landscaping, associated with urban parks, ecological corridors, street trees, green roofs. Area covered with ornamental plants.</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="99">
         <v>39</v>
       </c>
@@ -9523,7 +9569,7 @@
         <v>1359</v>
       </c>
       <c r="D39" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E39" s="52" t="s">
         <v>1431</v>
@@ -9605,7 +9651,7 @@
         <v>Element of green urban landscaping, associated with urban parks, ecological corridors, street trees, green roofs. Area covered by floors composed of stones and gravel.</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="99">
         <v>40</v>
       </c>
@@ -9616,7 +9662,7 @@
         <v>1359</v>
       </c>
       <c r="D40" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E40" s="52" t="s">
         <v>1432</v>
@@ -9698,7 +9744,7 @@
         <v>Gray urban landscaping element, associated with conventional infrastructure (paving, paving, monuments). It is non-vegetable paving.</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="99">
         <v>41</v>
       </c>
@@ -9709,7 +9755,7 @@
         <v>1359</v>
       </c>
       <c r="D41" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E41" s="52" t="s">
         <v>1432</v>
@@ -9791,7 +9837,7 @@
         <v>Gray urban landscaping element, associated with conventional infrastructure (paving, paving, monuments). It is pavement for pedestrian circulation.</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="99">
         <v>42</v>
       </c>
@@ -9802,7 +9848,7 @@
         <v>1359</v>
       </c>
       <c r="D42" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E42" s="52" t="s">
         <v>1432</v>
@@ -9884,7 +9930,7 @@
         <v>Gray urban landscaping element, associated with conventional infrastructure (paving, paving, monuments). It is an urban monument.</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="99">
         <v>43</v>
       </c>
@@ -9895,7 +9941,7 @@
         <v>1359</v>
       </c>
       <c r="D43" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E43" s="52" t="s">
         <v>1432</v>
@@ -9977,7 +10023,7 @@
         <v>Gray urban landscaping element, associated with conventional infrastructure (paving, paving, monuments). It is an urban ornament.</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="99">
         <v>44</v>
       </c>
@@ -9988,7 +10034,7 @@
         <v>1359</v>
       </c>
       <c r="D44" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E44" s="52" t="s">
         <v>1433</v>
@@ -10070,7 +10116,7 @@
         <v>Yellow urban landscaping element, linked to energetic or luminous elements. It is low height pedestrian light pole.</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="99">
         <v>45</v>
       </c>
@@ -10081,7 +10127,7 @@
         <v>1359</v>
       </c>
       <c r="D45" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E45" s="52" t="s">
         <v>1433</v>
@@ -10163,7 +10209,7 @@
         <v>Yellow urban landscaping element, linked to energetic or luminous elements. It is tall light pole for lighting avenues.</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="99">
         <v>46</v>
       </c>
@@ -10174,7 +10220,7 @@
         <v>1359</v>
       </c>
       <c r="D46" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E46" s="52" t="s">
         <v>1433</v>
@@ -10256,7 +10302,7 @@
         <v>Yellow urban landscaping element, linked to energetic or luminous elements. It is power line support pole.</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="99">
         <v>47</v>
       </c>
@@ -10267,7 +10313,7 @@
         <v>1359</v>
       </c>
       <c r="D47" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E47" s="52" t="s">
         <v>1433</v>
@@ -10349,7 +10395,7 @@
         <v>Yellow urban landscaping element, linked to energetic or luminous elements. It is an urban traffic sign.</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="99">
         <v>48</v>
       </c>
@@ -10360,7 +10406,7 @@
         <v>1359</v>
       </c>
       <c r="D48" s="52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E48" s="52" t="s">
         <v>1433</v>
@@ -10442,7 +10488,7 @@
         <v>Yellow urban landscaping element, linked to energetic or luminous elements. It is a totem of urban information.</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="99">
         <v>49</v>
       </c>
@@ -10453,7 +10499,7 @@
         <v>1423</v>
       </c>
       <c r="D49" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E49" s="52" t="s">
         <v>1426</v>
@@ -10521,7 +10567,7 @@
         <v>Key-PAISA-49</v>
       </c>
       <c r="X49" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y49" s="23" t="s">
         <v>1255</v>
@@ -10534,7 +10580,7 @@
         <v>An ornamental landscape element of shallow and calm water, usually decorative. It can include aquatic plants, fish, or sculptures. Refreshes the environment and reflects the environment, enlarging the landscape</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="99">
         <v>50</v>
       </c>
@@ -10545,7 +10591,7 @@
         <v>1423</v>
       </c>
       <c r="D50" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E50" s="52" t="s">
         <v>1426</v>
@@ -10613,7 +10659,7 @@
         <v>Key-PAISA-50</v>
       </c>
       <c r="X50" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y50" s="23" t="s">
         <v>1255</v>
@@ -10626,7 +10672,7 @@
         <v>Ornamental landscape element that uses moving water to create visual, sound and sensory effects in gardens, squares and public spaces</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="99">
         <v>51</v>
       </c>
@@ -10637,7 +10683,7 @@
         <v>1423</v>
       </c>
       <c r="D51" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E51" s="52" t="s">
         <v>1426</v>
@@ -10705,7 +10751,7 @@
         <v>Key-PAISA-51</v>
       </c>
       <c r="X51" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y51" s="23" t="s">
         <v>1255</v>
@@ -10718,7 +10764,7 @@
         <v>Ornamental landscaping element that simulates the natural flow of falling water, integrating aesthetics, shading, freshness and sound into the landscaping project</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="99">
         <v>52</v>
       </c>
@@ -10729,7 +10775,7 @@
         <v>1423</v>
       </c>
       <c r="D52" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E52" s="52" t="s">
         <v>1427</v>
@@ -10810,7 +10856,7 @@
         <v>Dense grouping of trees, with a natural or semi-natural appearance. Ideal for contemplation areas and wildlife refuge</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="99">
         <v>53</v>
       </c>
@@ -10821,7 +10867,7 @@
         <v>1423</v>
       </c>
       <c r="D53" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E53" s="52" t="s">
         <v>1427</v>
@@ -10902,7 +10948,7 @@
         <v>A path flanked by trees, usually symmetrical and with an aesthetic and shading function.</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="99">
         <v>54</v>
       </c>
@@ -10913,7 +10959,7 @@
         <v>1423</v>
       </c>
       <c r="D54" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E54" s="52" t="s">
         <v>1427</v>
@@ -10994,7 +11040,7 @@
         <v>Strip of vegetation used to delimit paths, flowerbeds or buildings. Usually composed of small flowering plants. Create visual finish and spatial organization</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="99">
         <v>55</v>
       </c>
@@ -11005,7 +11051,7 @@
         <v>1423</v>
       </c>
       <c r="D55" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E55" s="52" t="s">
         <v>1427</v>
@@ -11086,7 +11132,7 @@
         <v>Class used to identify and position the plants used on the sidewalks of a development</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="99">
         <v>56</v>
       </c>
@@ -11097,7 +11143,7 @@
         <v>1423</v>
       </c>
       <c r="D56" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E56" s="52" t="s">
         <v>1427</v>
@@ -11178,7 +11224,7 @@
         <v>Compact grouping of plants of the same species or function to create visual impact, fill, or enhancement. It can be shrubby, herbaceous or flowery</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="99">
         <v>57</v>
       </c>
@@ -11189,7 +11235,7 @@
         <v>1423</v>
       </c>
       <c r="D57" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E57" s="52" t="s">
         <v>1427</v>
@@ -11270,7 +11316,7 @@
         <v>Line of plants arranged linearly. Used for hedges, delineation or marking of visual axes</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="99">
         <v>58</v>
       </c>
@@ -11281,7 +11327,7 @@
         <v>1423</v>
       </c>
       <c r="D58" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E58" s="52" t="s">
         <v>1427</v>
@@ -11362,7 +11408,7 @@
         <v>Plants used on the sidewalks of a project</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="99">
         <v>59</v>
       </c>
@@ -11373,7 +11419,7 @@
         <v>1423</v>
       </c>
       <c r="D59" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E59" s="52" t="s">
         <v>1427</v>
@@ -11454,7 +11500,7 @@
         <v>Class used to identify and position the plants used in the pergolas of a project</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="99">
         <v>60</v>
       </c>
@@ -11465,7 +11511,7 @@
         <v>1423</v>
       </c>
       <c r="D60" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E60" s="52" t="s">
         <v>1427</v>
@@ -11546,7 +11592,7 @@
         <v>Landscape element used to identify and position areas of grass flooring in a garden or landscaping project</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="99">
         <v>61</v>
       </c>
@@ -11557,7 +11603,7 @@
         <v>1423</v>
       </c>
       <c r="D61" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E61" s="52" t="s">
         <v>1427</v>
@@ -11638,7 +11684,7 @@
         <v>Landscape element used to identify and position plants used as boundaries or fences</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="99">
         <v>62</v>
       </c>
@@ -11649,7 +11695,7 @@
         <v>1423</v>
       </c>
       <c r="D62" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E62" s="52" t="s">
         <v>1427</v>
@@ -11730,7 +11776,7 @@
         <v>Landscape element created by association of several species forming a sculptural plant volume that can combine colors and textures in the garden</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="99">
         <v>63</v>
       </c>
@@ -11741,7 +11787,7 @@
         <v>1423</v>
       </c>
       <c r="D63" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E63" s="52" t="s">
         <v>1427</v>
@@ -11809,7 +11855,7 @@
         <v>Key-PAISA-63</v>
       </c>
       <c r="X63" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y63" s="23" t="s">
         <v>1255</v>
@@ -11822,7 +11868,7 @@
         <v>Square characterized by little or no presence of vegetation elements. For rest, meditation or aesthetic appreciation of sculptural elements. Includes seats.</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="99">
         <v>64</v>
       </c>
@@ -11833,7 +11879,7 @@
         <v>1423</v>
       </c>
       <c r="D64" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E64" s="52" t="s">
         <v>1427</v>
@@ -11901,7 +11947,7 @@
         <v>Key-PAISA-64</v>
       </c>
       <c r="X64" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y64" s="23" t="s">
         <v>1255</v>
@@ -11914,7 +11960,7 @@
         <v>Square characterized by the slight presence of vegetation elements. Large spaces prepared for multitudinous events, with symbolic and sculptural elements. Includes seats.</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="99">
         <v>65</v>
       </c>
@@ -11925,7 +11971,7 @@
         <v>1423</v>
       </c>
       <c r="D65" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E65" s="52" t="s">
         <v>1427</v>
@@ -11993,7 +12039,7 @@
         <v>Key-PAISA-65</v>
       </c>
       <c r="X65" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y65" s="23" t="s">
         <v>1255</v>
@@ -12006,7 +12052,7 @@
         <v>Square with abundant presence of elements, vegetation and installations of recreational objects for young people and adults. Prepared with equipment for the elderly, it includes benches and tables for games.</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="99">
         <v>66</v>
       </c>
@@ -12017,7 +12063,7 @@
         <v>1423</v>
       </c>
       <c r="D66" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E66" s="52" t="s">
         <v>1427</v>
@@ -12085,7 +12131,7 @@
         <v>Key-PAISA-66</v>
       </c>
       <c r="X66" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y66" s="23" t="s">
         <v>1255</v>
@@ -12098,7 +12144,7 @@
         <v>Square with abundant presence of elements, vegetation and installations of recreational objects for all ages. Prepared for the installation of sales stations, it can be an avenue edge and serve as a space for the modal transfer of public transport.</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="99">
         <v>67</v>
       </c>
@@ -12109,7 +12155,7 @@
         <v>1423</v>
       </c>
       <c r="D67" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E67" s="52" t="s">
         <v>1427</v>
@@ -12177,7 +12223,7 @@
         <v>Key-PAISA-67</v>
       </c>
       <c r="X67" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y67" s="23" t="s">
         <v>1255</v>
@@ -12190,7 +12236,7 @@
         <v>Square with abundant presence of elements, vegetation and installations of recreational objects for all ages. Prepared to receive children and adults, preferably located in quiet streets, with little vehicular movement. Prepared for the coexistence of adults and children.</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="99">
         <v>68</v>
       </c>
@@ -12201,7 +12247,7 @@
         <v>1423</v>
       </c>
       <c r="D68" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E68" s="52" t="s">
         <v>1427</v>
@@ -12269,7 +12315,7 @@
         <v>Key-PAISA-68</v>
       </c>
       <c r="X68" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y68" s="23" t="s">
         <v>1255</v>
@@ -12282,7 +12328,7 @@
         <v>Green or dry space for rest, meditation or aesthetic appreciation. Includes benches, aromatic spices, shading and sensory elements</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="99">
         <v>69</v>
       </c>
@@ -12293,7 +12339,7 @@
         <v>1423</v>
       </c>
       <c r="D69" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E69" s="52" t="s">
         <v>1427</v>
@@ -12361,7 +12407,7 @@
         <v>Key-PAISA-69</v>
       </c>
       <c r="X69" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y69" s="23" t="s">
         <v>1255</v>
@@ -12374,7 +12420,7 @@
         <v>Garden with symmetrical and geometric arrangement of plants. Pruned plants. Classical inspiration (French, Italian). Use reflective edges, lines and ponds</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="99">
         <v>70</v>
       </c>
@@ -12385,7 +12431,7 @@
         <v>1423</v>
       </c>
       <c r="D70" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E70" s="52" t="s">
         <v>1427</v>
@@ -12453,7 +12499,7 @@
         <v>Key-PAISA-70</v>
       </c>
       <c r="X70" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y70" s="23" t="s">
         <v>1255</v>
@@ -12466,7 +12512,7 @@
         <v>Asymmetrical garden, with organic shapes and freer vegetation. Naturalistic inspiration (English or tropical). Promotes biodiversity and a sense of naturalness</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="99">
         <v>71</v>
       </c>
@@ -12477,7 +12523,7 @@
         <v>1423</v>
       </c>
       <c r="D71" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E71" s="52" t="s">
         <v>1427</v>
@@ -12545,7 +12591,7 @@
         <v>Key-PAISA-71</v>
       </c>
       <c r="X71" s="23" t="s">
-        <v>1434</v>
+        <v>1</v>
       </c>
       <c r="Y71" s="23" t="s">
         <v>1255</v>
@@ -12558,7 +12604,7 @@
         <v>Minimalist and contemplative garden, made of ornamental stones (granite, pebbles, quartzite, basalt) with gravel or sand to cover the ground. Xerophytic (drought-adapted) plants, such as succulents and cacti. Use of logs, sculptures, or lanterns as focal points. Symmetry or controlled asymmetry. Contrasting textures between rocks and vegetation</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="99">
         <v>72</v>
       </c>
@@ -12569,7 +12615,7 @@
         <v>1423</v>
       </c>
       <c r="D72" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E72" s="52" t="s">
         <v>1428</v>
@@ -12650,7 +12696,7 @@
         <v>Landscape element used to identify and position the dry floor areas of a garden or landscaping project</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="99">
         <v>73</v>
       </c>
@@ -12661,7 +12707,7 @@
         <v>1423</v>
       </c>
       <c r="D73" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E73" s="52" t="s">
         <v>1428</v>
@@ -12742,7 +12788,7 @@
         <v>Landscape element like Public Square Bench.</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="99">
         <v>74</v>
       </c>
@@ -12753,7 +12799,7 @@
         <v>1423</v>
       </c>
       <c r="D74" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E74" s="52" t="s">
         <v>1428</v>
@@ -12834,7 +12880,7 @@
         <v>Landscape element like Public square table.</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="99">
         <v>75</v>
       </c>
@@ -12845,7 +12891,7 @@
         <v>1423</v>
       </c>
       <c r="D75" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E75" s="52" t="s">
         <v>1428</v>
@@ -12926,7 +12972,7 @@
         <v>Landscaping element like Games Table for public square.</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="99">
         <v>76</v>
       </c>
@@ -12937,7 +12983,7 @@
         <v>1423</v>
       </c>
       <c r="D76" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E76" s="52" t="s">
         <v>1428</v>
@@ -13018,7 +13064,7 @@
         <v>Landscape element like Sculpture of a public square.</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="99">
         <v>77</v>
       </c>
@@ -13029,7 +13075,7 @@
         <v>1423</v>
       </c>
       <c r="D77" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E77" s="52" t="s">
         <v>1428</v>
@@ -13110,7 +13156,7 @@
         <v>Landscape element like Monument of a public square.</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="99">
         <v>78</v>
       </c>
@@ -13121,7 +13167,7 @@
         <v>1423</v>
       </c>
       <c r="D78" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E78" s="52" t="s">
         <v>1429</v>
@@ -13202,7 +13248,7 @@
         <v>Landscape element like Public lighting pole.</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="99">
         <v>79</v>
       </c>
@@ -13213,7 +13259,7 @@
         <v>1423</v>
       </c>
       <c r="D79" s="52" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E79" s="52" t="s">
         <v>1429</v>
@@ -13296,56 +13342,86 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:C1 L1:W1 Y1:Z16 L2:Q28 X49:Z51 L49:Q71 B49:B79 Y52:Y72 Z52:Z74 L72:P79 Y75:Z77 A80:C1048576 L80:W1048576 Y80:XFD1048576">
-    <cfRule type="cellIs" dxfId="16" priority="426" operator="equal">
+  <conditionalFormatting sqref="A1:C1 L1:W1 Y1:Z16 L2:Q28 L49:Q71 B49:B79 Y52:Y72 Z52:Z74 L72:P79 Y75:Z77 A80:C1048576 L80:W1048576 Y80:XFD1048576 Y49:Z51">
+    <cfRule type="cellIs" dxfId="23" priority="433" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q72:Q79">
-    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="23" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X78">
+    <cfRule type="containsText" dxfId="19" priority="25" operator="containsText" text="null">
+      <formula>NOT(ISERROR(SEARCH("null",X78)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X73:Y74">
+    <cfRule type="cellIs" dxfId="18" priority="24" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X17:Z22">
+    <cfRule type="cellIs" dxfId="17" priority="58" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z26:Z28">
+    <cfRule type="cellIs" dxfId="16" priority="9" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y23:Z25">
+    <cfRule type="cellIs" dxfId="15" priority="53" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1:AA79 A2:B2 B3:B48 A3:A79">
+    <cfRule type="cellIs" dxfId="14" priority="22" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB1:XFD79 S2:U79 D29:D48 L29:P48">
+    <cfRule type="cellIs" dxfId="13" priority="13" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X26:Y26">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X27:Y27">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X28:Y28">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X49">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X50">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X51">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X63:X71">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X78">
-    <cfRule type="containsText" dxfId="12" priority="18" operator="containsText" text="null">
-      <formula>NOT(ISERROR(SEARCH("null",X78)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X73:Y74">
-    <cfRule type="cellIs" dxfId="11" priority="17" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X17:Z22">
-    <cfRule type="cellIs" dxfId="10" priority="51" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X26:Z28">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y23:Z25">
-    <cfRule type="cellIs" dxfId="8" priority="46" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA79 A2:B2 B3:B48 A3:A79">
-    <cfRule type="cellIs" dxfId="7" priority="15" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB1:XFD79 S2:U79 L29:P48 D29:D48">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13357,15 +13433,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.28515625" style="1" customWidth="1"/>
-    <col min="2" max="10" width="5.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="5.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="1" max="1" width="2.3046875" style="1" customWidth="1"/>
+    <col min="2" max="10" width="5.15234375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.53515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
         <v>22</v>
       </c>
@@ -13430,7 +13506,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -13498,7 +13574,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13511,14 +13587,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="3.42578125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3828125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
+    <col min="2" max="2" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.15234375" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="12.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18">
         <v>1</v>
       </c>
@@ -13532,7 +13608,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12">
         <v>2</v>
       </c>
@@ -13546,7 +13622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>3</v>
       </c>
@@ -13560,7 +13636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>4</v>
       </c>
@@ -13574,13 +13650,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
     </row>
-    <row r="6" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6"/>
@@ -13588,7 +13664,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4">
-    <cfRule type="cellIs" dxfId="4" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13600,65 +13676,65 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC9BE003-A289-428E-9141-72F001D0AED0}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:BA299"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" style="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" style="89" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="89" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" style="89" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" style="89" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" style="89" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.84375" style="89" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.3828125" style="89" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.3046875" style="89" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.15234375" style="89" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.84375" style="89" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.84375" style="89" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.53515625" style="89" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" style="89" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.28515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.3046875" style="89" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" style="89" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" style="89" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="89" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="90.5703125" style="89" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.85546875" style="89" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.28515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="90.53515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.84375" style="89" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.3046875" style="89" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8" style="89" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.15234375" style="89" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="11" style="89" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.85546875" style="89" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.85546875" style="89" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.85546875" style="89" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" style="89" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.5703125" style="89" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.28515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.28515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.5703125" style="89" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="39.28515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.15234375" style="89" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.3046875" style="89" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.84375" style="89" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.84375" style="89" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.84375" style="89" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.53515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.53515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.3046875" style="89" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.3046875" style="89" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.15234375" style="89" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.53515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="39.3046875" style="89" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="6" style="89" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="255.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="9.140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="219.85546875" style="89" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="4.28515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="26.140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="255.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="9.15234375" style="89" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="219.84375" style="89" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="4.3046875" style="89" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="26.15234375" style="89" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="10" style="89" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="4.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="8.42578125" style="89" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="5.7109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="4.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.3828125" style="89" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="5.69140625" style="89" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="15" style="89" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="7.28515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="17.28515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="54" max="16384" width="9.28515625" style="89"/>
+    <col min="52" max="52" width="7.3046875" style="89" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="17.3046875" style="89" bestFit="1" customWidth="1"/>
+    <col min="54" max="16384" width="9.3046875" style="89"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="22">
         <v>1</v>
       </c>
@@ -13817,7 +13893,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="2" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="30">
         <v>2</v>
       </c>
@@ -13978,7 +14054,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="3" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="30">
         <v>3</v>
       </c>
@@ -14139,7 +14215,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="4" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="30">
         <v>4</v>
       </c>
@@ -14300,7 +14376,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="5" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="30">
         <v>5</v>
       </c>
@@ -14461,7 +14537,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="6" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="30">
         <v>6</v>
       </c>
@@ -14622,7 +14698,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="7" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="30">
         <v>7</v>
       </c>
@@ -14783,7 +14859,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="8" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="30">
         <v>8</v>
       </c>
@@ -14944,7 +15020,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="9" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="30">
         <v>9</v>
       </c>
@@ -15105,7 +15181,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="10" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="30">
         <v>10</v>
       </c>
@@ -15266,7 +15342,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="11" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="30">
         <v>11</v>
       </c>
@@ -15427,7 +15503,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="12" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="30">
         <v>12</v>
       </c>
@@ -15588,7 +15664,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="13" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="30">
         <v>13</v>
       </c>
@@ -15749,7 +15825,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="14" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="30">
         <v>14</v>
       </c>
@@ -15910,7 +15986,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="15" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="30">
         <v>15</v>
       </c>
@@ -16071,7 +16147,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="16" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="30">
         <v>16</v>
       </c>
@@ -16232,7 +16308,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="17" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="30">
         <v>17</v>
       </c>
@@ -16393,7 +16469,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="18" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="30">
         <v>18</v>
       </c>
@@ -16554,7 +16630,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="19" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="30">
         <v>19</v>
       </c>
@@ -16715,7 +16791,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="20" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="30">
         <v>20</v>
       </c>
@@ -16876,7 +16952,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="21" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="30">
         <v>21</v>
       </c>
@@ -17037,7 +17113,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="22" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="30">
         <v>22</v>
       </c>
@@ -17198,7 +17274,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="23" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="30">
         <v>23</v>
       </c>
@@ -17359,7 +17435,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="24" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="30">
         <v>24</v>
       </c>
@@ -17520,7 +17596,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="25" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="30">
         <v>25</v>
       </c>
@@ -17681,7 +17757,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="26" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="30">
         <v>26</v>
       </c>
@@ -17842,7 +17918,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="27" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="30">
         <v>27</v>
       </c>
@@ -18003,7 +18079,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="28" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="30">
         <v>28</v>
       </c>
@@ -18164,7 +18240,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="29" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="30">
         <v>29</v>
       </c>
@@ -18325,7 +18401,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="30" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="30">
         <v>30</v>
       </c>
@@ -18486,7 +18562,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="31" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="30">
         <v>31</v>
       </c>
@@ -18647,7 +18723,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="32" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="30">
         <v>32</v>
       </c>
@@ -18808,7 +18884,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="33" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="30">
         <v>33</v>
       </c>
@@ -18969,7 +19045,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="34" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="30">
         <v>34</v>
       </c>
@@ -19130,7 +19206,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="35" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="30">
         <v>35</v>
       </c>
@@ -19291,7 +19367,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="36" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="30">
         <v>36</v>
       </c>
@@ -19452,7 +19528,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="37" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="30">
         <v>37</v>
       </c>
@@ -19613,7 +19689,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="38" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="30">
         <v>38</v>
       </c>
@@ -19774,7 +19850,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="39" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="30">
         <v>39</v>
       </c>
@@ -19935,7 +20011,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="40" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="30">
         <v>40</v>
       </c>
@@ -20096,7 +20172,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="41" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="30">
         <v>41</v>
       </c>
@@ -20257,7 +20333,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="42" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="30">
         <v>42</v>
       </c>
@@ -20418,7 +20494,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="43" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="30">
         <v>43</v>
       </c>
@@ -20579,7 +20655,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="44" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="30">
         <v>44</v>
       </c>
@@ -20740,7 +20816,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="45" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="30">
         <v>45</v>
       </c>
@@ -20901,7 +20977,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="46" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="30">
         <v>46</v>
       </c>
@@ -21062,7 +21138,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="47" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="30">
         <v>47</v>
       </c>
@@ -21223,7 +21299,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="48" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="30">
         <v>48</v>
       </c>
@@ -21384,7 +21460,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="49" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="30">
         <v>49</v>
       </c>
@@ -21545,7 +21621,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="50" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="30">
         <v>50</v>
       </c>
@@ -21706,7 +21782,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="51" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="30">
         <v>51</v>
       </c>
@@ -21867,7 +21943,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="52" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="30">
         <v>52</v>
       </c>
@@ -22028,7 +22104,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="53" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="30">
         <v>53</v>
       </c>
@@ -22189,7 +22265,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="54" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="30">
         <v>54</v>
       </c>
@@ -22350,7 +22426,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="55" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="30">
         <v>55</v>
       </c>
@@ -22511,7 +22587,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="56" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="30">
         <v>56</v>
       </c>
@@ -22672,7 +22748,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="57" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="30">
         <v>57</v>
       </c>
@@ -22833,7 +22909,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="58" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="30">
         <v>58</v>
       </c>
@@ -22994,7 +23070,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="59" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="30">
         <v>59</v>
       </c>
@@ -23155,7 +23231,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="60" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="30">
         <v>60</v>
       </c>
@@ -23316,7 +23392,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="61" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="30">
         <v>61</v>
       </c>
@@ -23477,7 +23553,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="62" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="30">
         <v>62</v>
       </c>
@@ -23638,7 +23714,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="63" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="30">
         <v>63</v>
       </c>
@@ -23799,7 +23875,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="64" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="30">
         <v>64</v>
       </c>
@@ -23960,7 +24036,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="65" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="30">
         <v>65</v>
       </c>
@@ -24121,7 +24197,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="66" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="30">
         <v>66</v>
       </c>
@@ -24282,7 +24358,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="67" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="30">
         <v>67</v>
       </c>
@@ -24443,7 +24519,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="68" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="30">
         <v>68</v>
       </c>
@@ -24604,7 +24680,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="69" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="30">
         <v>69</v>
       </c>
@@ -24765,7 +24841,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="70" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="30">
         <v>70</v>
       </c>
@@ -24926,7 +25002,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="71" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="30">
         <v>71</v>
       </c>
@@ -25087,7 +25163,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="72" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="30">
         <v>72</v>
       </c>
@@ -25248,7 +25324,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="73" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="30">
         <v>73</v>
       </c>
@@ -25409,7 +25485,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="74" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="30">
         <v>74</v>
       </c>
@@ -25570,7 +25646,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="75" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="30">
         <v>75</v>
       </c>
@@ -25731,7 +25807,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="76" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="30">
         <v>76</v>
       </c>
@@ -25892,7 +25968,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="77" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="30">
         <v>77</v>
       </c>
@@ -26053,7 +26129,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="78" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="30">
         <v>78</v>
       </c>
@@ -26214,7 +26290,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="79" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="30">
         <v>79</v>
       </c>
@@ -26375,7 +26451,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="80" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="30">
         <v>80</v>
       </c>
@@ -26536,7 +26612,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="81" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="30">
         <v>81</v>
       </c>
@@ -26697,7 +26773,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="82" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="30">
         <v>82</v>
       </c>
@@ -26858,7 +26934,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="83" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="30">
         <v>83</v>
       </c>
@@ -27019,7 +27095,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="84" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="30">
         <v>84</v>
       </c>
@@ -27180,7 +27256,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="85" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="30">
         <v>85</v>
       </c>
@@ -27341,7 +27417,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="86" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="30">
         <v>86</v>
       </c>
@@ -27502,7 +27578,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="87" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30">
         <v>87</v>
       </c>
@@ -27663,7 +27739,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="88" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="30">
         <v>88</v>
       </c>
@@ -27824,7 +27900,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="89" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="30">
         <v>89</v>
       </c>
@@ -27985,7 +28061,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="90" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="30">
         <v>90</v>
       </c>
@@ -28146,7 +28222,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="91" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="30">
         <v>91</v>
       </c>
@@ -28307,7 +28383,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="92" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="30">
         <v>92</v>
       </c>
@@ -28468,7 +28544,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="93" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30">
         <v>93</v>
       </c>
@@ -28629,7 +28705,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="94" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30">
         <v>94</v>
       </c>
@@ -28790,7 +28866,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="95" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30">
         <v>95</v>
       </c>
@@ -28951,7 +29027,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="96" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="30">
         <v>96</v>
       </c>
@@ -29112,7 +29188,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="97" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="30">
         <v>97</v>
       </c>
@@ -29273,7 +29349,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="98" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30">
         <v>98</v>
       </c>
@@ -29434,7 +29510,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="99" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30">
         <v>99</v>
       </c>
@@ -29595,7 +29671,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="100" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="30">
         <v>100</v>
       </c>
@@ -29756,7 +29832,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="101" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="30">
         <v>101</v>
       </c>
@@ -29917,7 +29993,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="102" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="30">
         <v>102</v>
       </c>
@@ -30078,7 +30154,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="103" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="30">
         <v>103</v>
       </c>
@@ -30239,7 +30315,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="104" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="30">
         <v>104</v>
       </c>
@@ -30400,7 +30476,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="105" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="30">
         <v>105</v>
       </c>
@@ -30561,7 +30637,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="106" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="30">
         <v>106</v>
       </c>
@@ -30722,7 +30798,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="107" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30">
         <v>107</v>
       </c>
@@ -30883,7 +30959,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="108" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="30">
         <v>108</v>
       </c>
@@ -31044,7 +31120,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="109" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30">
         <v>109</v>
       </c>
@@ -31205,7 +31281,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="110" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="30">
         <v>110</v>
       </c>
@@ -31366,7 +31442,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="111" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="30">
         <v>111</v>
       </c>
@@ -31527,7 +31603,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="112" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="30">
         <v>112</v>
       </c>
@@ -31688,7 +31764,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="113" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="30">
         <v>113</v>
       </c>
@@ -31849,7 +31925,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="114" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="30">
         <v>114</v>
       </c>
@@ -32010,7 +32086,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="115" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="30">
         <v>115</v>
       </c>
@@ -32171,7 +32247,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="116" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="30">
         <v>116</v>
       </c>
@@ -32332,7 +32408,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="117" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30">
         <v>117</v>
       </c>
@@ -32493,7 +32569,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="118" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30">
         <v>118</v>
       </c>
@@ -32654,7 +32730,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="119" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="30">
         <v>119</v>
       </c>
@@ -32815,7 +32891,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="120" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="30">
         <v>120</v>
       </c>
@@ -32976,7 +33052,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="121" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="30">
         <v>121</v>
       </c>
@@ -33137,7 +33213,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="122" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="30">
         <v>122</v>
       </c>
@@ -33298,7 +33374,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="123" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="30">
         <v>123</v>
       </c>
@@ -33459,7 +33535,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="124" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="30">
         <v>124</v>
       </c>
@@ -33620,7 +33696,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="125" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="30">
         <v>125</v>
       </c>
@@ -33781,7 +33857,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="126" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30">
         <v>126</v>
       </c>
@@ -33942,7 +34018,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="127" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="30">
         <v>127</v>
       </c>
@@ -34103,7 +34179,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="128" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="30">
         <v>128</v>
       </c>
@@ -34264,7 +34340,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="129" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="30">
         <v>129</v>
       </c>
@@ -34425,7 +34501,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="130" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30">
         <v>130</v>
       </c>
@@ -34586,7 +34662,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="131" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="30">
         <v>131</v>
       </c>
@@ -34747,7 +34823,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="132" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30">
         <v>132</v>
       </c>
@@ -34908,7 +34984,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="133" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="30">
         <v>133</v>
       </c>
@@ -35069,7 +35145,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="134" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="30">
         <v>134</v>
       </c>
@@ -35230,7 +35306,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="135" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="30">
         <v>135</v>
       </c>
@@ -35391,7 +35467,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="136" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="30">
         <v>136</v>
       </c>
@@ -35552,7 +35628,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="137" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="30">
         <v>137</v>
       </c>
@@ -35713,7 +35789,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="138" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="30">
         <v>138</v>
       </c>
@@ -35874,7 +35950,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="139" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="30">
         <v>139</v>
       </c>
@@ -36035,7 +36111,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="140" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="30">
         <v>140</v>
       </c>
@@ -36196,7 +36272,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="141" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="30">
         <v>141</v>
       </c>
@@ -36357,7 +36433,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="142" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="30">
         <v>142</v>
       </c>
@@ -36518,7 +36594,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="143" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="30">
         <v>143</v>
       </c>
@@ -36679,7 +36755,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="144" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="30">
         <v>144</v>
       </c>
@@ -36840,7 +36916,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="145" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="30">
         <v>145</v>
       </c>
@@ -37001,7 +37077,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="146" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="30">
         <v>146</v>
       </c>
@@ -37162,7 +37238,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="147" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="30">
         <v>147</v>
       </c>
@@ -37323,7 +37399,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="148" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="30">
         <v>148</v>
       </c>
@@ -37484,7 +37560,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="149" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="30">
         <v>149</v>
       </c>
@@ -37645,7 +37721,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="150" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="30">
         <v>150</v>
       </c>
@@ -37806,7 +37882,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="151" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="30">
         <v>151</v>
       </c>
@@ -37967,7 +38043,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="152" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="30">
         <v>152</v>
       </c>
@@ -38128,7 +38204,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="153" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="30">
         <v>153</v>
       </c>
@@ -38289,7 +38365,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="154" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="30">
         <v>154</v>
       </c>
@@ -38450,7 +38526,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="155" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="30">
         <v>155</v>
       </c>
@@ -38611,7 +38687,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="156" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="30">
         <v>156</v>
       </c>
@@ -38772,7 +38848,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="157" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="30">
         <v>157</v>
       </c>
@@ -38933,7 +39009,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="158" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="30">
         <v>158</v>
       </c>
@@ -39094,7 +39170,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="159" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="30">
         <v>159</v>
       </c>
@@ -39255,7 +39331,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="160" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="30">
         <v>160</v>
       </c>
@@ -39416,7 +39492,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="161" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="30">
         <v>161</v>
       </c>
@@ -39577,7 +39653,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="162" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="30">
         <v>162</v>
       </c>
@@ -39738,7 +39814,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="163" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="30">
         <v>163</v>
       </c>
@@ -39899,7 +39975,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="164" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="30">
         <v>164</v>
       </c>
@@ -40060,7 +40136,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="165" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="30">
         <v>165</v>
       </c>
@@ -40221,7 +40297,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="166" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="30">
         <v>166</v>
       </c>
@@ -40382,7 +40458,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="167" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="30">
         <v>167</v>
       </c>
@@ -40543,7 +40619,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="168" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="30">
         <v>168</v>
       </c>
@@ -40704,7 +40780,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="169" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="30">
         <v>169</v>
       </c>
@@ -40865,7 +40941,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="170" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="30">
         <v>170</v>
       </c>
@@ -41026,7 +41102,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="171" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="30">
         <v>171</v>
       </c>
@@ -41187,7 +41263,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="172" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="30">
         <v>172</v>
       </c>
@@ -41348,7 +41424,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="173" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="30">
         <v>173</v>
       </c>
@@ -41509,7 +41585,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="174" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="30">
         <v>174</v>
       </c>
@@ -41670,7 +41746,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="175" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="30">
         <v>175</v>
       </c>
@@ -41831,7 +41907,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="176" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="30">
         <v>176</v>
       </c>
@@ -41992,7 +42068,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="177" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="30">
         <v>177</v>
       </c>
@@ -42153,7 +42229,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="178" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="30">
         <v>178</v>
       </c>
@@ -42314,7 +42390,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="179" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="30">
         <v>179</v>
       </c>
@@ -42475,7 +42551,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="180" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="30">
         <v>180</v>
       </c>
@@ -42636,7 +42712,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="181" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="30">
         <v>181</v>
       </c>
@@ -42797,7 +42873,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="182" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="30">
         <v>182</v>
       </c>
@@ -42958,7 +43034,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="183" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="30">
         <v>183</v>
       </c>
@@ -43119,7 +43195,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="184" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="30">
         <v>184</v>
       </c>
@@ -43280,7 +43356,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="185" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="30">
         <v>185</v>
       </c>
@@ -43441,7 +43517,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="186" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="30">
         <v>186</v>
       </c>
@@ -43602,7 +43678,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="187" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="30">
         <v>187</v>
       </c>
@@ -43763,7 +43839,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="188" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="30">
         <v>188</v>
       </c>
@@ -43924,7 +44000,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="189" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="30">
         <v>189</v>
       </c>
@@ -44085,7 +44161,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="190" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="30">
         <v>190</v>
       </c>
@@ -44246,7 +44322,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="191" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="30">
         <v>191</v>
       </c>
@@ -44407,7 +44483,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="192" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="30">
         <v>192</v>
       </c>
@@ -44568,7 +44644,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="193" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="30">
         <v>193</v>
       </c>
@@ -44729,7 +44805,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="194" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="30">
         <v>194</v>
       </c>
@@ -44890,7 +44966,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="195" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A195" s="30">
         <v>195</v>
       </c>
@@ -45051,7 +45127,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="196" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A196" s="30">
         <v>196</v>
       </c>
@@ -45212,7 +45288,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="197" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A197" s="30">
         <v>197</v>
       </c>
@@ -45373,7 +45449,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="198" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A198" s="30">
         <v>198</v>
       </c>
@@ -45534,7 +45610,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="199" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A199" s="30">
         <v>199</v>
       </c>
@@ -45695,7 +45771,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="200" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A200" s="30">
         <v>200</v>
       </c>
@@ -45856,7 +45932,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="201" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A201" s="30">
         <v>201</v>
       </c>
@@ -46017,7 +46093,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="202" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A202" s="30">
         <v>202</v>
       </c>
@@ -46178,7 +46254,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="203" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A203" s="30">
         <v>203</v>
       </c>
@@ -46339,7 +46415,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="204" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A204" s="30">
         <v>204</v>
       </c>
@@ -46500,7 +46576,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="205" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A205" s="30">
         <v>205</v>
       </c>
@@ -46661,7 +46737,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="206" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A206" s="30">
         <v>206</v>
       </c>
@@ -46822,7 +46898,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="207" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A207" s="30">
         <v>207</v>
       </c>
@@ -46983,7 +47059,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="208" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A208" s="30">
         <v>208</v>
       </c>
@@ -47144,7 +47220,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="209" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A209" s="30">
         <v>209</v>
       </c>
@@ -47305,7 +47381,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="210" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="30">
         <v>210</v>
       </c>
@@ -47466,7 +47542,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="211" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A211" s="30">
         <v>211</v>
       </c>
@@ -47627,7 +47703,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="212" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A212" s="30">
         <v>212</v>
       </c>
@@ -47788,7 +47864,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="213" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A213" s="30">
         <v>213</v>
       </c>
@@ -47949,7 +48025,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="214" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A214" s="30">
         <v>214</v>
       </c>
@@ -48110,7 +48186,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="215" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A215" s="30">
         <v>215</v>
       </c>
@@ -48271,7 +48347,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="216" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A216" s="30">
         <v>216</v>
       </c>
@@ -48432,7 +48508,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="217" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A217" s="30">
         <v>217</v>
       </c>
@@ -48593,7 +48669,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="218" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A218" s="30">
         <v>218</v>
       </c>
@@ -48754,7 +48830,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="219" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A219" s="30">
         <v>219</v>
       </c>
@@ -48915,7 +48991,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="220" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A220" s="30">
         <v>220</v>
       </c>
@@ -49076,7 +49152,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="221" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="30">
         <v>221</v>
       </c>
@@ -49237,7 +49313,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="222" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A222" s="30">
         <v>222</v>
       </c>
@@ -49398,7 +49474,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="223" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A223" s="30">
         <v>223</v>
       </c>
@@ -49559,7 +49635,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="224" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A224" s="30">
         <v>224</v>
       </c>
@@ -49720,7 +49796,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="225" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A225" s="30">
         <v>225</v>
       </c>
@@ -49881,7 +49957,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="226" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A226" s="30">
         <v>226</v>
       </c>
@@ -50042,7 +50118,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="227" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A227" s="30">
         <v>227</v>
       </c>
@@ -50203,7 +50279,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="228" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A228" s="30">
         <v>228</v>
       </c>
@@ -50364,7 +50440,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="229" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A229" s="30">
         <v>229</v>
       </c>
@@ -50525,7 +50601,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="230" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A230" s="30">
         <v>230</v>
       </c>
@@ -50686,7 +50762,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="231" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A231" s="30">
         <v>231</v>
       </c>
@@ -50847,7 +50923,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="232" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A232" s="30">
         <v>232</v>
       </c>
@@ -51008,7 +51084,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="233" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A233" s="30">
         <v>233</v>
       </c>
@@ -51169,7 +51245,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="234" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A234" s="30">
         <v>234</v>
       </c>
@@ -51330,7 +51406,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="235" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A235" s="30">
         <v>235</v>
       </c>
@@ -51491,7 +51567,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="236" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A236" s="30">
         <v>236</v>
       </c>
@@ -51652,7 +51728,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="237" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A237" s="30">
         <v>237</v>
       </c>
@@ -51813,7 +51889,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="238" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A238" s="30">
         <v>238</v>
       </c>
@@ -51974,7 +52050,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="239" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A239" s="30">
         <v>239</v>
       </c>
@@ -52135,7 +52211,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="240" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A240" s="30">
         <v>240</v>
       </c>
@@ -52296,7 +52372,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="241" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A241" s="30">
         <v>241</v>
       </c>
@@ -52457,7 +52533,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="242" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A242" s="30">
         <v>242</v>
       </c>
@@ -52618,7 +52694,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="243" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A243" s="30">
         <v>243</v>
       </c>
@@ -52779,7 +52855,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="244" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A244" s="30">
         <v>244</v>
       </c>
@@ -52940,7 +53016,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="245" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A245" s="30">
         <v>245</v>
       </c>
@@ -53101,7 +53177,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="246" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A246" s="30">
         <v>246</v>
       </c>
@@ -53262,7 +53338,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="247" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="30">
         <v>247</v>
       </c>
@@ -53423,7 +53499,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="248" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="30">
         <v>248</v>
       </c>
@@ -53584,7 +53660,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="249" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A249" s="30">
         <v>249</v>
       </c>
@@ -53745,7 +53821,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="250" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A250" s="30">
         <v>250</v>
       </c>
@@ -53906,7 +53982,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="251" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A251" s="30">
         <v>251</v>
       </c>
@@ -54067,7 +54143,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="252" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A252" s="30">
         <v>252</v>
       </c>
@@ -54228,7 +54304,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="253" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A253" s="30">
         <v>253</v>
       </c>
@@ -54389,7 +54465,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="254" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A254" s="30">
         <v>254</v>
       </c>
@@ -54550,7 +54626,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="255" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A255" s="30">
         <v>255</v>
       </c>
@@ -54711,7 +54787,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="256" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A256" s="30">
         <v>256</v>
       </c>
@@ -54872,7 +54948,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="257" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A257" s="30">
         <v>257</v>
       </c>
@@ -55033,7 +55109,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="258" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A258" s="30">
         <v>258</v>
       </c>
@@ -55194,7 +55270,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="259" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A259" s="30">
         <v>259</v>
       </c>
@@ -55355,7 +55431,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="260" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A260" s="30">
         <v>260</v>
       </c>
@@ -55516,7 +55592,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="261" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A261" s="30">
         <v>261</v>
       </c>
@@ -55677,7 +55753,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="262" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A262" s="30">
         <v>262</v>
       </c>
@@ -55838,7 +55914,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="263" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A263" s="30">
         <v>263</v>
       </c>
@@ -55999,7 +56075,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="264" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A264" s="30">
         <v>264</v>
       </c>
@@ -56160,7 +56236,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="265" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A265" s="30">
         <v>265</v>
       </c>
@@ -56321,7 +56397,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="266" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A266" s="30">
         <v>266</v>
       </c>
@@ -56482,7 +56558,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="267" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A267" s="30">
         <v>267</v>
       </c>
@@ -56643,7 +56719,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="268" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A268" s="30">
         <v>268</v>
       </c>
@@ -56804,7 +56880,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="269" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A269" s="30">
         <v>269</v>
       </c>
@@ -56965,7 +57041,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="270" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A270" s="30">
         <v>270</v>
       </c>
@@ -57126,7 +57202,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="271" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A271" s="30">
         <v>271</v>
       </c>
@@ -57287,7 +57363,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="272" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A272" s="30">
         <v>272</v>
       </c>
@@ -57448,7 +57524,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="273" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A273" s="30">
         <v>273</v>
       </c>
@@ -57609,7 +57685,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="274" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A274" s="30">
         <v>274</v>
       </c>
@@ -57770,7 +57846,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="275" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A275" s="30">
         <v>275</v>
       </c>
@@ -57931,7 +58007,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="276" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A276" s="30">
         <v>276</v>
       </c>
@@ -58092,7 +58168,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="277" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A277" s="30">
         <v>277</v>
       </c>
@@ -58253,7 +58329,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="278" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A278" s="30">
         <v>278</v>
       </c>
@@ -58414,7 +58490,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="279" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A279" s="30">
         <v>279</v>
       </c>
@@ -58575,7 +58651,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="280" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A280" s="30">
         <v>280</v>
       </c>
@@ -58736,7 +58812,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="281" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A281" s="30">
         <v>281</v>
       </c>
@@ -58897,7 +58973,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="282" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A282" s="30">
         <v>282</v>
       </c>
@@ -59058,7 +59134,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="283" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A283" s="30">
         <v>283</v>
       </c>
@@ -59219,7 +59295,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="284" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A284" s="30">
         <v>284</v>
       </c>
@@ -59380,7 +59456,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="285" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A285" s="30">
         <v>285</v>
       </c>
@@ -59541,7 +59617,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="286" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A286" s="30">
         <v>286</v>
       </c>
@@ -59702,7 +59778,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="287" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A287" s="30">
         <v>287</v>
       </c>
@@ -59863,7 +59939,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="288" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A288" s="30">
         <v>288</v>
       </c>
@@ -60024,7 +60100,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="289" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A289" s="30">
         <v>289</v>
       </c>
@@ -60185,7 +60261,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="290" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A290" s="30">
         <v>290</v>
       </c>
@@ -60346,7 +60422,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="291" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A291" s="30">
         <v>291</v>
       </c>
@@ -60507,7 +60583,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="292" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A292" s="30">
         <v>292</v>
       </c>
@@ -60668,7 +60744,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="293" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A293" s="30">
         <v>293</v>
       </c>
@@ -60829,7 +60905,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="294" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A294" s="30">
         <v>294</v>
       </c>
@@ -60990,7 +61066,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="295" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A295" s="30">
         <v>295</v>
       </c>
@@ -61034,7 +61110,7 @@
         <v>180</v>
       </c>
       <c r="O295" s="24" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="P295" s="26" t="s">
         <v>1271</v>
@@ -61151,7 +61227,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="296" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A296" s="30">
         <v>296</v>
       </c>
@@ -61195,7 +61271,7 @@
         <v>180</v>
       </c>
       <c r="O296" s="24" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="P296" s="26" t="s">
         <v>1271</v>
@@ -61312,7 +61388,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="297" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A297" s="30">
         <v>297</v>
       </c>
@@ -61356,7 +61432,7 @@
         <v>180</v>
       </c>
       <c r="O297" s="24" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="P297" s="26" t="s">
         <v>1271</v>
@@ -61473,7 +61549,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="298" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A298" s="30">
         <v>298</v>
       </c>
@@ -61517,7 +61593,7 @@
         <v>180</v>
       </c>
       <c r="O298" s="24" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="P298" s="26" t="s">
         <v>1271</v>
@@ -61634,7 +61710,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="299" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A299" s="30">
         <v>299</v>
       </c>
@@ -61678,7 +61754,7 @@
         <v>180</v>
       </c>
       <c r="O299" s="24" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="P299" s="26" t="s">
         <v>1271</v>
@@ -61800,16 +61876,16 @@
     <sortCondition ref="A1:A302"/>
   </sortState>
   <conditionalFormatting sqref="A1:BA299">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B299">
-    <cfRule type="duplicateValues" dxfId="2" priority="1923"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1924"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1923"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1924"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C264">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ARQ/Ontologia_Paisagismo.xlsx
+++ b/Versão5/ARQ/Ontologia_Paisagismo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC6A0C0-B275-445C-AE9B-D28B50F2761F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C37C40-92F3-49DC-B834-02BAB715E390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="577" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16434" uniqueCount="1521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16454" uniqueCount="1528">
   <si>
     <t>Key</t>
   </si>
@@ -4634,6 +4634,27 @@
   </si>
   <si>
     <t>Código ABNT</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
+  </si>
+  <si>
+    <t>Aplicativo Revit</t>
+  </si>
+  <si>
+    <t>Revit Aplication</t>
   </si>
 </sst>
 </file>
@@ -4762,7 +4783,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4901,6 +4922,24 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE79D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -4993,7 +5032,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5308,12 +5347,30 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="23">
     <dxf>
       <font>
         <b val="0"/>
@@ -5370,7 +5427,6 @@
       <font>
         <b val="0"/>
         <i/>
-        <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -5393,14 +5449,6 @@
       <font>
         <b val="0"/>
         <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -5416,6 +5464,15 @@
       <font>
         <b val="0"/>
         <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -5458,18 +5515,13 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -5485,6 +5537,22 @@
       <font>
         <b val="0"/>
         <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -6009,7 +6077,7 @@
       </c>
       <c r="B18" s="62">
         <f ca="1">NOW()</f>
-        <v>46253.627297685183</v>
+        <v>46258.593388310182</v>
       </c>
       <c r="C18" s="84" t="s">
         <v>1223</v>
@@ -6264,7 +6332,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC79"/>
+  <dimension ref="A1:AC80"/>
   <sheetFormatPr defaultColWidth="32.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
@@ -6279,7 +6347,8 @@
     <col min="13" max="13" width="15.42578125" style="27" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.5703125" style="27" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="255.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="255.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="178.5703125" style="27" customWidth="1"/>
     <col min="19" max="19" width="3.7109375" style="27" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9.7109375" style="27" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="15.42578125" style="27" bestFit="1" customWidth="1"/>
@@ -12786,7 +12855,7 @@
         <v>1252</v>
       </c>
       <c r="X67" s="98" t="str">
-        <f t="shared" ref="X67:X79" si="114">CONCATENATE("Key-PAISA-",A67)</f>
+        <f t="shared" ref="X67:X80" si="114">CONCATENATE("Key-PAISA-",A67)</f>
         <v>Key-PAISA-67</v>
       </c>
       <c r="Y67" s="23" t="s">
@@ -13741,7 +13810,7 @@
         <v>1</v>
       </c>
       <c r="T77" s="23" t="str">
-        <f t="shared" ref="T77:T79" si="147">SUBSTITUTE(C77, ".", " ")</f>
+        <f t="shared" ref="T77:V80" si="147">SUBSTITUTE(C77, ".", " ")</f>
         <v>De Paisagismo</v>
       </c>
       <c r="U77" s="23" t="str">
@@ -13876,19 +13945,19 @@
       <c r="A79" s="99">
         <v>79</v>
       </c>
-      <c r="B79" s="107" t="s">
+      <c r="B79" s="112" t="s">
         <v>74</v>
       </c>
-      <c r="C79" s="52" t="s">
+      <c r="C79" s="113" t="s">
         <v>1422</v>
       </c>
-      <c r="D79" s="52" t="s">
+      <c r="D79" s="113" t="s">
         <v>1434</v>
       </c>
-      <c r="E79" s="52" t="s">
+      <c r="E79" s="113" t="s">
         <v>1428</v>
       </c>
-      <c r="F79" s="52" t="s">
+      <c r="F79" s="113" t="s">
         <v>1415</v>
       </c>
       <c r="G79" s="96" t="s">
@@ -13969,83 +14038,183 @@
         <v>1318</v>
       </c>
     </row>
+    <row r="80" spans="1:29" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="99">
+        <v>80</v>
+      </c>
+      <c r="B80" s="112" t="s">
+        <v>74</v>
+      </c>
+      <c r="C80" s="113" t="s">
+        <v>1521</v>
+      </c>
+      <c r="D80" s="113" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E80" s="113" t="s">
+        <v>1523</v>
+      </c>
+      <c r="F80" s="113" t="s">
+        <v>1524</v>
+      </c>
+      <c r="G80" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="H80" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="I80" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="J80" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="K80" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="L80" s="108" t="str">
+        <f t="shared" ref="L80:O80" si="150">SUBSTITUTE(CONCATENATE("", C80), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M80" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N80" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>Macros</v>
+      </c>
+      <c r="O80" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P80" s="23" t="s">
+        <v>1525</v>
+      </c>
+      <c r="Q80" s="23" t="s">
+        <v>1526</v>
+      </c>
+      <c r="R80" s="23" t="s">
+        <v>1527</v>
+      </c>
+      <c r="S80" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T80" s="23" t="str">
+        <f t="shared" si="147"/>
+        <v>De API</v>
+      </c>
+      <c r="U80" s="23" t="str">
+        <f t="shared" si="147"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V80" s="109" t="str">
+        <f t="shared" si="147"/>
+        <v>Macros</v>
+      </c>
+      <c r="W80" s="23" t="s">
+        <v>1252</v>
+      </c>
+      <c r="X80" s="98" t="str">
+        <f t="shared" si="114"/>
+        <v>Key-PAISA-80</v>
+      </c>
+      <c r="Y80" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z80" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA80" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB80" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC80" s="110" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:C1 AA1:AA16 L1:Q28 L49:Q71 B49:B79 AA52:AA72 L72:P79 AA75:AA77 A80:C1048576 S1:X1 L80:X1048576 AC52:AC77 AC1:AC16 AA80:XFD1048576">
-    <cfRule type="cellIs" dxfId="21" priority="437" operator="equal">
+  <conditionalFormatting sqref="A2:B2 B3:B48 A3:A80">
+    <cfRule type="cellIs" dxfId="22" priority="29" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="20" priority="14"/>
+  <conditionalFormatting sqref="A1:C1 S1:X1 L1:Q28 L49:Q71 B49:B79 L72:P79 AA75:AA77 A81:C1048576 L81:X1048576">
+    <cfRule type="cellIs" dxfId="21" priority="440" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B80">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F79 F81:F1048576">
+    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F80">
+    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q72:Q79">
-    <cfRule type="cellIs" dxfId="19" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="30" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R80">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y17:Y22">
+    <cfRule type="cellIs" dxfId="15" priority="65" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y49:Y51 AA49:AA72 AC49:AC77">
+    <cfRule type="cellIs" dxfId="14" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y63:Y71">
-    <cfRule type="cellIs" dxfId="18" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y73:Y74 AA73:AA74">
+    <cfRule type="cellIs" dxfId="12" priority="31" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y78">
-    <cfRule type="containsText" dxfId="17" priority="29" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="11" priority="32" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",Y78)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y73:Y74 AA73:AA74">
-    <cfRule type="cellIs" dxfId="16" priority="28" operator="equal">
+  <conditionalFormatting sqref="Z1:Z79">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y17:Y22 AA17:AA22 AC17:AC22">
-    <cfRule type="cellIs" dxfId="15" priority="62" operator="equal">
+  <conditionalFormatting sqref="Z81:XFD1048576">
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y26:Y28 AA26:AA28 AC26:AC28">
-    <cfRule type="cellIs" dxfId="14" priority="9" operator="equal">
+  <conditionalFormatting sqref="AA1:AA28 AC1:AC28 Y26:Y28">
+    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y49:Y51 AA49:AA51 AC49:AC51">
-    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA23:AA25 AC23:AC25">
-    <cfRule type="cellIs" dxfId="12" priority="57" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B2 B3:B48 A3:A79">
-    <cfRule type="cellIs" dxfId="11" priority="26" operator="equal">
+  <conditionalFormatting sqref="AB1:AB79">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1:XFD79 T2:V79 D29:D48 L29:P48">
-    <cfRule type="cellIs" dxfId="10" priority="17" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R79">
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z80:Z1048576">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z1:Z79">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB1:AB79">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ARQ/Ontologia_Paisagismo.xlsx
+++ b/Versão5/ARQ/Ontologia_Paisagismo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C37C40-92F3-49DC-B834-02BAB715E390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CAB976F-5521-439C-A326-0F95E004A52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="577" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="577" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -5874,15 +5874,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10" style="6" customWidth="1"/>
-    <col min="2" max="2" width="51.85546875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="85" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="6"/>
+    <col min="2" max="2" width="51.84375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="85" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>35</v>
       </c>
@@ -5893,7 +5893,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>44</v>
       </c>
@@ -5904,7 +5904,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
         <v>45</v>
       </c>
@@ -5915,7 +5915,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
         <v>36</v>
       </c>
@@ -5926,7 +5926,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>37</v>
       </c>
@@ -5938,7 +5938,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>38</v>
       </c>
@@ -5950,7 +5950,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
         <v>39</v>
       </c>
@@ -5961,7 +5961,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
         <v>40</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
         <v>48</v>
       </c>
@@ -5983,7 +5983,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
         <v>50</v>
       </c>
@@ -5994,7 +5994,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
         <v>41</v>
       </c>
@@ -6005,7 +6005,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
         <v>42</v>
       </c>
@@ -6016,7 +6016,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
         <v>51</v>
       </c>
@@ -6027,7 +6027,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
         <v>52</v>
       </c>
@@ -6038,7 +6038,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
         <v>53</v>
       </c>
@@ -6049,7 +6049,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
         <v>54</v>
       </c>
@@ -6060,7 +6060,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
         <v>43</v>
       </c>
@@ -6071,19 +6071,19 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B18" s="62">
         <f ca="1">NOW()</f>
-        <v>46258.593388310182</v>
+        <v>46264.562965856479</v>
       </c>
       <c r="C18" s="84" t="s">
         <v>1223</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="8" t="s">
         <v>1232</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="8" t="s">
         <v>1226</v>
       </c>
@@ -6105,7 +6105,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="8" t="s">
         <v>1233</v>
       </c>
@@ -6116,7 +6116,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="8" t="s">
         <v>56</v>
       </c>
@@ -6127,7 +6127,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="8" t="s">
         <v>57</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
         <v>58</v>
       </c>
@@ -6149,7 +6149,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
         <v>59</v>
       </c>
@@ -6161,7 +6161,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
         <v>1220</v>
       </c>
@@ -6173,7 +6173,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="8" t="s">
         <v>1340</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="8" t="s">
         <v>1342</v>
       </c>
@@ -6195,7 +6195,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="8" t="s">
         <v>1344</v>
       </c>
@@ -6206,7 +6206,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>1346</v>
       </c>
@@ -6217,7 +6217,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>1347</v>
       </c>
@@ -6228,7 +6228,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>1348</v>
       </c>
@@ -6239,7 +6239,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>1349</v>
       </c>
@@ -6250,7 +6250,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>1350</v>
       </c>
@@ -6261,7 +6261,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>1351</v>
       </c>
@@ -6272,7 +6272,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>1352</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>1353</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="38" spans="1:3" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="10" t="s">
         <v>1354</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="28" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="28" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
         <v>1356</v>
       </c>
@@ -6333,37 +6333,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC80"/>
-  <sheetFormatPr defaultColWidth="32.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="32.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" style="27" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="255.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="178.5703125" style="27" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.5703125" style="27" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.5703125" style="27" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="51.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.85546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="41.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="32.140625" style="27"/>
+    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.69140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.3828125" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.53515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.3828125" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10.15234375" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.15234375" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.69140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.3828125" style="27" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.53515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.3828125" style="27" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="255.69140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="178.53515625" style="27" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.69140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.3828125" style="27" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.53515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.3046875" style="27" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.53515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="51.3828125" style="27" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.84375" style="27" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="41.69140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.3828125" style="27" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.69140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="32.15234375" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13">
         <v>1</v>
       </c>
@@ -6452,7 +6452,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="99">
         <v>2</v>
       </c>
@@ -6549,7 +6549,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="99">
         <v>3</v>
       </c>
@@ -6646,7 +6646,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="99">
         <v>4</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="99">
         <v>5</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="99">
         <v>6</v>
       </c>
@@ -6937,7 +6937,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="99">
         <v>7</v>
       </c>
@@ -7034,7 +7034,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="99">
         <v>8</v>
       </c>
@@ -7131,7 +7131,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="99">
         <v>9</v>
       </c>
@@ -7228,7 +7228,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="99">
         <v>10</v>
       </c>
@@ -7325,7 +7325,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="99">
         <v>11</v>
       </c>
@@ -7422,7 +7422,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="99">
         <v>12</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="99">
         <v>13</v>
       </c>
@@ -7616,7 +7616,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="99">
         <v>14</v>
       </c>
@@ -7713,7 +7713,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="99">
         <v>15</v>
       </c>
@@ -7810,7 +7810,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="99">
         <v>16</v>
       </c>
@@ -7907,7 +7907,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="99">
         <v>17</v>
       </c>
@@ -8004,7 +8004,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="99">
         <v>18</v>
       </c>
@@ -8101,7 +8101,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="99">
         <v>19</v>
       </c>
@@ -8198,7 +8198,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="99">
         <v>20</v>
       </c>
@@ -8295,7 +8295,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="99">
         <v>21</v>
       </c>
@@ -8392,7 +8392,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="99">
         <v>22</v>
       </c>
@@ -8489,7 +8489,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="99">
         <v>23</v>
       </c>
@@ -8586,7 +8586,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="99">
         <v>24</v>
       </c>
@@ -8683,7 +8683,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="99">
         <v>25</v>
       </c>
@@ -8780,7 +8780,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="99">
         <v>26</v>
       </c>
@@ -8877,7 +8877,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="99">
         <v>27</v>
       </c>
@@ -8974,7 +8974,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="99">
         <v>28</v>
       </c>
@@ -9071,7 +9071,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="99">
         <v>29</v>
       </c>
@@ -9169,7 +9169,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="99">
         <v>30</v>
       </c>
@@ -9267,7 +9267,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="99">
         <v>31</v>
       </c>
@@ -9365,7 +9365,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="99">
         <v>32</v>
       </c>
@@ -9463,7 +9463,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="99">
         <v>33</v>
       </c>
@@ -9561,7 +9561,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="99">
         <v>34</v>
       </c>
@@ -9659,7 +9659,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="99">
         <v>35</v>
       </c>
@@ -9757,7 +9757,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="99">
         <v>36</v>
       </c>
@@ -9855,7 +9855,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="99">
         <v>37</v>
       </c>
@@ -9953,7 +9953,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="99">
         <v>38</v>
       </c>
@@ -10051,7 +10051,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="99">
         <v>39</v>
       </c>
@@ -10149,7 +10149,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="99">
         <v>40</v>
       </c>
@@ -10247,7 +10247,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="99">
         <v>41</v>
       </c>
@@ -10345,7 +10345,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="99">
         <v>42</v>
       </c>
@@ -10443,7 +10443,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="99">
         <v>43</v>
       </c>
@@ -10541,7 +10541,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="99">
         <v>44</v>
       </c>
@@ -10639,7 +10639,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="99">
         <v>45</v>
       </c>
@@ -10737,7 +10737,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="99">
         <v>46</v>
       </c>
@@ -10835,7 +10835,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="99">
         <v>47</v>
       </c>
@@ -10933,7 +10933,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="99">
         <v>48</v>
       </c>
@@ -11031,7 +11031,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="99">
         <v>49</v>
       </c>
@@ -11128,7 +11128,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="99">
         <v>50</v>
       </c>
@@ -11225,7 +11225,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="99">
         <v>51</v>
       </c>
@@ -11322,7 +11322,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="99">
         <v>52</v>
       </c>
@@ -11419,7 +11419,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="99">
         <v>53</v>
       </c>
@@ -11516,7 +11516,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="99">
         <v>54</v>
       </c>
@@ -11613,7 +11613,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="99">
         <v>55</v>
       </c>
@@ -11710,7 +11710,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="99">
         <v>56</v>
       </c>
@@ -11807,7 +11807,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="99">
         <v>57</v>
       </c>
@@ -11904,7 +11904,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="99">
         <v>58</v>
       </c>
@@ -12001,7 +12001,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="99">
         <v>59</v>
       </c>
@@ -12098,7 +12098,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="99">
         <v>60</v>
       </c>
@@ -12195,7 +12195,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="99">
         <v>61</v>
       </c>
@@ -12292,7 +12292,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="99">
         <v>62</v>
       </c>
@@ -12389,7 +12389,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="99">
         <v>63</v>
       </c>
@@ -12486,7 +12486,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="99">
         <v>64</v>
       </c>
@@ -12583,7 +12583,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="99">
         <v>65</v>
       </c>
@@ -12680,7 +12680,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="99">
         <v>66</v>
       </c>
@@ -12777,7 +12777,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="99">
         <v>67</v>
       </c>
@@ -12874,7 +12874,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="99">
         <v>68</v>
       </c>
@@ -12971,7 +12971,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="99">
         <v>69</v>
       </c>
@@ -13068,7 +13068,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="99">
         <v>70</v>
       </c>
@@ -13165,7 +13165,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="99">
         <v>71</v>
       </c>
@@ -13262,7 +13262,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="99">
         <v>72</v>
       </c>
@@ -13359,7 +13359,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="99">
         <v>73</v>
       </c>
@@ -13456,7 +13456,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="99">
         <v>74</v>
       </c>
@@ -13553,7 +13553,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="99">
         <v>75</v>
       </c>
@@ -13650,7 +13650,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="99">
         <v>76</v>
       </c>
@@ -13747,7 +13747,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="99">
         <v>77</v>
       </c>
@@ -13844,7 +13844,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="99">
         <v>78</v>
       </c>
@@ -13941,7 +13941,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="99">
         <v>79</v>
       </c>
@@ -14038,7 +14038,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="80" spans="1:29" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:29" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="99">
         <v>80</v>
       </c>
@@ -14049,10 +14049,10 @@
         <v>1521</v>
       </c>
       <c r="D80" s="113" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E80" s="113" t="s">
         <v>1522</v>
-      </c>
-      <c r="E80" s="113" t="s">
-        <v>1523</v>
       </c>
       <c r="F80" s="113" t="s">
         <v>1524</v>
@@ -14078,11 +14078,11 @@
       </c>
       <c r="M80" s="108" t="str">
         <f t="shared" si="150"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N80" s="108" t="str">
         <f t="shared" si="150"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O80" s="108" t="str">
         <f t="shared" si="150"/>
@@ -14106,11 +14106,11 @@
       </c>
       <c r="U80" s="23" t="str">
         <f t="shared" si="147"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V80" s="109" t="str">
         <f t="shared" si="147"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W80" s="23" t="s">
         <v>1252</v>
@@ -14226,15 +14226,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.28515625" style="1" customWidth="1"/>
-    <col min="2" max="10" width="5.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="5.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="1" max="1" width="2.3046875" style="1" customWidth="1"/>
+    <col min="2" max="10" width="5.15234375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.53515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
         <v>22</v>
       </c>
@@ -14299,7 +14299,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -14380,14 +14380,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="3.42578125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3828125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
+    <col min="2" max="2" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.15234375" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="12.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18">
         <v>1</v>
       </c>
@@ -14401,7 +14401,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12">
         <v>2</v>
       </c>
@@ -14415,7 +14415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>3</v>
       </c>
@@ -14429,7 +14429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>4</v>
       </c>
@@ -14443,13 +14443,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
     </row>
-    <row r="6" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6"/>
@@ -14469,65 +14469,65 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC9BE003-A289-428E-9141-72F001D0AED0}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:BA299"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" style="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" style="89" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="89" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" style="89" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" style="89" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" style="89" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.84375" style="89" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.3828125" style="89" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.3046875" style="89" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.15234375" style="89" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.84375" style="89" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.84375" style="89" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.53515625" style="89" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" style="89" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.28515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.3046875" style="89" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" style="89" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" style="89" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="89" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="90.5703125" style="89" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.85546875" style="89" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.28515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="90.53515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.84375" style="89" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.3046875" style="89" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8" style="89" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.15234375" style="89" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="11" style="89" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.85546875" style="89" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.85546875" style="89" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.85546875" style="89" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" style="89" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.5703125" style="89" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.28515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.28515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.5703125" style="89" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="39.28515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.15234375" style="89" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.3046875" style="89" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.84375" style="89" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.84375" style="89" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.84375" style="89" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.53515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.53515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.3046875" style="89" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.3046875" style="89" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.15234375" style="89" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.53515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="39.3046875" style="89" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="6" style="89" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="255.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="9.140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="219.85546875" style="89" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="4.28515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="26.140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="255.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="9.15234375" style="89" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="219.84375" style="89" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="4.3046875" style="89" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="26.15234375" style="89" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="10" style="89" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="4.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="8.42578125" style="89" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.7109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="5.7109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="4.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.3828125" style="89" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="5.69140625" style="89" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="15" style="89" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="7.28515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="17.28515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="54" max="16384" width="9.28515625" style="89"/>
+    <col min="52" max="52" width="7.3046875" style="89" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="17.3046875" style="89" bestFit="1" customWidth="1"/>
+    <col min="54" max="16384" width="9.3046875" style="89"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="22">
         <v>1</v>
       </c>
@@ -14686,7 +14686,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="2" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="30">
         <v>2</v>
       </c>
@@ -14847,7 +14847,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="3" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="30">
         <v>3</v>
       </c>
@@ -15008,7 +15008,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="4" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="30">
         <v>4</v>
       </c>
@@ -15169,7 +15169,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="5" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="30">
         <v>5</v>
       </c>
@@ -15330,7 +15330,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="6" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="30">
         <v>6</v>
       </c>
@@ -15491,7 +15491,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="7" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="30">
         <v>7</v>
       </c>
@@ -15652,7 +15652,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="8" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="30">
         <v>8</v>
       </c>
@@ -15813,7 +15813,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="9" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="30">
         <v>9</v>
       </c>
@@ -15974,7 +15974,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="10" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="30">
         <v>10</v>
       </c>
@@ -16135,7 +16135,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="11" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="30">
         <v>11</v>
       </c>
@@ -16296,7 +16296,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="12" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="30">
         <v>12</v>
       </c>
@@ -16457,7 +16457,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="13" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="30">
         <v>13</v>
       </c>
@@ -16618,7 +16618,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="14" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="30">
         <v>14</v>
       </c>
@@ -16779,7 +16779,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="15" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="30">
         <v>15</v>
       </c>
@@ -16940,7 +16940,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="16" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="30">
         <v>16</v>
       </c>
@@ -17101,7 +17101,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="17" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="30">
         <v>17</v>
       </c>
@@ -17262,7 +17262,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="18" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="30">
         <v>18</v>
       </c>
@@ -17423,7 +17423,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="19" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="30">
         <v>19</v>
       </c>
@@ -17584,7 +17584,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="20" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="30">
         <v>20</v>
       </c>
@@ -17745,7 +17745,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="21" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="30">
         <v>21</v>
       </c>
@@ -17906,7 +17906,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="22" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="30">
         <v>22</v>
       </c>
@@ -18067,7 +18067,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="23" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="30">
         <v>23</v>
       </c>
@@ -18228,7 +18228,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="24" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="30">
         <v>24</v>
       </c>
@@ -18389,7 +18389,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="25" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="30">
         <v>25</v>
       </c>
@@ -18550,7 +18550,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="26" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="30">
         <v>26</v>
       </c>
@@ -18711,7 +18711,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="27" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="30">
         <v>27</v>
       </c>
@@ -18872,7 +18872,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="28" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="30">
         <v>28</v>
       </c>
@@ -19033,7 +19033,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="29" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="30">
         <v>29</v>
       </c>
@@ -19194,7 +19194,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="30" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="30">
         <v>30</v>
       </c>
@@ -19355,7 +19355,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="31" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="30">
         <v>31</v>
       </c>
@@ -19516,7 +19516,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="32" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="30">
         <v>32</v>
       </c>
@@ -19677,7 +19677,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="33" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="30">
         <v>33</v>
       </c>
@@ -19838,7 +19838,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="34" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="30">
         <v>34</v>
       </c>
@@ -19999,7 +19999,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="35" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="30">
         <v>35</v>
       </c>
@@ -20160,7 +20160,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="36" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="30">
         <v>36</v>
       </c>
@@ -20321,7 +20321,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="37" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="30">
         <v>37</v>
       </c>
@@ -20482,7 +20482,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="38" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="30">
         <v>38</v>
       </c>
@@ -20643,7 +20643,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="39" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="30">
         <v>39</v>
       </c>
@@ -20804,7 +20804,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="40" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="30">
         <v>40</v>
       </c>
@@ -20965,7 +20965,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="41" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="30">
         <v>41</v>
       </c>
@@ -21126,7 +21126,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="42" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="30">
         <v>42</v>
       </c>
@@ -21287,7 +21287,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="43" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="30">
         <v>43</v>
       </c>
@@ -21448,7 +21448,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="44" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="30">
         <v>44</v>
       </c>
@@ -21609,7 +21609,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="45" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="30">
         <v>45</v>
       </c>
@@ -21770,7 +21770,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="46" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="30">
         <v>46</v>
       </c>
@@ -21931,7 +21931,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="47" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="30">
         <v>47</v>
       </c>
@@ -22092,7 +22092,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="48" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="30">
         <v>48</v>
       </c>
@@ -22253,7 +22253,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="49" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="30">
         <v>49</v>
       </c>
@@ -22414,7 +22414,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="50" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="30">
         <v>50</v>
       </c>
@@ -22575,7 +22575,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="51" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="30">
         <v>51</v>
       </c>
@@ -22736,7 +22736,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="52" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="30">
         <v>52</v>
       </c>
@@ -22897,7 +22897,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="53" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="30">
         <v>53</v>
       </c>
@@ -23058,7 +23058,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="54" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="30">
         <v>54</v>
       </c>
@@ -23219,7 +23219,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="55" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="30">
         <v>55</v>
       </c>
@@ -23380,7 +23380,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="56" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="30">
         <v>56</v>
       </c>
@@ -23541,7 +23541,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="57" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="30">
         <v>57</v>
       </c>
@@ -23702,7 +23702,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="58" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="30">
         <v>58</v>
       </c>
@@ -23863,7 +23863,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="59" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="30">
         <v>59</v>
       </c>
@@ -24024,7 +24024,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="60" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="30">
         <v>60</v>
       </c>
@@ -24185,7 +24185,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="61" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="30">
         <v>61</v>
       </c>
@@ -24346,7 +24346,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="62" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="30">
         <v>62</v>
       </c>
@@ -24507,7 +24507,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="63" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="30">
         <v>63</v>
       </c>
@@ -24668,7 +24668,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="64" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="30">
         <v>64</v>
       </c>
@@ -24829,7 +24829,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="65" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="30">
         <v>65</v>
       </c>
@@ -24990,7 +24990,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="66" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="30">
         <v>66</v>
       </c>
@@ -25151,7 +25151,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="67" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="30">
         <v>67</v>
       </c>
@@ -25312,7 +25312,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="68" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="30">
         <v>68</v>
       </c>
@@ -25473,7 +25473,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="69" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="30">
         <v>69</v>
       </c>
@@ -25634,7 +25634,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="70" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="30">
         <v>70</v>
       </c>
@@ -25795,7 +25795,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="71" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="30">
         <v>71</v>
       </c>
@@ -25956,7 +25956,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="72" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="30">
         <v>72</v>
       </c>
@@ -26117,7 +26117,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="73" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="30">
         <v>73</v>
       </c>
@@ -26278,7 +26278,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="74" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="30">
         <v>74</v>
       </c>
@@ -26439,7 +26439,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="75" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="30">
         <v>75</v>
       </c>
@@ -26600,7 +26600,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="76" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="30">
         <v>76</v>
       </c>
@@ -26761,7 +26761,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="77" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="30">
         <v>77</v>
       </c>
@@ -26922,7 +26922,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="78" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="30">
         <v>78</v>
       </c>
@@ -27083,7 +27083,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="79" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="30">
         <v>79</v>
       </c>
@@ -27244,7 +27244,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="80" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="30">
         <v>80</v>
       </c>
@@ -27405,7 +27405,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="81" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="30">
         <v>81</v>
       </c>
@@ -27566,7 +27566,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="82" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="30">
         <v>82</v>
       </c>
@@ -27727,7 +27727,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="83" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="30">
         <v>83</v>
       </c>
@@ -27888,7 +27888,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="84" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="30">
         <v>84</v>
       </c>
@@ -28049,7 +28049,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="85" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="30">
         <v>85</v>
       </c>
@@ -28210,7 +28210,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="86" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="30">
         <v>86</v>
       </c>
@@ -28371,7 +28371,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="87" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30">
         <v>87</v>
       </c>
@@ -28532,7 +28532,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="88" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="30">
         <v>88</v>
       </c>
@@ -28693,7 +28693,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="89" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="30">
         <v>89</v>
       </c>
@@ -28854,7 +28854,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="90" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="30">
         <v>90</v>
       </c>
@@ -29015,7 +29015,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="91" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="30">
         <v>91</v>
       </c>
@@ -29176,7 +29176,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="92" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="30">
         <v>92</v>
       </c>
@@ -29337,7 +29337,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="93" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30">
         <v>93</v>
       </c>
@@ -29498,7 +29498,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="94" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30">
         <v>94</v>
       </c>
@@ -29659,7 +29659,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="95" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30">
         <v>95</v>
       </c>
@@ -29820,7 +29820,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="96" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="30">
         <v>96</v>
       </c>
@@ -29981,7 +29981,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="97" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="30">
         <v>97</v>
       </c>
@@ -30142,7 +30142,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="98" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30">
         <v>98</v>
       </c>
@@ -30303,7 +30303,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="99" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30">
         <v>99</v>
       </c>
@@ -30464,7 +30464,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="100" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="30">
         <v>100</v>
       </c>
@@ -30625,7 +30625,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="101" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="30">
         <v>101</v>
       </c>
@@ -30786,7 +30786,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="102" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="30">
         <v>102</v>
       </c>
@@ -30947,7 +30947,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="103" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="30">
         <v>103</v>
       </c>
@@ -31108,7 +31108,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="104" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="30">
         <v>104</v>
       </c>
@@ -31269,7 +31269,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="105" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="30">
         <v>105</v>
       </c>
@@ -31430,7 +31430,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="106" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="30">
         <v>106</v>
       </c>
@@ -31591,7 +31591,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="107" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30">
         <v>107</v>
       </c>
@@ -31752,7 +31752,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="108" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="30">
         <v>108</v>
       </c>
@@ -31913,7 +31913,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="109" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30">
         <v>109</v>
       </c>
@@ -32074,7 +32074,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="110" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="30">
         <v>110</v>
       </c>
@@ -32235,7 +32235,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="111" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="30">
         <v>111</v>
       </c>
@@ -32396,7 +32396,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="112" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="30">
         <v>112</v>
       </c>
@@ -32557,7 +32557,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="113" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="30">
         <v>113</v>
       </c>
@@ -32718,7 +32718,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="114" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="30">
         <v>114</v>
       </c>
@@ -32879,7 +32879,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="115" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="30">
         <v>115</v>
       </c>
@@ -33040,7 +33040,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="116" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="30">
         <v>116</v>
       </c>
@@ -33201,7 +33201,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="117" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30">
         <v>117</v>
       </c>
@@ -33362,7 +33362,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="118" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30">
         <v>118</v>
       </c>
@@ -33523,7 +33523,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="119" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="30">
         <v>119</v>
       </c>
@@ -33684,7 +33684,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="120" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="30">
         <v>120</v>
       </c>
@@ -33845,7 +33845,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="121" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="30">
         <v>121</v>
       </c>
@@ -34006,7 +34006,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="122" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="30">
         <v>122</v>
       </c>
@@ -34167,7 +34167,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="123" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="30">
         <v>123</v>
       </c>
@@ -34328,7 +34328,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="124" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="30">
         <v>124</v>
       </c>
@@ -34489,7 +34489,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="125" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="30">
         <v>125</v>
       </c>
@@ -34650,7 +34650,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="126" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30">
         <v>126</v>
       </c>
@@ -34811,7 +34811,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="127" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="30">
         <v>127</v>
       </c>
@@ -34972,7 +34972,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="128" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="30">
         <v>128</v>
       </c>
@@ -35133,7 +35133,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="129" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="30">
         <v>129</v>
       </c>
@@ -35294,7 +35294,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="130" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30">
         <v>130</v>
       </c>
@@ -35455,7 +35455,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="131" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="30">
         <v>131</v>
       </c>
@@ -35616,7 +35616,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="132" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30">
         <v>132</v>
       </c>
@@ -35777,7 +35777,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="133" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="30">
         <v>133</v>
       </c>
@@ -35938,7 +35938,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="134" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="30">
         <v>134</v>
       </c>
@@ -36099,7 +36099,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="135" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="30">
         <v>135</v>
       </c>
@@ -36260,7 +36260,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="136" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="30">
         <v>136</v>
       </c>
@@ -36421,7 +36421,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="137" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="30">
         <v>137</v>
       </c>
@@ -36582,7 +36582,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="138" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="30">
         <v>138</v>
       </c>
@@ -36743,7 +36743,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="139" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="30">
         <v>139</v>
       </c>
@@ -36904,7 +36904,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="140" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="30">
         <v>140</v>
       </c>
@@ -37065,7 +37065,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="141" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="30">
         <v>141</v>
       </c>
@@ -37226,7 +37226,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="142" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="30">
         <v>142</v>
       </c>
@@ -37387,7 +37387,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="143" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="30">
         <v>143</v>
       </c>
@@ -37548,7 +37548,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="144" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="30">
         <v>144</v>
       </c>
@@ -37709,7 +37709,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="145" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="30">
         <v>145</v>
       </c>
@@ -37870,7 +37870,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="146" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="30">
         <v>146</v>
       </c>
@@ -38031,7 +38031,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="147" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="30">
         <v>147</v>
       </c>
@@ -38192,7 +38192,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="148" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="30">
         <v>148</v>
       </c>
@@ -38353,7 +38353,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="149" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="30">
         <v>149</v>
       </c>
@@ -38514,7 +38514,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="150" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="30">
         <v>150</v>
       </c>
@@ -38675,7 +38675,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="151" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="30">
         <v>151</v>
       </c>
@@ -38836,7 +38836,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="152" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="30">
         <v>152</v>
       </c>
@@ -38997,7 +38997,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="153" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="30">
         <v>153</v>
       </c>
@@ -39158,7 +39158,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="154" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="30">
         <v>154</v>
       </c>
@@ -39319,7 +39319,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="155" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="30">
         <v>155</v>
       </c>
@@ -39480,7 +39480,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="156" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="30">
         <v>156</v>
       </c>
@@ -39641,7 +39641,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="157" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="30">
         <v>157</v>
       </c>
@@ -39802,7 +39802,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="158" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="30">
         <v>158</v>
       </c>
@@ -39963,7 +39963,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="159" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="30">
         <v>159</v>
       </c>
@@ -40124,7 +40124,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="160" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="30">
         <v>160</v>
       </c>
@@ -40285,7 +40285,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="161" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="30">
         <v>161</v>
       </c>
@@ -40446,7 +40446,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="162" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="30">
         <v>162</v>
       </c>
@@ -40607,7 +40607,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="163" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="30">
         <v>163</v>
       </c>
@@ -40768,7 +40768,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="164" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="30">
         <v>164</v>
       </c>
@@ -40929,7 +40929,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="165" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="30">
         <v>165</v>
       </c>
@@ -41090,7 +41090,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="166" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="30">
         <v>166</v>
       </c>
@@ -41251,7 +41251,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="167" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="30">
         <v>167</v>
       </c>
@@ -41412,7 +41412,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="168" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="30">
         <v>168</v>
       </c>
@@ -41573,7 +41573,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="169" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="30">
         <v>169</v>
       </c>
@@ -41734,7 +41734,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="170" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="30">
         <v>170</v>
       </c>
@@ -41895,7 +41895,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="171" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="30">
         <v>171</v>
       </c>
@@ -42056,7 +42056,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="172" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="30">
         <v>172</v>
       </c>
@@ -42217,7 +42217,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="173" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="30">
         <v>173</v>
       </c>
@@ -42378,7 +42378,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="174" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="30">
         <v>174</v>
       </c>
@@ -42539,7 +42539,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="175" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="30">
         <v>175</v>
       </c>
@@ -42700,7 +42700,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="176" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="30">
         <v>176</v>
       </c>
@@ -42861,7 +42861,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="177" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="30">
         <v>177</v>
       </c>
@@ -43022,7 +43022,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="178" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="30">
         <v>178</v>
       </c>
@@ -43183,7 +43183,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="179" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="30">
         <v>179</v>
       </c>
@@ -43344,7 +43344,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="180" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="30">
         <v>180</v>
       </c>
@@ -43505,7 +43505,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="181" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="30">
         <v>181</v>
       </c>
@@ -43666,7 +43666,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="182" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="30">
         <v>182</v>
       </c>
@@ -43827,7 +43827,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="183" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="30">
         <v>183</v>
       </c>
@@ -43988,7 +43988,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="184" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="30">
         <v>184</v>
       </c>
@@ -44149,7 +44149,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="185" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="30">
         <v>185</v>
       </c>
@@ -44310,7 +44310,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="186" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="30">
         <v>186</v>
       </c>
@@ -44471,7 +44471,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="187" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="30">
         <v>187</v>
       </c>
@@ -44632,7 +44632,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="188" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="30">
         <v>188</v>
       </c>
@@ -44793,7 +44793,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="189" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="30">
         <v>189</v>
       </c>
@@ -44954,7 +44954,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="190" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="30">
         <v>190</v>
       </c>
@@ -45115,7 +45115,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="191" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="30">
         <v>191</v>
       </c>
@@ -45276,7 +45276,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="192" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="30">
         <v>192</v>
       </c>
@@ -45437,7 +45437,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="193" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="30">
         <v>193</v>
       </c>
@@ -45598,7 +45598,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="194" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="30">
         <v>194</v>
       </c>
@@ -45759,7 +45759,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="195" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A195" s="30">
         <v>195</v>
       </c>
@@ -45920,7 +45920,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="196" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A196" s="30">
         <v>196</v>
       </c>
@@ -46081,7 +46081,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="197" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A197" s="30">
         <v>197</v>
       </c>
@@ -46242,7 +46242,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="198" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A198" s="30">
         <v>198</v>
       </c>
@@ -46403,7 +46403,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="199" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A199" s="30">
         <v>199</v>
       </c>
@@ -46564,7 +46564,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="200" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A200" s="30">
         <v>200</v>
       </c>
@@ -46725,7 +46725,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="201" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A201" s="30">
         <v>201</v>
       </c>
@@ -46886,7 +46886,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="202" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A202" s="30">
         <v>202</v>
       </c>
@@ -47047,7 +47047,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="203" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A203" s="30">
         <v>203</v>
       </c>
@@ -47208,7 +47208,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="204" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A204" s="30">
         <v>204</v>
       </c>
@@ -47369,7 +47369,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="205" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A205" s="30">
         <v>205</v>
       </c>
@@ -47530,7 +47530,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="206" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A206" s="30">
         <v>206</v>
       </c>
@@ -47691,7 +47691,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="207" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A207" s="30">
         <v>207</v>
       </c>
@@ -47852,7 +47852,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="208" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A208" s="30">
         <v>208</v>
       </c>
@@ -48013,7 +48013,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="209" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A209" s="30">
         <v>209</v>
       </c>
@@ -48174,7 +48174,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="210" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="30">
         <v>210</v>
       </c>
@@ -48335,7 +48335,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="211" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A211" s="30">
         <v>211</v>
       </c>
@@ -48496,7 +48496,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="212" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A212" s="30">
         <v>212</v>
       </c>
@@ -48657,7 +48657,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="213" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A213" s="30">
         <v>213</v>
       </c>
@@ -48818,7 +48818,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="214" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A214" s="30">
         <v>214</v>
       </c>
@@ -48979,7 +48979,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="215" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A215" s="30">
         <v>215</v>
       </c>
@@ -49140,7 +49140,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="216" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A216" s="30">
         <v>216</v>
       </c>
@@ -49301,7 +49301,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="217" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A217" s="30">
         <v>217</v>
       </c>
@@ -49462,7 +49462,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="218" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A218" s="30">
         <v>218</v>
       </c>
@@ -49623,7 +49623,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="219" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A219" s="30">
         <v>219</v>
       </c>
@@ -49784,7 +49784,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="220" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A220" s="30">
         <v>220</v>
       </c>
@@ -49945,7 +49945,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="221" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="30">
         <v>221</v>
       </c>
@@ -50106,7 +50106,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="222" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A222" s="30">
         <v>222</v>
       </c>
@@ -50267,7 +50267,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="223" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A223" s="30">
         <v>223</v>
       </c>
@@ -50428,7 +50428,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="224" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A224" s="30">
         <v>224</v>
       </c>
@@ -50589,7 +50589,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="225" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A225" s="30">
         <v>225</v>
       </c>
@@ -50750,7 +50750,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="226" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A226" s="30">
         <v>226</v>
       </c>
@@ -50911,7 +50911,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="227" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A227" s="30">
         <v>227</v>
       </c>
@@ -51072,7 +51072,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="228" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A228" s="30">
         <v>228</v>
       </c>
@@ -51233,7 +51233,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="229" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A229" s="30">
         <v>229</v>
       </c>
@@ -51394,7 +51394,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="230" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A230" s="30">
         <v>230</v>
       </c>
@@ -51555,7 +51555,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="231" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A231" s="30">
         <v>231</v>
       </c>
@@ -51716,7 +51716,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="232" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A232" s="30">
         <v>232</v>
       </c>
@@ -51877,7 +51877,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="233" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A233" s="30">
         <v>233</v>
       </c>
@@ -52038,7 +52038,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="234" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A234" s="30">
         <v>234</v>
       </c>
@@ -52199,7 +52199,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="235" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A235" s="30">
         <v>235</v>
       </c>
@@ -52360,7 +52360,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="236" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A236" s="30">
         <v>236</v>
       </c>
@@ -52521,7 +52521,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="237" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A237" s="30">
         <v>237</v>
       </c>
@@ -52682,7 +52682,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="238" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A238" s="30">
         <v>238</v>
       </c>
@@ -52843,7 +52843,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="239" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A239" s="30">
         <v>239</v>
       </c>
@@ -53004,7 +53004,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="240" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A240" s="30">
         <v>240</v>
       </c>
@@ -53165,7 +53165,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="241" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A241" s="30">
         <v>241</v>
       </c>
@@ -53326,7 +53326,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="242" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A242" s="30">
         <v>242</v>
       </c>
@@ -53487,7 +53487,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="243" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A243" s="30">
         <v>243</v>
       </c>
@@ -53648,7 +53648,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="244" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A244" s="30">
         <v>244</v>
       </c>
@@ -53809,7 +53809,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="245" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A245" s="30">
         <v>245</v>
       </c>
@@ -53970,7 +53970,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="246" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A246" s="30">
         <v>246</v>
       </c>
@@ -54131,7 +54131,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="247" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="30">
         <v>247</v>
       </c>
@@ -54292,7 +54292,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="248" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="30">
         <v>248</v>
       </c>
@@ -54453,7 +54453,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="249" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A249" s="30">
         <v>249</v>
       </c>
@@ -54614,7 +54614,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="250" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A250" s="30">
         <v>250</v>
       </c>
@@ -54775,7 +54775,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="251" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A251" s="30">
         <v>251</v>
       </c>
@@ -54936,7 +54936,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="252" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A252" s="30">
         <v>252</v>
       </c>
@@ -55097,7 +55097,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="253" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A253" s="30">
         <v>253</v>
       </c>
@@ -55258,7 +55258,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="254" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A254" s="30">
         <v>254</v>
       </c>
@@ -55419,7 +55419,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="255" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A255" s="30">
         <v>255</v>
       </c>
@@ -55580,7 +55580,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="256" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A256" s="30">
         <v>256</v>
       </c>
@@ -55741,7 +55741,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="257" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A257" s="30">
         <v>257</v>
       </c>
@@ -55902,7 +55902,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="258" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A258" s="30">
         <v>258</v>
       </c>
@@ -56063,7 +56063,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="259" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A259" s="30">
         <v>259</v>
       </c>
@@ -56224,7 +56224,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="260" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A260" s="30">
         <v>260</v>
       </c>
@@ -56385,7 +56385,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="261" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A261" s="30">
         <v>261</v>
       </c>
@@ -56546,7 +56546,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="262" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A262" s="30">
         <v>262</v>
       </c>
@@ -56707,7 +56707,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="263" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A263" s="30">
         <v>263</v>
       </c>
@@ -56868,7 +56868,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="264" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A264" s="30">
         <v>264</v>
       </c>
@@ -57029,7 +57029,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="265" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A265" s="30">
         <v>265</v>
       </c>
@@ -57190,7 +57190,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="266" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A266" s="30">
         <v>266</v>
       </c>
@@ -57351,7 +57351,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="267" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A267" s="30">
         <v>267</v>
       </c>
@@ -57512,7 +57512,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="268" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A268" s="30">
         <v>268</v>
       </c>
@@ -57673,7 +57673,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="269" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A269" s="30">
         <v>269</v>
       </c>
@@ -57834,7 +57834,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="270" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A270" s="30">
         <v>270</v>
       </c>
@@ -57995,7 +57995,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="271" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A271" s="30">
         <v>271</v>
       </c>
@@ -58156,7 +58156,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="272" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A272" s="30">
         <v>272</v>
       </c>
@@ -58317,7 +58317,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="273" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A273" s="30">
         <v>273</v>
       </c>
@@ -58478,7 +58478,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="274" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A274" s="30">
         <v>274</v>
       </c>
@@ -58639,7 +58639,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="275" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A275" s="30">
         <v>275</v>
       </c>
@@ -58800,7 +58800,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="276" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A276" s="30">
         <v>276</v>
       </c>
@@ -58961,7 +58961,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="277" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A277" s="30">
         <v>277</v>
       </c>
@@ -59122,7 +59122,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="278" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A278" s="30">
         <v>278</v>
       </c>
@@ -59283,7 +59283,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="279" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A279" s="30">
         <v>279</v>
       </c>
@@ -59444,7 +59444,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="280" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A280" s="30">
         <v>280</v>
       </c>
@@ -59605,7 +59605,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="281" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A281" s="30">
         <v>281</v>
       </c>
@@ -59766,7 +59766,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="282" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A282" s="30">
         <v>282</v>
       </c>
@@ -59927,7 +59927,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="283" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A283" s="30">
         <v>283</v>
       </c>
@@ -60088,7 +60088,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="284" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A284" s="30">
         <v>284</v>
       </c>
@@ -60249,7 +60249,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="285" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A285" s="30">
         <v>285</v>
       </c>
@@ -60410,7 +60410,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="286" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A286" s="30">
         <v>286</v>
       </c>
@@ -60571,7 +60571,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="287" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A287" s="30">
         <v>287</v>
       </c>
@@ -60732,7 +60732,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="288" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A288" s="30">
         <v>288</v>
       </c>
@@ -60893,7 +60893,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="289" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A289" s="30">
         <v>289</v>
       </c>
@@ -61054,7 +61054,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="290" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A290" s="30">
         <v>290</v>
       </c>
@@ -61215,7 +61215,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="291" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A291" s="30">
         <v>291</v>
       </c>
@@ -61376,7 +61376,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="292" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A292" s="30">
         <v>292</v>
       </c>
@@ -61537,7 +61537,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="293" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A293" s="30">
         <v>293</v>
       </c>
@@ -61698,7 +61698,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="294" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A294" s="30">
         <v>294</v>
       </c>
@@ -61859,7 +61859,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="295" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A295" s="30">
         <v>295</v>
       </c>
@@ -62020,7 +62020,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="296" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A296" s="30">
         <v>296</v>
       </c>
@@ -62181,7 +62181,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="297" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A297" s="30">
         <v>297</v>
       </c>
@@ -62342,7 +62342,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="298" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A298" s="30">
         <v>298</v>
       </c>
@@ -62503,7 +62503,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="299" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A299" s="30">
         <v>299</v>
       </c>

--- a/Versão5/ARQ/Ontologia_Paisagismo.xlsx
+++ b/Versão5/ARQ/Ontologia_Paisagismo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CAB976F-5521-439C-A326-0F95E004A52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88210F22-9421-434C-A551-1D547CE6013F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="577" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="577" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16454" uniqueCount="1528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16534" uniqueCount="1544">
   <si>
     <t>Key</t>
   </si>
@@ -4624,9 +4624,6 @@
     <t>Landscape element such as Totem or Panel used to inform.</t>
   </si>
   <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>Parâmetro Rvt</t>
   </si>
   <si>
@@ -4645,16 +4642,67 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
   </si>
 </sst>
 </file>
@@ -4783,7 +4831,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4934,12 +4982,6 @@
         <bgColor rgb="FFFEF2CB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE79D"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -5032,7 +5074,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5359,18 +5401,48 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="26">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -5545,14 +5617,6 @@
       <font>
         <b val="0"/>
         <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -5874,15 +5938,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="6" customWidth="1"/>
-    <col min="2" max="2" width="51.84375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="85" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.3046875" style="6"/>
+    <col min="2" max="2" width="51.85546875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="85" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.28515625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>35</v>
       </c>
@@ -5893,7 +5957,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>44</v>
       </c>
@@ -5904,7 +5968,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>45</v>
       </c>
@@ -5915,7 +5979,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>36</v>
       </c>
@@ -5926,7 +5990,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>37</v>
       </c>
@@ -5938,7 +6002,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>38</v>
       </c>
@@ -5950,7 +6014,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>39</v>
       </c>
@@ -5961,7 +6025,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>40</v>
       </c>
@@ -5972,7 +6036,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>48</v>
       </c>
@@ -5983,7 +6047,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>50</v>
       </c>
@@ -5994,7 +6058,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>41</v>
       </c>
@@ -6005,7 +6069,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>42</v>
       </c>
@@ -6016,7 +6080,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>51</v>
       </c>
@@ -6027,7 +6091,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>52</v>
       </c>
@@ -6038,7 +6102,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>53</v>
       </c>
@@ -6049,7 +6113,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>54</v>
       </c>
@@ -6060,7 +6124,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>43</v>
       </c>
@@ -6071,19 +6135,19 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B18" s="62">
         <f ca="1">NOW()</f>
-        <v>46264.562965856479</v>
+        <v>46268.509091087966</v>
       </c>
       <c r="C18" s="84" t="s">
         <v>1223</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>1232</v>
       </c>
@@ -6094,7 +6158,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>1226</v>
       </c>
@@ -6105,7 +6169,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>1233</v>
       </c>
@@ -6116,7 +6180,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>56</v>
       </c>
@@ -6127,7 +6191,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>57</v>
       </c>
@@ -6138,7 +6202,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>58</v>
       </c>
@@ -6149,7 +6213,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>59</v>
       </c>
@@ -6161,7 +6225,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>1220</v>
       </c>
@@ -6173,7 +6237,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>1340</v>
       </c>
@@ -6184,7 +6248,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>1342</v>
       </c>
@@ -6195,7 +6259,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>1344</v>
       </c>
@@ -6206,7 +6270,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
         <v>1346</v>
       </c>
@@ -6217,7 +6281,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
         <v>1347</v>
       </c>
@@ -6228,7 +6292,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
         <v>1348</v>
       </c>
@@ -6239,7 +6303,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
         <v>1349</v>
       </c>
@@ -6250,7 +6314,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
         <v>1350</v>
       </c>
@@ -6261,7 +6325,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
         <v>1351</v>
       </c>
@@ -6272,7 +6336,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
         <v>1352</v>
       </c>
@@ -6283,7 +6347,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="8" t="s">
         <v>1353</v>
       </c>
@@ -6294,7 +6358,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="38" spans="1:3" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>1354</v>
       </c>
@@ -6305,7 +6369,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="28" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="28" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="8" t="s">
         <v>1356</v>
       </c>
@@ -6332,38 +6396,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC80"/>
-  <sheetFormatPr defaultColWidth="32.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AC84"/>
+  <sheetFormatPr defaultColWidth="32.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.69140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.3828125" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.53515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.3828125" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.15234375" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.15234375" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.69140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.3828125" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.53515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.3828125" style="27" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="255.69140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="178.53515625" style="27" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.69140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.3828125" style="27" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.53515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.3046875" style="27" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.53515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="51.3828125" style="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.84375" style="27" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="41.69140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.3828125" style="27" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.69140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="32.15234375" style="27"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="255.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="178.5703125" style="27" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="51.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.85546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="41.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="32.140625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13">
         <v>1</v>
       </c>
@@ -6440,19 +6504,19 @@
         <v>78</v>
       </c>
       <c r="Z1" s="83" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="AA1" s="15" t="s">
         <v>77</v>
       </c>
       <c r="AB1" s="83" t="s">
+        <v>1518</v>
+      </c>
+      <c r="AC1" s="15" t="s">
         <v>1519</v>
       </c>
-      <c r="AC1" s="15" t="s">
-        <v>1520</v>
-      </c>
     </row>
-    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="99">
         <v>2</v>
       </c>
@@ -6536,20 +6600,20 @@
       <c r="Y2" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z2" s="23" t="s">
-        <v>1517</v>
+      <c r="Z2" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA2" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB2" s="23" t="s">
-        <v>1517</v>
+      <c r="AB2" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC2" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="99">
         <v>3</v>
       </c>
@@ -6633,20 +6697,20 @@
       <c r="Y3" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z3" s="23" t="s">
-        <v>1517</v>
+      <c r="Z3" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA3" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB3" s="23" t="s">
-        <v>1517</v>
+      <c r="AB3" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC3" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="99">
         <v>4</v>
       </c>
@@ -6730,20 +6794,20 @@
       <c r="Y4" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z4" s="23" t="s">
-        <v>1517</v>
+      <c r="Z4" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA4" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB4" s="23" t="s">
-        <v>1517</v>
+      <c r="AB4" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC4" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="99">
         <v>5</v>
       </c>
@@ -6827,20 +6891,20 @@
       <c r="Y5" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z5" s="23" t="s">
-        <v>1517</v>
+      <c r="Z5" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA5" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB5" s="23" t="s">
-        <v>1517</v>
+      <c r="AB5" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC5" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="99">
         <v>6</v>
       </c>
@@ -6924,20 +6988,20 @@
       <c r="Y6" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z6" s="23" t="s">
-        <v>1517</v>
+      <c r="Z6" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA6" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB6" s="23" t="s">
-        <v>1517</v>
+      <c r="AB6" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC6" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="99">
         <v>7</v>
       </c>
@@ -7021,20 +7085,20 @@
       <c r="Y7" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z7" s="23" t="s">
-        <v>1517</v>
+      <c r="Z7" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA7" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB7" s="23" t="s">
-        <v>1517</v>
+      <c r="AB7" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC7" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="99">
         <v>8</v>
       </c>
@@ -7118,20 +7182,20 @@
       <c r="Y8" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z8" s="23" t="s">
-        <v>1517</v>
+      <c r="Z8" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA8" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB8" s="23" t="s">
-        <v>1517</v>
+      <c r="AB8" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC8" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="99">
         <v>9</v>
       </c>
@@ -7215,20 +7279,20 @@
       <c r="Y9" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z9" s="23" t="s">
-        <v>1517</v>
+      <c r="Z9" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA9" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB9" s="23" t="s">
-        <v>1517</v>
+      <c r="AB9" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC9" s="23" t="s">
         <v>1256</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="99">
         <v>10</v>
       </c>
@@ -7312,20 +7376,20 @@
       <c r="Y10" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z10" s="23" t="s">
-        <v>1517</v>
+      <c r="Z10" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA10" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB10" s="23" t="s">
-        <v>1517</v>
+      <c r="AB10" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC10" s="23" t="s">
         <v>1256</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="99">
         <v>11</v>
       </c>
@@ -7409,20 +7473,20 @@
       <c r="Y11" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z11" s="23" t="s">
-        <v>1517</v>
+      <c r="Z11" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA11" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB11" s="23" t="s">
-        <v>1517</v>
+      <c r="AB11" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC11" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="99">
         <v>12</v>
       </c>
@@ -7506,20 +7570,20 @@
       <c r="Y12" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z12" s="23" t="s">
-        <v>1517</v>
+      <c r="Z12" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA12" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB12" s="23" t="s">
-        <v>1517</v>
+      <c r="AB12" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC12" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="99">
         <v>13</v>
       </c>
@@ -7603,20 +7667,20 @@
       <c r="Y13" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z13" s="23" t="s">
-        <v>1517</v>
+      <c r="Z13" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA13" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB13" s="23" t="s">
-        <v>1517</v>
+      <c r="AB13" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC13" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="99">
         <v>14</v>
       </c>
@@ -7700,20 +7764,20 @@
       <c r="Y14" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z14" s="23" t="s">
-        <v>1517</v>
+      <c r="Z14" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA14" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB14" s="23" t="s">
-        <v>1517</v>
+      <c r="AB14" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC14" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="99">
         <v>15</v>
       </c>
@@ -7797,20 +7861,20 @@
       <c r="Y15" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z15" s="23" t="s">
-        <v>1517</v>
+      <c r="Z15" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA15" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB15" s="23" t="s">
-        <v>1517</v>
+      <c r="AB15" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC15" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="99">
         <v>16</v>
       </c>
@@ -7894,20 +7958,20 @@
       <c r="Y16" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z16" s="23" t="s">
-        <v>1517</v>
+      <c r="Z16" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA16" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB16" s="23" t="s">
-        <v>1517</v>
+      <c r="AB16" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC16" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="99">
         <v>17</v>
       </c>
@@ -7988,23 +8052,23 @@
         <f t="shared" si="14"/>
         <v>Key-PAISA-17</v>
       </c>
-      <c r="Y17" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="23" t="s">
-        <v>1517</v>
-      </c>
-      <c r="AA17" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="23" t="s">
-        <v>1517</v>
+      <c r="Y17" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC17" s="23" t="s">
         <v>1261</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="99">
         <v>18</v>
       </c>
@@ -8085,23 +8149,23 @@
         <f t="shared" si="14"/>
         <v>Key-PAISA-18</v>
       </c>
-      <c r="Y18" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="23" t="s">
-        <v>1517</v>
-      </c>
-      <c r="AA18" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="23" t="s">
-        <v>1517</v>
+      <c r="Y18" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC18" s="23" t="s">
         <v>1261</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="99">
         <v>19</v>
       </c>
@@ -8182,23 +8246,23 @@
         <f t="shared" si="14"/>
         <v>Key-PAISA-19</v>
       </c>
-      <c r="Y19" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="23" t="s">
-        <v>1517</v>
-      </c>
-      <c r="AA19" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="23" t="s">
-        <v>1517</v>
+      <c r="Y19" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC19" s="23" t="s">
         <v>1261</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="99">
         <v>20</v>
       </c>
@@ -8279,23 +8343,23 @@
         <f t="shared" si="14"/>
         <v>Key-PAISA-20</v>
       </c>
-      <c r="Y20" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="23" t="s">
-        <v>1517</v>
-      </c>
-      <c r="AA20" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="23" t="s">
-        <v>1517</v>
+      <c r="Y20" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC20" s="23" t="s">
         <v>1257</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="99">
         <v>21</v>
       </c>
@@ -8376,23 +8440,23 @@
         <f t="shared" si="14"/>
         <v>Key-PAISA-21</v>
       </c>
-      <c r="Y21" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="23" t="s">
-        <v>1517</v>
-      </c>
-      <c r="AA21" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB21" s="23" t="s">
-        <v>1517</v>
+      <c r="Y21" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC21" s="23" t="s">
         <v>1261</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="99">
         <v>22</v>
       </c>
@@ -8473,23 +8537,23 @@
         <f t="shared" si="14"/>
         <v>Key-PAISA-22</v>
       </c>
-      <c r="Y22" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="23" t="s">
-        <v>1517</v>
-      </c>
-      <c r="AA22" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB22" s="23" t="s">
-        <v>1517</v>
+      <c r="Y22" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC22" s="23" t="s">
         <v>1261</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="99">
         <v>23</v>
       </c>
@@ -8573,20 +8637,20 @@
       <c r="Y23" s="23" t="s">
         <v>1258</v>
       </c>
-      <c r="Z23" s="23" t="s">
-        <v>1517</v>
+      <c r="Z23" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA23" s="23" t="s">
         <v>1259</v>
       </c>
-      <c r="AB23" s="23" t="s">
-        <v>1517</v>
+      <c r="AB23" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC23" s="23" t="s">
         <v>1256</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="99">
         <v>24</v>
       </c>
@@ -8670,20 +8734,20 @@
       <c r="Y24" s="23" t="s">
         <v>1258</v>
       </c>
-      <c r="Z24" s="23" t="s">
-        <v>1517</v>
+      <c r="Z24" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA24" s="23" t="s">
         <v>1259</v>
       </c>
-      <c r="AB24" s="23" t="s">
-        <v>1517</v>
+      <c r="AB24" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC24" s="23" t="s">
         <v>1256</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="99">
         <v>25</v>
       </c>
@@ -8767,20 +8831,20 @@
       <c r="Y25" s="23" t="s">
         <v>1258</v>
       </c>
-      <c r="Z25" s="23" t="s">
-        <v>1517</v>
+      <c r="Z25" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA25" s="23" t="s">
         <v>1259</v>
       </c>
-      <c r="AB25" s="23" t="s">
-        <v>1517</v>
+      <c r="AB25" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC25" s="23" t="s">
         <v>1260</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="99">
         <v>26</v>
       </c>
@@ -8861,23 +8925,23 @@
         <f t="shared" si="14"/>
         <v>Key-PAISA-26</v>
       </c>
-      <c r="Y26" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z26" s="23" t="s">
-        <v>1517</v>
+      <c r="Y26" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA26" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="AB26" s="23" t="s">
-        <v>1517</v>
+      <c r="AB26" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC26" s="23" t="s">
         <v>1261</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="99">
         <v>27</v>
       </c>
@@ -8958,23 +9022,23 @@
         <f t="shared" si="14"/>
         <v>Key-PAISA-27</v>
       </c>
-      <c r="Y27" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="23" t="s">
-        <v>1517</v>
+      <c r="Y27" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA27" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="AB27" s="23" t="s">
-        <v>1517</v>
+      <c r="AB27" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC27" s="23" t="s">
         <v>1261</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="99">
         <v>28</v>
       </c>
@@ -9055,23 +9119,23 @@
         <f t="shared" si="14"/>
         <v>Key-PAISA-28</v>
       </c>
-      <c r="Y28" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="23" t="s">
-        <v>1517</v>
+      <c r="Y28" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA28" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="AB28" s="23" t="s">
-        <v>1517</v>
+      <c r="AB28" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC28" s="23" t="s">
         <v>1261</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="99">
         <v>29</v>
       </c>
@@ -9156,20 +9220,20 @@
       <c r="Y29" s="23" t="s">
         <v>1362</v>
       </c>
-      <c r="Z29" s="23" t="s">
-        <v>1517</v>
+      <c r="Z29" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA29" s="23" t="s">
         <v>1363</v>
       </c>
-      <c r="AB29" s="23" t="s">
-        <v>1517</v>
+      <c r="AB29" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC29" s="101" t="s">
         <v>1364</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="99">
         <v>30</v>
       </c>
@@ -9254,20 +9318,20 @@
       <c r="Y30" s="23" t="s">
         <v>1362</v>
       </c>
-      <c r="Z30" s="23" t="s">
-        <v>1517</v>
+      <c r="Z30" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA30" s="23" t="s">
         <v>1363</v>
       </c>
-      <c r="AB30" s="23" t="s">
-        <v>1517</v>
+      <c r="AB30" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC30" s="101" t="s">
         <v>1364</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="99">
         <v>31</v>
       </c>
@@ -9352,20 +9416,20 @@
       <c r="Y31" s="23" t="s">
         <v>1362</v>
       </c>
-      <c r="Z31" s="23" t="s">
-        <v>1517</v>
+      <c r="Z31" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA31" s="23" t="s">
         <v>1363</v>
       </c>
-      <c r="AB31" s="23" t="s">
-        <v>1517</v>
+      <c r="AB31" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC31" s="101" t="s">
         <v>1364</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="99">
         <v>32</v>
       </c>
@@ -9450,20 +9514,20 @@
       <c r="Y32" s="23" t="s">
         <v>1371</v>
       </c>
-      <c r="Z32" s="23" t="s">
-        <v>1517</v>
+      <c r="Z32" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA32" s="23" t="s">
         <v>1363</v>
       </c>
-      <c r="AB32" s="23" t="s">
-        <v>1517</v>
+      <c r="AB32" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC32" s="101" t="s">
         <v>1372</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="99">
         <v>33</v>
       </c>
@@ -9548,20 +9612,20 @@
       <c r="Y33" s="23" t="s">
         <v>1371</v>
       </c>
-      <c r="Z33" s="23" t="s">
-        <v>1517</v>
+      <c r="Z33" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA33" s="23" t="s">
         <v>1363</v>
       </c>
-      <c r="AB33" s="23" t="s">
-        <v>1517</v>
+      <c r="AB33" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC33" s="101" t="s">
         <v>1372</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="99">
         <v>34</v>
       </c>
@@ -9646,20 +9710,20 @@
       <c r="Y34" s="23" t="s">
         <v>1371</v>
       </c>
-      <c r="Z34" s="23" t="s">
-        <v>1517</v>
+      <c r="Z34" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA34" s="23" t="s">
         <v>1363</v>
       </c>
-      <c r="AB34" s="23" t="s">
-        <v>1517</v>
+      <c r="AB34" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC34" s="101" t="s">
         <v>1372</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="99">
         <v>35</v>
       </c>
@@ -9744,20 +9808,20 @@
       <c r="Y35" s="23" t="s">
         <v>1371</v>
       </c>
-      <c r="Z35" s="23" t="s">
-        <v>1517</v>
+      <c r="Z35" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA35" s="23" t="s">
         <v>1363</v>
       </c>
-      <c r="AB35" s="23" t="s">
-        <v>1517</v>
+      <c r="AB35" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC35" s="101" t="s">
         <v>1372</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="99">
         <v>36</v>
       </c>
@@ -9842,20 +9906,20 @@
       <c r="Y36" s="23" t="s">
         <v>1381</v>
       </c>
-      <c r="Z36" s="23" t="s">
-        <v>1517</v>
+      <c r="Z36" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA36" s="23" t="s">
         <v>1382</v>
       </c>
-      <c r="AB36" s="23" t="s">
-        <v>1517</v>
+      <c r="AB36" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC36" s="101" t="s">
         <v>1383</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="99">
         <v>37</v>
       </c>
@@ -9940,20 +10004,20 @@
       <c r="Y37" s="23" t="s">
         <v>1381</v>
       </c>
-      <c r="Z37" s="23" t="s">
-        <v>1517</v>
+      <c r="Z37" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA37" s="23" t="s">
         <v>1382</v>
       </c>
-      <c r="AB37" s="23" t="s">
-        <v>1517</v>
+      <c r="AB37" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC37" s="101" t="s">
         <v>1386</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="99">
         <v>38</v>
       </c>
@@ -10038,20 +10102,20 @@
       <c r="Y38" s="23" t="s">
         <v>1389</v>
       </c>
-      <c r="Z38" s="23" t="s">
-        <v>1517</v>
+      <c r="Z38" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA38" s="23" t="s">
         <v>1390</v>
       </c>
-      <c r="AB38" s="23" t="s">
-        <v>1517</v>
+      <c r="AB38" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC38" s="101" t="s">
         <v>1386</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="99">
         <v>39</v>
       </c>
@@ -10136,20 +10200,20 @@
       <c r="Y39" s="23" t="s">
         <v>1381</v>
       </c>
-      <c r="Z39" s="23" t="s">
-        <v>1517</v>
+      <c r="Z39" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA39" s="23" t="s">
         <v>1382</v>
       </c>
-      <c r="AB39" s="23" t="s">
-        <v>1517</v>
+      <c r="AB39" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC39" s="101" t="s">
         <v>1386</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="99">
         <v>40</v>
       </c>
@@ -10234,20 +10298,20 @@
       <c r="Y40" s="23" t="s">
         <v>1381</v>
       </c>
-      <c r="Z40" s="23" t="s">
-        <v>1517</v>
+      <c r="Z40" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA40" s="23" t="s">
         <v>1382</v>
       </c>
-      <c r="AB40" s="23" t="s">
-        <v>1517</v>
+      <c r="AB40" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC40" s="101" t="s">
         <v>1386</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="99">
         <v>41</v>
       </c>
@@ -10332,20 +10396,20 @@
       <c r="Y41" s="23" t="s">
         <v>1381</v>
       </c>
-      <c r="Z41" s="23" t="s">
-        <v>1517</v>
+      <c r="Z41" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA41" s="23" t="s">
         <v>1382</v>
       </c>
-      <c r="AB41" s="23" t="s">
-        <v>1517</v>
+      <c r="AB41" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC41" s="101" t="s">
         <v>1386</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="99">
         <v>42</v>
       </c>
@@ -10430,20 +10494,20 @@
       <c r="Y42" s="23" t="s">
         <v>1362</v>
       </c>
-      <c r="Z42" s="23" t="s">
-        <v>1517</v>
+      <c r="Z42" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA42" s="23" t="s">
         <v>1363</v>
       </c>
-      <c r="AB42" s="23" t="s">
-        <v>1517</v>
+      <c r="AB42" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC42" s="101" t="s">
         <v>1364</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="99">
         <v>43</v>
       </c>
@@ -10528,20 +10592,20 @@
       <c r="Y43" s="23" t="s">
         <v>1362</v>
       </c>
-      <c r="Z43" s="23" t="s">
-        <v>1517</v>
+      <c r="Z43" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA43" s="23" t="s">
         <v>1363</v>
       </c>
-      <c r="AB43" s="23" t="s">
-        <v>1517</v>
+      <c r="AB43" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC43" s="101" t="s">
         <v>1364</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="99">
         <v>44</v>
       </c>
@@ -10626,20 +10690,20 @@
       <c r="Y44" s="23" t="s">
         <v>1403</v>
       </c>
-      <c r="Z44" s="23" t="s">
-        <v>1517</v>
+      <c r="Z44" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA44" s="23" t="s">
         <v>1404</v>
       </c>
-      <c r="AB44" s="23" t="s">
-        <v>1517</v>
+      <c r="AB44" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC44" s="101" t="s">
         <v>1405</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="99">
         <v>45</v>
       </c>
@@ -10724,20 +10788,20 @@
       <c r="Y45" s="23" t="s">
         <v>1403</v>
       </c>
-      <c r="Z45" s="23" t="s">
-        <v>1517</v>
+      <c r="Z45" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA45" s="23" t="s">
         <v>1404</v>
       </c>
-      <c r="AB45" s="23" t="s">
-        <v>1517</v>
+      <c r="AB45" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC45" s="101" t="s">
         <v>1405</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="99">
         <v>46</v>
       </c>
@@ -10822,20 +10886,20 @@
       <c r="Y46" s="23" t="s">
         <v>1403</v>
       </c>
-      <c r="Z46" s="23" t="s">
-        <v>1517</v>
+      <c r="Z46" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA46" s="23" t="s">
         <v>1404</v>
       </c>
-      <c r="AB46" s="23" t="s">
-        <v>1517</v>
+      <c r="AB46" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC46" s="101" t="s">
         <v>1410</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="99">
         <v>47</v>
       </c>
@@ -10920,20 +10984,20 @@
       <c r="Y47" s="23" t="s">
         <v>1403</v>
       </c>
-      <c r="Z47" s="23" t="s">
-        <v>1517</v>
+      <c r="Z47" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA47" s="23" t="s">
         <v>1404</v>
       </c>
-      <c r="AB47" s="23" t="s">
-        <v>1517</v>
+      <c r="AB47" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC47" s="101" t="s">
         <v>1405</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="99">
         <v>48</v>
       </c>
@@ -11018,20 +11082,20 @@
       <c r="Y48" s="23" t="s">
         <v>1403</v>
       </c>
-      <c r="Z48" s="23" t="s">
-        <v>1517</v>
+      <c r="Z48" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA48" s="23" t="s">
         <v>1404</v>
       </c>
-      <c r="AB48" s="23" t="s">
-        <v>1517</v>
+      <c r="AB48" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC48" s="101" t="s">
         <v>1405</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="99">
         <v>49</v>
       </c>
@@ -11112,23 +11176,23 @@
         <f t="shared" si="14"/>
         <v>Key-PAISA-49</v>
       </c>
-      <c r="Y49" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z49" s="23" t="s">
-        <v>1517</v>
+      <c r="Y49" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z49" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA49" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB49" s="23" t="s">
-        <v>1517</v>
+      <c r="AB49" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC49" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="99">
         <v>50</v>
       </c>
@@ -11209,23 +11273,23 @@
         <f t="shared" si="14"/>
         <v>Key-PAISA-50</v>
       </c>
-      <c r="Y50" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="23" t="s">
-        <v>1517</v>
+      <c r="Y50" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA50" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB50" s="23" t="s">
-        <v>1517</v>
+      <c r="AB50" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC50" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="99">
         <v>51</v>
       </c>
@@ -11306,23 +11370,23 @@
         <f t="shared" si="14"/>
         <v>Key-PAISA-51</v>
       </c>
-      <c r="Y51" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="23" t="s">
-        <v>1517</v>
+      <c r="Y51" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA51" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB51" s="23" t="s">
-        <v>1517</v>
+      <c r="AB51" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC51" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="99">
         <v>52</v>
       </c>
@@ -11406,20 +11470,20 @@
       <c r="Y52" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z52" s="23" t="s">
-        <v>1517</v>
+      <c r="Z52" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA52" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB52" s="23" t="s">
-        <v>1517</v>
+      <c r="AB52" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC52" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="99">
         <v>53</v>
       </c>
@@ -11503,20 +11567,20 @@
       <c r="Y53" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z53" s="23" t="s">
-        <v>1517</v>
+      <c r="Z53" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA53" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB53" s="23" t="s">
-        <v>1517</v>
+      <c r="AB53" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC53" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="99">
         <v>54</v>
       </c>
@@ -11600,20 +11664,20 @@
       <c r="Y54" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z54" s="23" t="s">
-        <v>1517</v>
+      <c r="Z54" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA54" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB54" s="23" t="s">
-        <v>1517</v>
+      <c r="AB54" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC54" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="99">
         <v>55</v>
       </c>
@@ -11697,20 +11761,20 @@
       <c r="Y55" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z55" s="23" t="s">
-        <v>1517</v>
+      <c r="Z55" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA55" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB55" s="23" t="s">
-        <v>1517</v>
+      <c r="AB55" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC55" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="99">
         <v>56</v>
       </c>
@@ -11794,20 +11858,20 @@
       <c r="Y56" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z56" s="23" t="s">
-        <v>1517</v>
+      <c r="Z56" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA56" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB56" s="23" t="s">
-        <v>1517</v>
+      <c r="AB56" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC56" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="99">
         <v>57</v>
       </c>
@@ -11891,20 +11955,20 @@
       <c r="Y57" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z57" s="23" t="s">
-        <v>1517</v>
+      <c r="Z57" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA57" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB57" s="23" t="s">
-        <v>1517</v>
+      <c r="AB57" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC57" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="99">
         <v>58</v>
       </c>
@@ -11988,20 +12052,20 @@
       <c r="Y58" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z58" s="23" t="s">
-        <v>1517</v>
+      <c r="Z58" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA58" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB58" s="23" t="s">
-        <v>1517</v>
+      <c r="AB58" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC58" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="99">
         <v>59</v>
       </c>
@@ -12085,20 +12149,20 @@
       <c r="Y59" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z59" s="23" t="s">
-        <v>1517</v>
+      <c r="Z59" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA59" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB59" s="23" t="s">
-        <v>1517</v>
+      <c r="AB59" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC59" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="99">
         <v>60</v>
       </c>
@@ -12182,20 +12246,20 @@
       <c r="Y60" s="23" t="s">
         <v>1258</v>
       </c>
-      <c r="Z60" s="23" t="s">
-        <v>1517</v>
+      <c r="Z60" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA60" s="23" t="s">
         <v>1259</v>
       </c>
-      <c r="AB60" s="23" t="s">
-        <v>1517</v>
+      <c r="AB60" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC60" s="23" t="s">
         <v>1256</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="99">
         <v>61</v>
       </c>
@@ -12279,20 +12343,20 @@
       <c r="Y61" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z61" s="23" t="s">
-        <v>1517</v>
+      <c r="Z61" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA61" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB61" s="23" t="s">
-        <v>1517</v>
+      <c r="AB61" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC61" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="99">
         <v>62</v>
       </c>
@@ -12376,20 +12440,20 @@
       <c r="Y62" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="Z62" s="23" t="s">
-        <v>1517</v>
+      <c r="Z62" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA62" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB62" s="23" t="s">
-        <v>1517</v>
+      <c r="AB62" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC62" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="99">
         <v>63</v>
       </c>
@@ -12470,23 +12534,23 @@
         <f t="shared" si="14"/>
         <v>Key-PAISA-63</v>
       </c>
-      <c r="Y63" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z63" s="23" t="s">
-        <v>1517</v>
+      <c r="Y63" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z63" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA63" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB63" s="23" t="s">
-        <v>1517</v>
+      <c r="AB63" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC63" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="99">
         <v>64</v>
       </c>
@@ -12567,23 +12631,23 @@
         <f t="shared" si="14"/>
         <v>Key-PAISA-64</v>
       </c>
-      <c r="Y64" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z64" s="23" t="s">
-        <v>1517</v>
+      <c r="Y64" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z64" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA64" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB64" s="23" t="s">
-        <v>1517</v>
+      <c r="AB64" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC64" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="99">
         <v>65</v>
       </c>
@@ -12664,23 +12728,23 @@
         <f t="shared" si="14"/>
         <v>Key-PAISA-65</v>
       </c>
-      <c r="Y65" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z65" s="23" t="s">
-        <v>1517</v>
+      <c r="Y65" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z65" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA65" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB65" s="23" t="s">
-        <v>1517</v>
+      <c r="AB65" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC65" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="99">
         <v>66</v>
       </c>
@@ -12761,23 +12825,23 @@
         <f t="shared" si="14"/>
         <v>Key-PAISA-66</v>
       </c>
-      <c r="Y66" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z66" s="23" t="s">
-        <v>1517</v>
+      <c r="Y66" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z66" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA66" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB66" s="23" t="s">
-        <v>1517</v>
+      <c r="AB66" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC66" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="99">
         <v>67</v>
       </c>
@@ -12855,26 +12919,26 @@
         <v>1252</v>
       </c>
       <c r="X67" s="98" t="str">
-        <f t="shared" ref="X67:X80" si="114">CONCATENATE("Key-PAISA-",A67)</f>
+        <f t="shared" ref="X67:X84" si="114">CONCATENATE("Key-PAISA-",A67)</f>
         <v>Key-PAISA-67</v>
       </c>
-      <c r="Y67" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z67" s="23" t="s">
-        <v>1517</v>
+      <c r="Y67" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z67" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA67" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB67" s="23" t="s">
-        <v>1517</v>
+      <c r="AB67" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC67" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="99">
         <v>68</v>
       </c>
@@ -12955,23 +13019,23 @@
         <f t="shared" si="114"/>
         <v>Key-PAISA-68</v>
       </c>
-      <c r="Y68" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z68" s="23" t="s">
-        <v>1517</v>
+      <c r="Y68" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z68" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA68" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB68" s="23" t="s">
-        <v>1517</v>
+      <c r="AB68" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC68" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="99">
         <v>69</v>
       </c>
@@ -13052,23 +13116,23 @@
         <f t="shared" si="114"/>
         <v>Key-PAISA-69</v>
       </c>
-      <c r="Y69" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z69" s="23" t="s">
-        <v>1517</v>
+      <c r="Y69" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z69" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA69" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB69" s="23" t="s">
-        <v>1517</v>
+      <c r="AB69" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC69" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="99">
         <v>70</v>
       </c>
@@ -13149,23 +13213,23 @@
         <f t="shared" si="114"/>
         <v>Key-PAISA-70</v>
       </c>
-      <c r="Y70" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z70" s="23" t="s">
-        <v>1517</v>
+      <c r="Y70" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z70" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA70" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB70" s="23" t="s">
-        <v>1517</v>
+      <c r="AB70" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC70" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="99">
         <v>71</v>
       </c>
@@ -13246,23 +13310,23 @@
         <f t="shared" si="114"/>
         <v>Key-PAISA-71</v>
       </c>
-      <c r="Y71" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z71" s="23" t="s">
-        <v>1517</v>
+      <c r="Y71" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z71" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA71" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB71" s="23" t="s">
-        <v>1517</v>
+      <c r="AB71" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC71" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="99">
         <v>72</v>
       </c>
@@ -13346,20 +13410,20 @@
       <c r="Y72" s="23" t="s">
         <v>1258</v>
       </c>
-      <c r="Z72" s="23" t="s">
-        <v>1517</v>
+      <c r="Z72" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA72" s="23" t="s">
         <v>1259</v>
       </c>
-      <c r="AB72" s="23" t="s">
-        <v>1517</v>
+      <c r="AB72" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC72" s="23" t="s">
         <v>1256</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="99">
         <v>73</v>
       </c>
@@ -13443,20 +13507,20 @@
       <c r="Y73" s="23" t="s">
         <v>1320</v>
       </c>
-      <c r="Z73" s="23" t="s">
-        <v>1517</v>
+      <c r="Z73" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA73" s="23" t="s">
         <v>1321</v>
       </c>
-      <c r="AB73" s="23" t="s">
-        <v>1517</v>
+      <c r="AB73" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC73" s="23" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="99">
         <v>74</v>
       </c>
@@ -13540,20 +13604,20 @@
       <c r="Y74" s="23" t="s">
         <v>1320</v>
       </c>
-      <c r="Z74" s="23" t="s">
-        <v>1517</v>
+      <c r="Z74" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA74" s="23" t="s">
         <v>1321</v>
       </c>
-      <c r="AB74" s="23" t="s">
-        <v>1517</v>
+      <c r="AB74" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC74" s="23" t="s">
         <v>1256</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="99">
         <v>75</v>
       </c>
@@ -13637,20 +13701,20 @@
       <c r="Y75" s="23" t="s">
         <v>1319</v>
       </c>
-      <c r="Z75" s="23" t="s">
-        <v>1517</v>
+      <c r="Z75" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA75" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB75" s="23" t="s">
-        <v>1517</v>
+      <c r="AB75" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC75" s="23" t="s">
         <v>1256</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="99">
         <v>76</v>
       </c>
@@ -13734,20 +13798,20 @@
       <c r="Y76" s="23" t="s">
         <v>1319</v>
       </c>
-      <c r="Z76" s="23" t="s">
-        <v>1517</v>
+      <c r="Z76" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA76" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB76" s="23" t="s">
-        <v>1517</v>
+      <c r="AB76" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC76" s="23" t="s">
         <v>1256</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="99">
         <v>77</v>
       </c>
@@ -13810,7 +13874,7 @@
         <v>1</v>
       </c>
       <c r="T77" s="23" t="str">
-        <f t="shared" ref="T77:V80" si="147">SUBSTITUTE(C77, ".", " ")</f>
+        <f t="shared" ref="T77:V84" si="147">SUBSTITUTE(C77, ".", " ")</f>
         <v>De Paisagismo</v>
       </c>
       <c r="U77" s="23" t="str">
@@ -13831,20 +13895,20 @@
       <c r="Y77" s="23" t="s">
         <v>1319</v>
       </c>
-      <c r="Z77" s="23" t="s">
-        <v>1517</v>
+      <c r="Z77" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA77" s="23" t="s">
         <v>1254</v>
       </c>
-      <c r="AB77" s="23" t="s">
-        <v>1517</v>
+      <c r="AB77" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC77" s="23" t="s">
         <v>1256</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="99">
         <v>78</v>
       </c>
@@ -13928,36 +13992,36 @@
       <c r="Y78" s="23" t="s">
         <v>1313</v>
       </c>
-      <c r="Z78" s="23" t="s">
-        <v>1517</v>
+      <c r="Z78" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA78" s="101" t="s">
         <v>1314</v>
       </c>
-      <c r="AB78" s="23" t="s">
-        <v>1517</v>
+      <c r="AB78" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC78" s="23" t="s">
         <v>1315</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="99">
         <v>79</v>
       </c>
-      <c r="B79" s="112" t="s">
+      <c r="B79" s="107" t="s">
         <v>74</v>
       </c>
-      <c r="C79" s="113" t="s">
+      <c r="C79" s="52" t="s">
         <v>1422</v>
       </c>
-      <c r="D79" s="113" t="s">
+      <c r="D79" s="52" t="s">
         <v>1434</v>
       </c>
-      <c r="E79" s="113" t="s">
+      <c r="E79" s="52" t="s">
         <v>1428</v>
       </c>
-      <c r="F79" s="113" t="s">
+      <c r="F79" s="52" t="s">
         <v>1415</v>
       </c>
       <c r="G79" s="96" t="s">
@@ -14025,38 +14089,38 @@
       <c r="Y79" s="101" t="s">
         <v>1316</v>
       </c>
-      <c r="Z79" s="23" t="s">
-        <v>1517</v>
+      <c r="Z79" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AA79" s="101" t="s">
         <v>1317</v>
       </c>
-      <c r="AB79" s="23" t="s">
-        <v>1517</v>
+      <c r="AB79" s="110" t="s">
+        <v>1</v>
       </c>
       <c r="AC79" s="23" t="s">
         <v>1318</v>
       </c>
     </row>
-    <row r="80" spans="1:29" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="99">
         <v>80</v>
       </c>
-      <c r="B80" s="112" t="s">
+      <c r="B80" s="107" t="s">
         <v>74</v>
       </c>
-      <c r="C80" s="113" t="s">
+      <c r="C80" s="52" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D80" s="52" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E80" s="52" t="s">
         <v>1521</v>
       </c>
-      <c r="D80" s="113" t="s">
+      <c r="F80" s="52" t="s">
         <v>1523</v>
       </c>
-      <c r="E80" s="113" t="s">
-        <v>1522</v>
-      </c>
-      <c r="F80" s="113" t="s">
-        <v>1524</v>
-      </c>
       <c r="G80" s="96" t="s">
         <v>1</v>
       </c>
@@ -14073,7 +14137,7 @@
         <v>1</v>
       </c>
       <c r="L80" s="108" t="str">
-        <f t="shared" ref="L80:O80" si="150">SUBSTITUTE(CONCATENATE("", C80), ".", " ")</f>
+        <f t="shared" ref="L80:O84" si="150">SUBSTITUTE(CONCATENATE("", C80), ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="M80" s="108" t="str">
@@ -14086,16 +14150,16 @@
       </c>
       <c r="O80" s="108" t="str">
         <f t="shared" si="150"/>
-        <v>API Revit</v>
+        <v>Função Auxiliar</v>
       </c>
       <c r="P80" s="23" t="s">
+        <v>1524</v>
+      </c>
+      <c r="Q80" s="23" t="s">
         <v>1525</v>
       </c>
-      <c r="Q80" s="23" t="s">
+      <c r="R80" s="23" t="s">
         <v>1526</v>
-      </c>
-      <c r="R80" s="23" t="s">
-        <v>1527</v>
       </c>
       <c r="S80" s="23" t="s">
         <v>1</v>
@@ -14135,88 +14199,469 @@
         <v>1</v>
       </c>
     </row>
+    <row r="81" spans="1:29" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="99">
+        <v>81</v>
+      </c>
+      <c r="B81" s="107" t="s">
+        <v>74</v>
+      </c>
+      <c r="C81" s="52" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D81" s="52" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E81" s="52" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F81" s="52" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G81" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="H81" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="I81" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="J81" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="K81" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="L81" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>De API</v>
+      </c>
+      <c r="M81" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>Macros</v>
+      </c>
+      <c r="N81" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O81" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P81" s="23" t="s">
+        <v>1528</v>
+      </c>
+      <c r="Q81" s="23" t="s">
+        <v>1529</v>
+      </c>
+      <c r="R81" s="23" t="s">
+        <v>1530</v>
+      </c>
+      <c r="S81" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T81" s="23" t="str">
+        <f t="shared" si="147"/>
+        <v>De API</v>
+      </c>
+      <c r="U81" s="23" t="str">
+        <f t="shared" si="147"/>
+        <v>Macros</v>
+      </c>
+      <c r="V81" s="109" t="str">
+        <f t="shared" si="147"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W81" s="23" t="s">
+        <v>1252</v>
+      </c>
+      <c r="X81" s="98" t="str">
+        <f t="shared" si="114"/>
+        <v>Key-PAISA-81</v>
+      </c>
+      <c r="Y81" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z81" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA81" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB81" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC81" s="110" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:29" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="99">
+        <v>82</v>
+      </c>
+      <c r="B82" s="107" t="s">
+        <v>74</v>
+      </c>
+      <c r="C82" s="52" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D82" s="52" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E82" s="52" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F82" s="52" t="s">
+        <v>1531</v>
+      </c>
+      <c r="G82" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="H82" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="I82" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="J82" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="K82" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="L82" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>De API</v>
+      </c>
+      <c r="M82" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>Macros</v>
+      </c>
+      <c r="N82" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O82" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P82" s="23" t="s">
+        <v>1532</v>
+      </c>
+      <c r="Q82" s="23" t="s">
+        <v>1533</v>
+      </c>
+      <c r="R82" s="23" t="s">
+        <v>1534</v>
+      </c>
+      <c r="S82" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T82" s="23" t="str">
+        <f t="shared" si="147"/>
+        <v>De API</v>
+      </c>
+      <c r="U82" s="23" t="str">
+        <f t="shared" si="147"/>
+        <v>Macros</v>
+      </c>
+      <c r="V82" s="109" t="str">
+        <f t="shared" si="147"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W82" s="23" t="s">
+        <v>1252</v>
+      </c>
+      <c r="X82" s="98" t="str">
+        <f t="shared" si="114"/>
+        <v>Key-PAISA-82</v>
+      </c>
+      <c r="Y82" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z82" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA82" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB82" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC82" s="110" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:29" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="99">
+        <v>83</v>
+      </c>
+      <c r="B83" s="107" t="s">
+        <v>74</v>
+      </c>
+      <c r="C83" s="52" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D83" s="52" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E83" s="52" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F83" s="52" t="s">
+        <v>1535</v>
+      </c>
+      <c r="G83" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="H83" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="I83" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="J83" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="K83" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="L83" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>De API</v>
+      </c>
+      <c r="M83" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>Macros</v>
+      </c>
+      <c r="N83" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O83" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P83" s="23" t="s">
+        <v>1536</v>
+      </c>
+      <c r="Q83" s="23" t="s">
+        <v>1537</v>
+      </c>
+      <c r="R83" s="23" t="s">
+        <v>1538</v>
+      </c>
+      <c r="S83" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T83" s="23" t="str">
+        <f t="shared" si="147"/>
+        <v>De API</v>
+      </c>
+      <c r="U83" s="23" t="str">
+        <f t="shared" si="147"/>
+        <v>Macros</v>
+      </c>
+      <c r="V83" s="109" t="str">
+        <f t="shared" si="147"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W83" s="23" t="s">
+        <v>1252</v>
+      </c>
+      <c r="X83" s="98" t="str">
+        <f t="shared" si="114"/>
+        <v>Key-PAISA-83</v>
+      </c>
+      <c r="Y83" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z83" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA83" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB83" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC83" s="110" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:29" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="99">
+        <v>84</v>
+      </c>
+      <c r="B84" s="107" t="s">
+        <v>74</v>
+      </c>
+      <c r="C84" s="52" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D84" s="52" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E84" s="52" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F84" s="52" t="s">
+        <v>1540</v>
+      </c>
+      <c r="G84" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="H84" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="I84" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="J84" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="K84" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="L84" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>De API</v>
+      </c>
+      <c r="M84" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>Macros</v>
+      </c>
+      <c r="N84" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O84" s="108" t="str">
+        <f t="shared" si="150"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P84" s="23" t="s">
+        <v>1541</v>
+      </c>
+      <c r="Q84" s="23" t="s">
+        <v>1542</v>
+      </c>
+      <c r="R84" s="23" t="s">
+        <v>1543</v>
+      </c>
+      <c r="S84" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T84" s="23" t="str">
+        <f t="shared" si="147"/>
+        <v>De API</v>
+      </c>
+      <c r="U84" s="23" t="str">
+        <f t="shared" si="147"/>
+        <v>Macros</v>
+      </c>
+      <c r="V84" s="109" t="str">
+        <f t="shared" si="147"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W84" s="23" t="s">
+        <v>1252</v>
+      </c>
+      <c r="X84" s="98" t="str">
+        <f t="shared" si="114"/>
+        <v>Key-PAISA-84</v>
+      </c>
+      <c r="Y84" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z84" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA84" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB84" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC84" s="110" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B2 B3:B48 A3:A80">
-    <cfRule type="cellIs" dxfId="22" priority="29" operator="equal">
+  <conditionalFormatting sqref="A2:B2 B3:B48 A3:A84">
+    <cfRule type="cellIs" dxfId="0" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:C1 S1:X1 L1:Q28 L49:Q71 B49:B79 L72:P79 AA75:AA77 A81:C1048576 L81:X1048576">
-    <cfRule type="cellIs" dxfId="21" priority="440" operator="equal">
+  <conditionalFormatting sqref="A1:C1 S1:X1 L1:Q28 L49:Q71 B49:B79 L72:P79 AA75:AA77 A85:C1048576 L85:X1048576">
+    <cfRule type="cellIs" dxfId="25" priority="443" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B80">
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
+  <conditionalFormatting sqref="F1:F79 F85:F1048576">
+    <cfRule type="duplicateValues" dxfId="23" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q72:Q79">
+    <cfRule type="cellIs" dxfId="21" priority="33" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F79 F81:F1048576">
-    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F80">
-    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q72:Q79">
-    <cfRule type="cellIs" dxfId="17" priority="30" operator="equal">
+  <conditionalFormatting sqref="R1:R79">
+    <cfRule type="cellIs" dxfId="20" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R80">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y17:Y22">
-    <cfRule type="cellIs" dxfId="15" priority="65" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y49:Y51 AA49:AA72 AC49:AC77">
-    <cfRule type="cellIs" dxfId="14" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y63:Y71">
-    <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
+  <conditionalFormatting sqref="AA49:AA72 AC49:AC77">
+    <cfRule type="cellIs" dxfId="18" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y73:Y74 AA73:AA74">
-    <cfRule type="cellIs" dxfId="12" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="34" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y78">
-    <cfRule type="containsText" dxfId="11" priority="32" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="15" priority="35" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",Y78)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z1:Z79">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+  <conditionalFormatting sqref="Z1">
+    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z81:XFD1048576">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
+  <conditionalFormatting sqref="Z85:XFD1048576">
+    <cfRule type="cellIs" dxfId="13" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA28 AC1:AC28 Y26:Y28">
-    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
+  <conditionalFormatting sqref="AA1:AA16 AC1:AC28 AA23:AA28">
+    <cfRule type="cellIs" dxfId="12" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB1:AB79">
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+  <conditionalFormatting sqref="AB1">
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1:XFD79 T2:V79 D29:D48 L29:P48">
-    <cfRule type="cellIs" dxfId="6" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="23" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B80:B84">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E84:F84">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F80:F83">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -14226,15 +14671,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.3046875" style="1" customWidth="1"/>
-    <col min="2" max="10" width="5.15234375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="5.53515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="5"/>
+    <col min="1" max="1" width="2.28515625" style="1" customWidth="1"/>
+    <col min="2" max="10" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="20" t="s">
         <v>22</v>
       </c>
@@ -14299,7 +14744,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -14367,7 +14812,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14380,14 +14825,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="3.3828125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.42578125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="6.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.15234375" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18">
         <v>1</v>
       </c>
@@ -14401,7 +14846,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="12">
         <v>2</v>
       </c>
@@ -14415,7 +14860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="12">
         <v>3</v>
       </c>
@@ -14429,7 +14874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12">
         <v>4</v>
       </c>
@@ -14443,13 +14888,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
     </row>
-    <row r="6" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6"/>
@@ -14457,7 +14902,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4">
-    <cfRule type="cellIs" dxfId="4" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14469,65 +14914,65 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC9BE003-A289-428E-9141-72F001D0AED0}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:BA299"/>
-  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" style="89" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.84375" style="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.3828125" style="89" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.3046875" style="89" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.15234375" style="89" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.69140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.84375" style="89" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.84375" style="89" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.53515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" style="89" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" style="89" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="89" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" style="89" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" style="89" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" style="89" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.3046875" style="89" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.28515625" style="89" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" style="89" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" style="89" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="89" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="90.53515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.84375" style="89" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.3046875" style="89" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="90.5703125" style="89" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.85546875" style="89" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.28515625" style="89" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8" style="89" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.15234375" style="89" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.140625" style="89" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="11" style="89" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.69140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.15234375" style="89" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.69140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.3046875" style="89" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.84375" style="89" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.69140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.69140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.84375" style="89" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.69140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.84375" style="89" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.53515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.69140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.53515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.3046875" style="89" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.69140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.3046875" style="89" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.15234375" style="89" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.53515625" style="89" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="39.3046875" style="89" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.7109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.7109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.85546875" style="89" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.7109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.7109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.85546875" style="89" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.7109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.85546875" style="89" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.5703125" style="89" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.7109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.5703125" style="89" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.28515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7.7109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.28515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.5703125" style="89" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="39.28515625" style="89" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="6" style="89" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="255.69140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="9.15234375" style="89" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="219.84375" style="89" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="4.3046875" style="89" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="26.15234375" style="89" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="255.7109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="9.140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="219.85546875" style="89" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="4.28515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="26.140625" style="89" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="10" style="89" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="4.69140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="8.3828125" style="89" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.69140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="5.69140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="4.7109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.42578125" style="89" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.7109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="5.7109375" style="89" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="15" style="89" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="7.3046875" style="89" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="17.3046875" style="89" bestFit="1" customWidth="1"/>
-    <col min="54" max="16384" width="9.3046875" style="89"/>
+    <col min="52" max="52" width="7.28515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="17.28515625" style="89" bestFit="1" customWidth="1"/>
+    <col min="54" max="16384" width="9.28515625" style="89"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:53" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22">
         <v>1</v>
       </c>
@@ -14686,7 +15131,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="2" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30">
         <v>2</v>
       </c>
@@ -14847,7 +15292,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="3" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="30">
         <v>3</v>
       </c>
@@ -15008,7 +15453,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="4" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="30">
         <v>4</v>
       </c>
@@ -15169,7 +15614,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="5" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="30">
         <v>5</v>
       </c>
@@ -15330,7 +15775,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="6" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="30">
         <v>6</v>
       </c>
@@ -15491,7 +15936,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="7" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="30">
         <v>7</v>
       </c>
@@ -15652,7 +16097,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="8" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="30">
         <v>8</v>
       </c>
@@ -15813,7 +16258,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="9" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="30">
         <v>9</v>
       </c>
@@ -15974,7 +16419,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="10" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="30">
         <v>10</v>
       </c>
@@ -16135,7 +16580,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="11" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="30">
         <v>11</v>
       </c>
@@ -16296,7 +16741,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="12" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="30">
         <v>12</v>
       </c>
@@ -16457,7 +16902,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="13" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="30">
         <v>13</v>
       </c>
@@ -16618,7 +17063,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="14" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="30">
         <v>14</v>
       </c>
@@ -16779,7 +17224,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="15" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>15</v>
       </c>
@@ -16940,7 +17385,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="16" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="30">
         <v>16</v>
       </c>
@@ -17101,7 +17546,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="17" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="30">
         <v>17</v>
       </c>
@@ -17262,7 +17707,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="18" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="30">
         <v>18</v>
       </c>
@@ -17423,7 +17868,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="19" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="30">
         <v>19</v>
       </c>
@@ -17584,7 +18029,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="20" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="30">
         <v>20</v>
       </c>
@@ -17745,7 +18190,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="21" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="30">
         <v>21</v>
       </c>
@@ -17906,7 +18351,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="22" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="30">
         <v>22</v>
       </c>
@@ -18067,7 +18512,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="23" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="30">
         <v>23</v>
       </c>
@@ -18228,7 +18673,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="24" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="30">
         <v>24</v>
       </c>
@@ -18389,7 +18834,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="25" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="30">
         <v>25</v>
       </c>
@@ -18550,7 +18995,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="26" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="30">
         <v>26</v>
       </c>
@@ -18711,7 +19156,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="27" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="30">
         <v>27</v>
       </c>
@@ -18872,7 +19317,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="28" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="30">
         <v>28</v>
       </c>
@@ -19033,7 +19478,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="29" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="30">
         <v>29</v>
       </c>
@@ -19194,7 +19639,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="30" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="30">
         <v>30</v>
       </c>
@@ -19355,7 +19800,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="31" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="30">
         <v>31</v>
       </c>
@@ -19516,7 +19961,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="32" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="30">
         <v>32</v>
       </c>
@@ -19677,7 +20122,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="33" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="30">
         <v>33</v>
       </c>
@@ -19838,7 +20283,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="34" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="30">
         <v>34</v>
       </c>
@@ -19999,7 +20444,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="35" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="30">
         <v>35</v>
       </c>
@@ -20160,7 +20605,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="36" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="30">
         <v>36</v>
       </c>
@@ -20321,7 +20766,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="37" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="30">
         <v>37</v>
       </c>
@@ -20482,7 +20927,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="38" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="30">
         <v>38</v>
       </c>
@@ -20643,7 +21088,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="39" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="30">
         <v>39</v>
       </c>
@@ -20804,7 +21249,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="40" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="30">
         <v>40</v>
       </c>
@@ -20965,7 +21410,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="41" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="30">
         <v>41</v>
       </c>
@@ -21126,7 +21571,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="42" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="30">
         <v>42</v>
       </c>
@@ -21287,7 +21732,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="43" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="30">
         <v>43</v>
       </c>
@@ -21448,7 +21893,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="44" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="30">
         <v>44</v>
       </c>
@@ -21609,7 +22054,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="45" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="30">
         <v>45</v>
       </c>
@@ -21770,7 +22215,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="46" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="30">
         <v>46</v>
       </c>
@@ -21931,7 +22376,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="47" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="30">
         <v>47</v>
       </c>
@@ -22092,7 +22537,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="48" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="30">
         <v>48</v>
       </c>
@@ -22253,7 +22698,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="49" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="30">
         <v>49</v>
       </c>
@@ -22414,7 +22859,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="50" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="30">
         <v>50</v>
       </c>
@@ -22575,7 +23020,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="51" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="30">
         <v>51</v>
       </c>
@@ -22736,7 +23181,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="52" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="30">
         <v>52</v>
       </c>
@@ -22897,7 +23342,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="53" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="30">
         <v>53</v>
       </c>
@@ -23058,7 +23503,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="54" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30">
         <v>54</v>
       </c>
@@ -23219,7 +23664,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="55" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="30">
         <v>55</v>
       </c>
@@ -23380,7 +23825,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="56" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="30">
         <v>56</v>
       </c>
@@ -23541,7 +23986,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="57" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="30">
         <v>57</v>
       </c>
@@ -23702,7 +24147,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="58" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="30">
         <v>58</v>
       </c>
@@ -23863,7 +24308,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="59" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="30">
         <v>59</v>
       </c>
@@ -24024,7 +24469,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="60" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="30">
         <v>60</v>
       </c>
@@ -24185,7 +24630,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="61" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="30">
         <v>61</v>
       </c>
@@ -24346,7 +24791,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="62" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="30">
         <v>62</v>
       </c>
@@ -24507,7 +24952,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="63" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="30">
         <v>63</v>
       </c>
@@ -24668,7 +25113,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="64" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="30">
         <v>64</v>
       </c>
@@ -24829,7 +25274,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="65" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="30">
         <v>65</v>
       </c>
@@ -24990,7 +25435,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="66" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="30">
         <v>66</v>
       </c>
@@ -25151,7 +25596,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="67" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="30">
         <v>67</v>
       </c>
@@ -25312,7 +25757,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="68" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="30">
         <v>68</v>
       </c>
@@ -25473,7 +25918,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="69" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="30">
         <v>69</v>
       </c>
@@ -25634,7 +26079,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="70" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="30">
         <v>70</v>
       </c>
@@ -25795,7 +26240,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="71" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="30">
         <v>71</v>
       </c>
@@ -25956,7 +26401,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="72" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="30">
         <v>72</v>
       </c>
@@ -26117,7 +26562,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="73" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="30">
         <v>73</v>
       </c>
@@ -26278,7 +26723,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="74" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="30">
         <v>74</v>
       </c>
@@ -26439,7 +26884,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="75" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="30">
         <v>75</v>
       </c>
@@ -26600,7 +27045,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="76" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="30">
         <v>76</v>
       </c>
@@ -26761,7 +27206,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="77" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="30">
         <v>77</v>
       </c>
@@ -26922,7 +27367,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="78" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="30">
         <v>78</v>
       </c>
@@ -27083,7 +27528,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="79" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="30">
         <v>79</v>
       </c>
@@ -27244,7 +27689,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="80" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="30">
         <v>80</v>
       </c>
@@ -27405,7 +27850,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="81" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="30">
         <v>81</v>
       </c>
@@ -27566,7 +28011,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="82" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="30">
         <v>82</v>
       </c>
@@ -27727,7 +28172,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="83" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="30">
         <v>83</v>
       </c>
@@ -27888,7 +28333,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="84" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="30">
         <v>84</v>
       </c>
@@ -28049,7 +28494,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="85" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="30">
         <v>85</v>
       </c>
@@ -28210,7 +28655,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="86" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="30">
         <v>86</v>
       </c>
@@ -28371,7 +28816,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="87" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="30">
         <v>87</v>
       </c>
@@ -28532,7 +28977,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="88" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="30">
         <v>88</v>
       </c>
@@ -28693,7 +29138,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="89" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="30">
         <v>89</v>
       </c>
@@ -28854,7 +29299,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="90" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="30">
         <v>90</v>
       </c>
@@ -29015,7 +29460,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="91" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="30">
         <v>91</v>
       </c>
@@ -29176,7 +29621,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="92" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="30">
         <v>92</v>
       </c>
@@ -29337,7 +29782,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="93" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="30">
         <v>93</v>
       </c>
@@ -29498,7 +29943,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="94" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="30">
         <v>94</v>
       </c>
@@ -29659,7 +30104,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="95" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="30">
         <v>95</v>
       </c>
@@ -29820,7 +30265,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="96" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="30">
         <v>96</v>
       </c>
@@ -29981,7 +30426,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="97" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="30">
         <v>97</v>
       </c>
@@ -30142,7 +30587,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="98" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="30">
         <v>98</v>
       </c>
@@ -30303,7 +30748,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="99" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="30">
         <v>99</v>
       </c>
@@ -30464,7 +30909,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="100" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="30">
         <v>100</v>
       </c>
@@ -30625,7 +31070,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="101" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="30">
         <v>101</v>
       </c>
@@ -30786,7 +31231,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="102" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="30">
         <v>102</v>
       </c>
@@ -30947,7 +31392,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="103" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="30">
         <v>103</v>
       </c>
@@ -31108,7 +31553,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="104" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="30">
         <v>104</v>
       </c>
@@ -31269,7 +31714,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="105" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="30">
         <v>105</v>
       </c>
@@ -31430,7 +31875,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="106" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="30">
         <v>106</v>
       </c>
@@ -31591,7 +32036,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="107" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="30">
         <v>107</v>
       </c>
@@ -31752,7 +32197,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="108" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="30">
         <v>108</v>
       </c>
@@ -31913,7 +32358,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="109" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="30">
         <v>109</v>
       </c>
@@ -32074,7 +32519,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="110" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="30">
         <v>110</v>
       </c>
@@ -32235,7 +32680,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="111" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="30">
         <v>111</v>
       </c>
@@ -32396,7 +32841,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="112" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="30">
         <v>112</v>
       </c>
@@ -32557,7 +33002,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="113" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="30">
         <v>113</v>
       </c>
@@ -32718,7 +33163,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="114" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="30">
         <v>114</v>
       </c>
@@ -32879,7 +33324,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="115" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="30">
         <v>115</v>
       </c>
@@ -33040,7 +33485,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="116" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="30">
         <v>116</v>
       </c>
@@ -33201,7 +33646,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="117" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="30">
         <v>117</v>
       </c>
@@ -33362,7 +33807,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="118" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="30">
         <v>118</v>
       </c>
@@ -33523,7 +33968,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="119" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="30">
         <v>119</v>
       </c>
@@ -33684,7 +34129,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="120" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="30">
         <v>120</v>
       </c>
@@ -33845,7 +34290,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="121" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="30">
         <v>121</v>
       </c>
@@ -34006,7 +34451,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="122" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="30">
         <v>122</v>
       </c>
@@ -34167,7 +34612,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="123" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="30">
         <v>123</v>
       </c>
@@ -34328,7 +34773,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="124" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="30">
         <v>124</v>
       </c>
@@ -34489,7 +34934,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="125" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="30">
         <v>125</v>
       </c>
@@ -34650,7 +35095,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="126" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="30">
         <v>126</v>
       </c>
@@ -34811,7 +35256,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="127" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="30">
         <v>127</v>
       </c>
@@ -34972,7 +35417,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="128" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="30">
         <v>128</v>
       </c>
@@ -35133,7 +35578,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="129" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="30">
         <v>129</v>
       </c>
@@ -35294,7 +35739,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="130" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="30">
         <v>130</v>
       </c>
@@ -35455,7 +35900,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="131" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="30">
         <v>131</v>
       </c>
@@ -35616,7 +36061,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="132" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="30">
         <v>132</v>
       </c>
@@ -35777,7 +36222,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="133" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="30">
         <v>133</v>
       </c>
@@ -35938,7 +36383,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="134" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="30">
         <v>134</v>
       </c>
@@ -36099,7 +36544,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="135" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="30">
         <v>135</v>
       </c>
@@ -36260,7 +36705,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="136" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="30">
         <v>136</v>
       </c>
@@ -36421,7 +36866,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="137" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="30">
         <v>137</v>
       </c>
@@ -36582,7 +37027,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="138" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="30">
         <v>138</v>
       </c>
@@ -36743,7 +37188,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="139" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="30">
         <v>139</v>
       </c>
@@ -36904,7 +37349,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="140" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="30">
         <v>140</v>
       </c>
@@ -37065,7 +37510,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="141" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="30">
         <v>141</v>
       </c>
@@ -37226,7 +37671,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="142" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="30">
         <v>142</v>
       </c>
@@ -37387,7 +37832,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="143" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="30">
         <v>143</v>
       </c>
@@ -37548,7 +37993,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="144" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="30">
         <v>144</v>
       </c>
@@ -37709,7 +38154,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="145" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="30">
         <v>145</v>
       </c>
@@ -37870,7 +38315,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="146" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="30">
         <v>146</v>
       </c>
@@ -38031,7 +38476,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="147" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="30">
         <v>147</v>
       </c>
@@ -38192,7 +38637,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="148" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="30">
         <v>148</v>
       </c>
@@ -38353,7 +38798,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="149" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="30">
         <v>149</v>
       </c>
@@ -38514,7 +38959,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="150" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="30">
         <v>150</v>
       </c>
@@ -38675,7 +39120,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="151" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="30">
         <v>151</v>
       </c>
@@ -38836,7 +39281,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="152" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="30">
         <v>152</v>
       </c>
@@ -38997,7 +39442,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="153" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="30">
         <v>153</v>
       </c>
@@ -39158,7 +39603,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="154" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="30">
         <v>154</v>
       </c>
@@ -39319,7 +39764,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="155" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="30">
         <v>155</v>
       </c>
@@ -39480,7 +39925,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="156" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="30">
         <v>156</v>
       </c>
@@ -39641,7 +40086,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="157" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="30">
         <v>157</v>
       </c>
@@ -39802,7 +40247,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="158" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="30">
         <v>158</v>
       </c>
@@ -39963,7 +40408,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="159" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="30">
         <v>159</v>
       </c>
@@ -40124,7 +40569,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="160" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="30">
         <v>160</v>
       </c>
@@ -40285,7 +40730,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="161" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="30">
         <v>161</v>
       </c>
@@ -40446,7 +40891,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="162" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="30">
         <v>162</v>
       </c>
@@ -40607,7 +41052,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="163" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="30">
         <v>163</v>
       </c>
@@ -40768,7 +41213,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="164" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="30">
         <v>164</v>
       </c>
@@ -40929,7 +41374,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="165" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="30">
         <v>165</v>
       </c>
@@ -41090,7 +41535,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="166" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="30">
         <v>166</v>
       </c>
@@ -41251,7 +41696,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="167" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="30">
         <v>167</v>
       </c>
@@ -41412,7 +41857,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="168" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="30">
         <v>168</v>
       </c>
@@ -41573,7 +42018,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="169" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="30">
         <v>169</v>
       </c>
@@ -41734,7 +42179,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="170" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="30">
         <v>170</v>
       </c>
@@ -41895,7 +42340,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="171" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="30">
         <v>171</v>
       </c>
@@ -42056,7 +42501,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="172" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="30">
         <v>172</v>
       </c>
@@ -42217,7 +42662,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="173" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="30">
         <v>173</v>
       </c>
@@ -42378,7 +42823,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="174" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="30">
         <v>174</v>
       </c>
@@ -42539,7 +42984,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="175" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="30">
         <v>175</v>
       </c>
@@ -42700,7 +43145,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="176" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="30">
         <v>176</v>
       </c>
@@ -42861,7 +43306,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="177" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="30">
         <v>177</v>
       </c>
@@ -43022,7 +43467,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="178" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="30">
         <v>178</v>
       </c>
@@ -43183,7 +43628,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="179" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="30">
         <v>179</v>
       </c>
@@ -43344,7 +43789,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="180" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="30">
         <v>180</v>
       </c>
@@ -43505,7 +43950,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="181" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="30">
         <v>181</v>
       </c>
@@ -43666,7 +44111,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="182" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="30">
         <v>182</v>
       </c>
@@ -43827,7 +44272,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="183" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="30">
         <v>183</v>
       </c>
@@ -43988,7 +44433,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="184" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="30">
         <v>184</v>
       </c>
@@ -44149,7 +44594,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="185" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="30">
         <v>185</v>
       </c>
@@ -44310,7 +44755,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="186" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="30">
         <v>186</v>
       </c>
@@ -44471,7 +44916,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="187" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="30">
         <v>187</v>
       </c>
@@ -44632,7 +45077,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="188" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="30">
         <v>188</v>
       </c>
@@ -44793,7 +45238,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="189" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="30">
         <v>189</v>
       </c>
@@ -44954,7 +45399,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="190" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="30">
         <v>190</v>
       </c>
@@ -45115,7 +45560,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="191" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="30">
         <v>191</v>
       </c>
@@ -45276,7 +45721,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="192" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="30">
         <v>192</v>
       </c>
@@ -45437,7 +45882,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="193" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="30">
         <v>193</v>
       </c>
@@ -45598,7 +46043,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="194" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="30">
         <v>194</v>
       </c>
@@ -45759,7 +46204,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="195" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="30">
         <v>195</v>
       </c>
@@ -45920,7 +46365,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="196" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="30">
         <v>196</v>
       </c>
@@ -46081,7 +46526,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="197" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="30">
         <v>197</v>
       </c>
@@ -46242,7 +46687,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="198" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="30">
         <v>198</v>
       </c>
@@ -46403,7 +46848,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="199" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="30">
         <v>199</v>
       </c>
@@ -46564,7 +47009,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="200" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="30">
         <v>200</v>
       </c>
@@ -46725,7 +47170,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="201" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="30">
         <v>201</v>
       </c>
@@ -46886,7 +47331,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="202" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="30">
         <v>202</v>
       </c>
@@ -47047,7 +47492,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="203" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="30">
         <v>203</v>
       </c>
@@ -47208,7 +47653,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="204" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="30">
         <v>204</v>
       </c>
@@ -47369,7 +47814,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="205" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="30">
         <v>205</v>
       </c>
@@ -47530,7 +47975,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="206" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="30">
         <v>206</v>
       </c>
@@ -47691,7 +48136,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="207" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="30">
         <v>207</v>
       </c>
@@ -47852,7 +48297,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="208" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="30">
         <v>208</v>
       </c>
@@ -48013,7 +48458,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="209" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="30">
         <v>209</v>
       </c>
@@ -48174,7 +48619,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="210" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="30">
         <v>210</v>
       </c>
@@ -48335,7 +48780,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="211" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="30">
         <v>211</v>
       </c>
@@ -48496,7 +48941,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="212" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="30">
         <v>212</v>
       </c>
@@ -48657,7 +49102,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="213" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="30">
         <v>213</v>
       </c>
@@ -48818,7 +49263,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="214" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="30">
         <v>214</v>
       </c>
@@ -48979,7 +49424,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="215" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="30">
         <v>215</v>
       </c>
@@ -49140,7 +49585,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="216" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="30">
         <v>216</v>
       </c>
@@ -49301,7 +49746,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="217" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="30">
         <v>217</v>
       </c>
@@ -49462,7 +49907,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="218" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="30">
         <v>218</v>
       </c>
@@ -49623,7 +50068,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="219" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="30">
         <v>219</v>
       </c>
@@ -49784,7 +50229,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="220" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="30">
         <v>220</v>
       </c>
@@ -49945,7 +50390,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="221" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="30">
         <v>221</v>
       </c>
@@ -50106,7 +50551,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="222" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="30">
         <v>222</v>
       </c>
@@ -50267,7 +50712,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="223" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="30">
         <v>223</v>
       </c>
@@ -50428,7 +50873,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="224" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="30">
         <v>224</v>
       </c>
@@ -50589,7 +51034,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="225" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="30">
         <v>225</v>
       </c>
@@ -50750,7 +51195,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="226" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="30">
         <v>226</v>
       </c>
@@ -50911,7 +51356,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="227" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="30">
         <v>227</v>
       </c>
@@ -51072,7 +51517,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="228" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="30">
         <v>228</v>
       </c>
@@ -51233,7 +51678,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="229" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="30">
         <v>229</v>
       </c>
@@ -51394,7 +51839,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="230" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="30">
         <v>230</v>
       </c>
@@ -51555,7 +52000,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="231" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="30">
         <v>231</v>
       </c>
@@ -51716,7 +52161,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="232" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="30">
         <v>232</v>
       </c>
@@ -51877,7 +52322,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="233" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="30">
         <v>233</v>
       </c>
@@ -52038,7 +52483,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="234" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="30">
         <v>234</v>
       </c>
@@ -52199,7 +52644,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="235" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="30">
         <v>235</v>
       </c>
@@ -52360,7 +52805,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="236" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="30">
         <v>236</v>
       </c>
@@ -52521,7 +52966,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="237" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="30">
         <v>237</v>
       </c>
@@ -52682,7 +53127,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="238" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="30">
         <v>238</v>
       </c>
@@ -52843,7 +53288,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="239" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="30">
         <v>239</v>
       </c>
@@ -53004,7 +53449,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="240" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="30">
         <v>240</v>
       </c>
@@ -53165,7 +53610,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="241" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="30">
         <v>241</v>
       </c>
@@ -53326,7 +53771,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="242" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="30">
         <v>242</v>
       </c>
@@ -53487,7 +53932,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="243" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="30">
         <v>243</v>
       </c>
@@ -53648,7 +54093,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="244" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="30">
         <v>244</v>
       </c>
@@ -53809,7 +54254,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="245" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="30">
         <v>245</v>
       </c>
@@ -53970,7 +54415,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="246" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="30">
         <v>246</v>
       </c>
@@ -54131,7 +54576,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="247" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="30">
         <v>247</v>
       </c>
@@ -54292,7 +54737,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="248" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="30">
         <v>248</v>
       </c>
@@ -54453,7 +54898,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="249" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="30">
         <v>249</v>
       </c>
@@ -54614,7 +55059,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="250" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="30">
         <v>250</v>
       </c>
@@ -54775,7 +55220,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="251" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="30">
         <v>251</v>
       </c>
@@ -54936,7 +55381,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="252" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="30">
         <v>252</v>
       </c>
@@ -55097,7 +55542,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="253" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="30">
         <v>253</v>
       </c>
@@ -55258,7 +55703,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="254" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="30">
         <v>254</v>
       </c>
@@ -55419,7 +55864,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="255" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="30">
         <v>255</v>
       </c>
@@ -55580,7 +56025,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="256" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="30">
         <v>256</v>
       </c>
@@ -55741,7 +56186,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="257" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="30">
         <v>257</v>
       </c>
@@ -55902,7 +56347,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="258" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="30">
         <v>258</v>
       </c>
@@ -56063,7 +56508,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="259" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="30">
         <v>259</v>
       </c>
@@ -56224,7 +56669,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="260" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="30">
         <v>260</v>
       </c>
@@ -56385,7 +56830,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="261" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="30">
         <v>261</v>
       </c>
@@ -56546,7 +56991,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="262" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="30">
         <v>262</v>
       </c>
@@ -56707,7 +57152,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="263" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="30">
         <v>263</v>
       </c>
@@ -56868,7 +57313,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="264" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="30">
         <v>264</v>
       </c>
@@ -57029,7 +57474,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="265" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="30">
         <v>265</v>
       </c>
@@ -57190,7 +57635,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="266" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="30">
         <v>266</v>
       </c>
@@ -57351,7 +57796,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="267" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="30">
         <v>267</v>
       </c>
@@ -57512,7 +57957,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="268" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="30">
         <v>268</v>
       </c>
@@ -57673,7 +58118,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="269" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="30">
         <v>269</v>
       </c>
@@ -57834,7 +58279,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="270" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="30">
         <v>270</v>
       </c>
@@ -57995,7 +58440,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="271" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="30">
         <v>271</v>
       </c>
@@ -58156,7 +58601,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="272" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="30">
         <v>272</v>
       </c>
@@ -58317,7 +58762,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="273" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="30">
         <v>273</v>
       </c>
@@ -58478,7 +58923,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="274" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="30">
         <v>274</v>
       </c>
@@ -58639,7 +59084,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="275" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="30">
         <v>275</v>
       </c>
@@ -58800,7 +59245,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="276" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="30">
         <v>276</v>
       </c>
@@ -58961,7 +59406,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="277" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="30">
         <v>277</v>
       </c>
@@ -59122,7 +59567,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="278" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="30">
         <v>278</v>
       </c>
@@ -59283,7 +59728,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="279" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="30">
         <v>279</v>
       </c>
@@ -59444,7 +59889,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="280" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="30">
         <v>280</v>
       </c>
@@ -59605,7 +60050,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="281" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="30">
         <v>281</v>
       </c>
@@ -59766,7 +60211,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="282" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="30">
         <v>282</v>
       </c>
@@ -59927,7 +60372,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="283" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="30">
         <v>283</v>
       </c>
@@ -60088,7 +60533,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="284" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="30">
         <v>284</v>
       </c>
@@ -60249,7 +60694,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="285" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="30">
         <v>285</v>
       </c>
@@ -60410,7 +60855,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="286" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="30">
         <v>286</v>
       </c>
@@ -60571,7 +61016,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="287" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="30">
         <v>287</v>
       </c>
@@ -60732,7 +61177,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="288" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="30">
         <v>288</v>
       </c>
@@ -60893,7 +61338,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="289" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="30">
         <v>289</v>
       </c>
@@ -61054,7 +61499,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="290" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="30">
         <v>290</v>
       </c>
@@ -61215,7 +61660,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="291" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="30">
         <v>291</v>
       </c>
@@ -61376,7 +61821,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="292" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="30">
         <v>292</v>
       </c>
@@ -61537,7 +61982,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="293" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="30">
         <v>293</v>
       </c>
@@ -61698,7 +62143,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="294" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="30">
         <v>294</v>
       </c>
@@ -61859,7 +62304,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="295" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="30">
         <v>295</v>
       </c>
@@ -62020,7 +62465,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="296" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="30">
         <v>296</v>
       </c>
@@ -62181,7 +62626,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="297" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="30">
         <v>297</v>
       </c>
@@ -62342,7 +62787,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="298" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="30">
         <v>298</v>
       </c>
@@ -62503,7 +62948,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="299" spans="1:53" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:53" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="30">
         <v>299</v>
       </c>
@@ -62669,16 +63114,16 @@
     <sortCondition ref="A1:A302"/>
   </sortState>
   <conditionalFormatting sqref="A1:BA299">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B299">
-    <cfRule type="duplicateValues" dxfId="2" priority="1923"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1924"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1923"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1924"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C264">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ARQ/Ontologia_Paisagismo.xlsx
+++ b/Versão5/ARQ/Ontologia_Paisagismo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88210F22-9421-434C-A551-1D547CE6013F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8126D0A-61D8-4928-9E1C-E9611A5608A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="577" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="577" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16534" uniqueCount="1544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16618" uniqueCount="1545">
   <si>
     <t>Key</t>
   </si>
@@ -4703,6 +4703,9 @@
   </si>
   <si>
     <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -5406,35 +5409,7 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="23">
     <dxf>
       <font>
         <b val="0"/>
@@ -5528,7 +5503,6 @@
       <font>
         <b val="0"/>
         <i/>
-        <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -5552,20 +5526,7 @@
       <font>
         <b val="0"/>
         <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
+        <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -5607,6 +5568,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
@@ -5617,6 +5588,14 @@
       <font>
         <b val="0"/>
         <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -6141,7 +6120,7 @@
       </c>
       <c r="B18" s="62">
         <f ca="1">NOW()</f>
-        <v>46268.509091087966</v>
+        <v>46268.688899189816</v>
       </c>
       <c r="C18" s="84" t="s">
         <v>1223</v>
@@ -6396,7 +6375,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AD84"/>
   <sheetFormatPr defaultColWidth="32.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
@@ -6424,10 +6403,11 @@
     <col min="27" max="27" width="41.7109375" style="27" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="8.42578125" style="27" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="13.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="32.140625" style="27"/>
+    <col min="30" max="30" width="8.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="32.140625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13">
         <v>1</v>
       </c>
@@ -6515,8 +6495,11 @@
       <c r="AC1" s="15" t="s">
         <v>1519</v>
       </c>
+      <c r="AD1" s="83" t="s">
+        <v>1544</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="99">
         <v>2</v>
       </c>
@@ -6612,8 +6595,11 @@
       <c r="AC2" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD2" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="99">
         <v>3</v>
       </c>
@@ -6709,8 +6695,11 @@
       <c r="AC3" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD3" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="99">
         <v>4</v>
       </c>
@@ -6806,8 +6795,11 @@
       <c r="AC4" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD4" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="99">
         <v>5</v>
       </c>
@@ -6903,8 +6895,11 @@
       <c r="AC5" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD5" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="99">
         <v>6</v>
       </c>
@@ -7000,8 +6995,11 @@
       <c r="AC6" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD6" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="99">
         <v>7</v>
       </c>
@@ -7097,8 +7095,11 @@
       <c r="AC7" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD7" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="99">
         <v>8</v>
       </c>
@@ -7194,8 +7195,11 @@
       <c r="AC8" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD8" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="99">
         <v>9</v>
       </c>
@@ -7291,8 +7295,11 @@
       <c r="AC9" s="23" t="s">
         <v>1256</v>
       </c>
+      <c r="AD9" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="99">
         <v>10</v>
       </c>
@@ -7388,8 +7395,11 @@
       <c r="AC10" s="23" t="s">
         <v>1256</v>
       </c>
+      <c r="AD10" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="99">
         <v>11</v>
       </c>
@@ -7485,8 +7495,11 @@
       <c r="AC11" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD11" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="99">
         <v>12</v>
       </c>
@@ -7582,8 +7595,11 @@
       <c r="AC12" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD12" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="99">
         <v>13</v>
       </c>
@@ -7679,8 +7695,11 @@
       <c r="AC13" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD13" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="99">
         <v>14</v>
       </c>
@@ -7776,8 +7795,11 @@
       <c r="AC14" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD14" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="99">
         <v>15</v>
       </c>
@@ -7873,8 +7895,11 @@
       <c r="AC15" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD15" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="99">
         <v>16</v>
       </c>
@@ -7970,8 +7995,11 @@
       <c r="AC16" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD16" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="99">
         <v>17</v>
       </c>
@@ -8067,8 +8095,11 @@
       <c r="AC17" s="23" t="s">
         <v>1261</v>
       </c>
+      <c r="AD17" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="99">
         <v>18</v>
       </c>
@@ -8164,8 +8195,11 @@
       <c r="AC18" s="23" t="s">
         <v>1261</v>
       </c>
+      <c r="AD18" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="99">
         <v>19</v>
       </c>
@@ -8261,8 +8295,11 @@
       <c r="AC19" s="23" t="s">
         <v>1261</v>
       </c>
+      <c r="AD19" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="99">
         <v>20</v>
       </c>
@@ -8358,8 +8395,11 @@
       <c r="AC20" s="23" t="s">
         <v>1257</v>
       </c>
+      <c r="AD20" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="99">
         <v>21</v>
       </c>
@@ -8455,8 +8495,11 @@
       <c r="AC21" s="23" t="s">
         <v>1261</v>
       </c>
+      <c r="AD21" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="99">
         <v>22</v>
       </c>
@@ -8552,8 +8595,11 @@
       <c r="AC22" s="23" t="s">
         <v>1261</v>
       </c>
+      <c r="AD22" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="99">
         <v>23</v>
       </c>
@@ -8649,8 +8695,11 @@
       <c r="AC23" s="23" t="s">
         <v>1256</v>
       </c>
+      <c r="AD23" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="99">
         <v>24</v>
       </c>
@@ -8746,8 +8795,11 @@
       <c r="AC24" s="23" t="s">
         <v>1256</v>
       </c>
+      <c r="AD24" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="99">
         <v>25</v>
       </c>
@@ -8843,8 +8895,11 @@
       <c r="AC25" s="23" t="s">
         <v>1260</v>
       </c>
+      <c r="AD25" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="99">
         <v>26</v>
       </c>
@@ -8940,8 +8995,11 @@
       <c r="AC26" s="23" t="s">
         <v>1261</v>
       </c>
+      <c r="AD26" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="99">
         <v>27</v>
       </c>
@@ -9037,8 +9095,11 @@
       <c r="AC27" s="23" t="s">
         <v>1261</v>
       </c>
+      <c r="AD27" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="99">
         <v>28</v>
       </c>
@@ -9134,8 +9195,11 @@
       <c r="AC28" s="23" t="s">
         <v>1261</v>
       </c>
+      <c r="AD28" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="99">
         <v>29</v>
       </c>
@@ -9232,8 +9296,11 @@
       <c r="AC29" s="101" t="s">
         <v>1364</v>
       </c>
+      <c r="AD29" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="99">
         <v>30</v>
       </c>
@@ -9330,8 +9397,11 @@
       <c r="AC30" s="101" t="s">
         <v>1364</v>
       </c>
+      <c r="AD30" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="99">
         <v>31</v>
       </c>
@@ -9428,8 +9498,11 @@
       <c r="AC31" s="101" t="s">
         <v>1364</v>
       </c>
+      <c r="AD31" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="99">
         <v>32</v>
       </c>
@@ -9526,8 +9599,11 @@
       <c r="AC32" s="101" t="s">
         <v>1372</v>
       </c>
+      <c r="AD32" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="99">
         <v>33</v>
       </c>
@@ -9624,8 +9700,11 @@
       <c r="AC33" s="101" t="s">
         <v>1372</v>
       </c>
+      <c r="AD33" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="99">
         <v>34</v>
       </c>
@@ -9722,8 +9801,11 @@
       <c r="AC34" s="101" t="s">
         <v>1372</v>
       </c>
+      <c r="AD34" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="99">
         <v>35</v>
       </c>
@@ -9820,8 +9902,11 @@
       <c r="AC35" s="101" t="s">
         <v>1372</v>
       </c>
+      <c r="AD35" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="99">
         <v>36</v>
       </c>
@@ -9918,8 +10003,11 @@
       <c r="AC36" s="101" t="s">
         <v>1383</v>
       </c>
+      <c r="AD36" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="99">
         <v>37</v>
       </c>
@@ -10016,8 +10104,11 @@
       <c r="AC37" s="101" t="s">
         <v>1386</v>
       </c>
+      <c r="AD37" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="99">
         <v>38</v>
       </c>
@@ -10114,8 +10205,11 @@
       <c r="AC38" s="101" t="s">
         <v>1386</v>
       </c>
+      <c r="AD38" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="99">
         <v>39</v>
       </c>
@@ -10212,8 +10306,11 @@
       <c r="AC39" s="101" t="s">
         <v>1386</v>
       </c>
+      <c r="AD39" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="99">
         <v>40</v>
       </c>
@@ -10310,8 +10407,11 @@
       <c r="AC40" s="101" t="s">
         <v>1386</v>
       </c>
+      <c r="AD40" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="99">
         <v>41</v>
       </c>
@@ -10408,8 +10508,11 @@
       <c r="AC41" s="101" t="s">
         <v>1386</v>
       </c>
+      <c r="AD41" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="99">
         <v>42</v>
       </c>
@@ -10506,8 +10609,11 @@
       <c r="AC42" s="101" t="s">
         <v>1364</v>
       </c>
+      <c r="AD42" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="99">
         <v>43</v>
       </c>
@@ -10604,8 +10710,11 @@
       <c r="AC43" s="101" t="s">
         <v>1364</v>
       </c>
+      <c r="AD43" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="99">
         <v>44</v>
       </c>
@@ -10702,8 +10811,11 @@
       <c r="AC44" s="101" t="s">
         <v>1405</v>
       </c>
+      <c r="AD44" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="99">
         <v>45</v>
       </c>
@@ -10800,8 +10912,11 @@
       <c r="AC45" s="101" t="s">
         <v>1405</v>
       </c>
+      <c r="AD45" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="99">
         <v>46</v>
       </c>
@@ -10898,8 +11013,11 @@
       <c r="AC46" s="101" t="s">
         <v>1410</v>
       </c>
+      <c r="AD46" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="47" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="99">
         <v>47</v>
       </c>
@@ -10996,8 +11114,11 @@
       <c r="AC47" s="101" t="s">
         <v>1405</v>
       </c>
+      <c r="AD47" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="99">
         <v>48</v>
       </c>
@@ -11094,8 +11215,11 @@
       <c r="AC48" s="101" t="s">
         <v>1405</v>
       </c>
+      <c r="AD48" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="49" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="99">
         <v>49</v>
       </c>
@@ -11191,8 +11315,11 @@
       <c r="AC49" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD49" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="50" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="99">
         <v>50</v>
       </c>
@@ -11288,8 +11415,11 @@
       <c r="AC50" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD50" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="51" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="99">
         <v>51</v>
       </c>
@@ -11385,8 +11515,11 @@
       <c r="AC51" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD51" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="52" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="99">
         <v>52</v>
       </c>
@@ -11482,8 +11615,11 @@
       <c r="AC52" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD52" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="53" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="99">
         <v>53</v>
       </c>
@@ -11579,8 +11715,11 @@
       <c r="AC53" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD53" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="54" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="99">
         <v>54</v>
       </c>
@@ -11676,8 +11815,11 @@
       <c r="AC54" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD54" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="55" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="99">
         <v>55</v>
       </c>
@@ -11773,8 +11915,11 @@
       <c r="AC55" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD55" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="56" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="99">
         <v>56</v>
       </c>
@@ -11870,8 +12015,11 @@
       <c r="AC56" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD56" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="57" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="99">
         <v>57</v>
       </c>
@@ -11967,8 +12115,11 @@
       <c r="AC57" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD57" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="99">
         <v>58</v>
       </c>
@@ -12064,8 +12215,11 @@
       <c r="AC58" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD58" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="59" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="99">
         <v>59</v>
       </c>
@@ -12161,8 +12315,11 @@
       <c r="AC59" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD59" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="60" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="99">
         <v>60</v>
       </c>
@@ -12258,8 +12415,11 @@
       <c r="AC60" s="23" t="s">
         <v>1256</v>
       </c>
+      <c r="AD60" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="61" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="99">
         <v>61</v>
       </c>
@@ -12355,8 +12515,11 @@
       <c r="AC61" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD61" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="62" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="99">
         <v>62</v>
       </c>
@@ -12452,8 +12615,11 @@
       <c r="AC62" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD62" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="63" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="99">
         <v>63</v>
       </c>
@@ -12549,8 +12715,11 @@
       <c r="AC63" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD63" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="64" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="99">
         <v>64</v>
       </c>
@@ -12646,8 +12815,11 @@
       <c r="AC64" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD64" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="65" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="99">
         <v>65</v>
       </c>
@@ -12743,8 +12915,11 @@
       <c r="AC65" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD65" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="66" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="99">
         <v>66</v>
       </c>
@@ -12840,8 +13015,11 @@
       <c r="AC66" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD66" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="67" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="99">
         <v>67</v>
       </c>
@@ -12937,8 +13115,11 @@
       <c r="AC67" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD67" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="68" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="99">
         <v>68</v>
       </c>
@@ -13034,8 +13215,11 @@
       <c r="AC68" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD68" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="69" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="99">
         <v>69</v>
       </c>
@@ -13131,8 +13315,11 @@
       <c r="AC69" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD69" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="70" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="99">
         <v>70</v>
       </c>
@@ -13228,8 +13415,11 @@
       <c r="AC70" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD70" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="71" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="99">
         <v>71</v>
       </c>
@@ -13325,8 +13515,11 @@
       <c r="AC71" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD71" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="72" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="99">
         <v>72</v>
       </c>
@@ -13422,8 +13615,11 @@
       <c r="AC72" s="23" t="s">
         <v>1256</v>
       </c>
+      <c r="AD72" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="73" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="99">
         <v>73</v>
       </c>
@@ -13519,8 +13715,11 @@
       <c r="AC73" s="23" t="s">
         <v>1255</v>
       </c>
+      <c r="AD73" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="74" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="99">
         <v>74</v>
       </c>
@@ -13616,8 +13815,11 @@
       <c r="AC74" s="23" t="s">
         <v>1256</v>
       </c>
+      <c r="AD74" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="75" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="99">
         <v>75</v>
       </c>
@@ -13713,8 +13915,11 @@
       <c r="AC75" s="23" t="s">
         <v>1256</v>
       </c>
+      <c r="AD75" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="76" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="99">
         <v>76</v>
       </c>
@@ -13810,8 +14015,11 @@
       <c r="AC76" s="23" t="s">
         <v>1256</v>
       </c>
+      <c r="AD76" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="77" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="99">
         <v>77</v>
       </c>
@@ -13907,8 +14115,11 @@
       <c r="AC77" s="23" t="s">
         <v>1256</v>
       </c>
+      <c r="AD77" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="78" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="99">
         <v>78</v>
       </c>
@@ -14004,8 +14215,11 @@
       <c r="AC78" s="23" t="s">
         <v>1315</v>
       </c>
+      <c r="AD78" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="79" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="99">
         <v>79</v>
       </c>
@@ -14101,8 +14315,11 @@
       <c r="AC79" s="23" t="s">
         <v>1318</v>
       </c>
+      <c r="AD79" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="80" spans="1:29" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:30" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="99">
         <v>80</v>
       </c>
@@ -14198,8 +14415,11 @@
       <c r="AC80" s="110" t="s">
         <v>1</v>
       </c>
+      <c r="AD80" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="81" spans="1:29" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:30" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="99">
         <v>81</v>
       </c>
@@ -14295,8 +14515,11 @@
       <c r="AC81" s="110" t="s">
         <v>1</v>
       </c>
+      <c r="AD81" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="82" spans="1:29" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:30" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="99">
         <v>82</v>
       </c>
@@ -14392,8 +14615,11 @@
       <c r="AC82" s="110" t="s">
         <v>1</v>
       </c>
+      <c r="AD82" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="83" spans="1:29" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:30" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="99">
         <v>83</v>
       </c>
@@ -14489,8 +14715,11 @@
       <c r="AC83" s="110" t="s">
         <v>1</v>
       </c>
+      <c r="AD83" s="110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="84" spans="1:29" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:30" s="111" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="99">
         <v>84</v>
       </c>
@@ -14584,84 +14813,92 @@
         <v>1</v>
       </c>
       <c r="AC84" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD84" s="110" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:B2 B3:B48 A3:A84">
-    <cfRule type="cellIs" dxfId="0" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="33" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:C1 S1:X1 L1:Q28 L49:Q71 B49:B79 L72:P79 AA75:AA77 A85:C1048576 L85:X1048576">
-    <cfRule type="cellIs" dxfId="25" priority="443" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="444" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B80:B84">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E84:F84">
+    <cfRule type="duplicateValues" dxfId="19" priority="3"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F79 F85:F1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F80:F83">
+    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q72:Q79">
-    <cfRule type="cellIs" dxfId="21" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="34" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R79">
-    <cfRule type="cellIs" dxfId="20" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y73:Y74 AA73:AA74">
+    <cfRule type="cellIs" dxfId="14" priority="35" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y78">
+    <cfRule type="containsText" dxfId="13" priority="36" operator="containsText" text="null">
+      <formula>NOT(ISERROR(SEARCH("null",Y78)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z1">
+    <cfRule type="cellIs" dxfId="12" priority="9" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z85:XFD1048576">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1:AA16 AC1:AC28 AA23:AA28">
+    <cfRule type="cellIs" dxfId="10" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA49:AA72 AC49:AC77">
-    <cfRule type="cellIs" dxfId="18" priority="12" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y73:Y74 AA73:AA74">
-    <cfRule type="cellIs" dxfId="16" priority="34" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y78">
-    <cfRule type="containsText" dxfId="15" priority="35" operator="containsText" text="null">
-      <formula>NOT(ISERROR(SEARCH("null",Y78)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z85:XFD1048576">
-    <cfRule type="cellIs" dxfId="13" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA16 AC1:AC28 AA23:AA28">
-    <cfRule type="cellIs" dxfId="12" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD1:XFD79 T2:V79 D29:D48 L29:P48">
-    <cfRule type="cellIs" dxfId="10" priority="23" operator="equal">
+  <conditionalFormatting sqref="AE1:XFD79 T2:V79 D29:D48 L29:P48">
+    <cfRule type="cellIs" dxfId="7" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B80:B84">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+  <conditionalFormatting sqref="AD1">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E84:F84">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F80:F83">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -14812,7 +15049,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14902,7 +15139,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4">
-    <cfRule type="cellIs" dxfId="8" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63114,16 +63351,16 @@
     <sortCondition ref="A1:A302"/>
   </sortState>
   <conditionalFormatting sqref="A1:BA299">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B299">
-    <cfRule type="duplicateValues" dxfId="6" priority="1923"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1924"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1923"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1924"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C264">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
